--- a/results/gap_matrix_reviewed.xlsx
+++ b/results/gap_matrix_reviewed.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="gap_matrix" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="evidence" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gap_matrix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="evidence" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -561,37 +561,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hasan, H. A., Al-Hussayni, K. H., &amp; Matloob, A. Z. K. (2025). Attention Mapping for Hallucination Reduction in Arabic Financial Using Retrieval-Augmented Generation Systems. Journal of Intelligent Informatics, Networking, and Cybersecurity 1(2). https://doi.org/10.65445/3106-1192.1006</t>
+          <t>Zhao, Y., Singh, P., Bhathena, H., et al. (2024). Optimizing LLM Based Retrieval Augmented Generation Pipelines in the Financial Domain. NAACL 2024 Industry Track, 279-294. https://doi.org/10.18653/v1/2024.naacl-industry.23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Penelitian ini mengatasi masalah halusinasi pada sistem Retrieval-Augmented Generation (RAG) bahasa Arab untuk analisis dokumen keuangan.</t>
+          <t>Penulis menilai faktor-faktor yang memengaruhi kualitas jawaban dalam sistem RAG LLM pada domain keuangan, termasuk sensitivitas terhadap kualitas retrieval dan dampak prompt.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Domain keuangan, dokumen finansial berbahasa Arab, dengan dataset baru berisi 7.000 pasangan query-konteks beranotasi.</t>
+          <t>Studi memakai dua dataset RAG di sektor perbankan: halaman web publik berisi informasi umum produk perbankan dan panduan kebijakan internal untuk customer service executive. Pertanyaan berasal dari pengguna nyata (log sistem produksi), dan 800 query di-sampling per dataset.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Metode memperluas MarBERT dengan mekanisme supervisi perhatian dua tahap dan loss yang sadar halusinasi, serta ambang presisi dinamis untuk penolakan output.</t>
+          <t>Retriever menggunakan OpenAI Embeddings, dokumen dipotong menjadi chunk, dan generator berupa model LLM seperti GPT-4 dan Llama-2; variasi kualitas retrieval diuji dengan manipulasi list hasil retrieval.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dievaluasi dengan akurasi klasifikasi 95.04%, presisi 95.84%, recall 94.12%, F1 94.97%, serta deteksi halusinasi 87.63% dengan false alarm 8.91% dan latensi 3.2 token.</t>
+          <t>Evaluasi mencakup kemampuan LLM mengikuti instruksi, kualitas jawaban, serta metrik ekstraktivitas, dengan perbandingan antar model seperti GPT-4, GPT-3.5-Turbo, dan Llama-2.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Model mencapai akurasi klasifikasi 95,04% dan F1 94,97%, mengungguli baseline AraELECTRA dan mBERT-RAG. Untuk deteksi halusinasi, detection rate mencapai 87,63% dengan false alarm hanya 8,91% dan latensi deteksi 3,2 token.</t>
+          <t>Optimasi retrieval penting meskipun memakai GPT-4: recall retrieval perlu diprioritaskan karena LLM menunjukkan pseudo-helpfulness ketika dokumen gold tidak ter-retrieve, dan peningkatan precision diperkirakan memperbaiki performa. Model sensitif terhadap distractor; selisih besar terlihat antara LLM vendor (OpenAI) dan model open-source kecil, dan Llama-2 kecil sering gagal mengikuti instruksi panjang.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -601,900 +601,477 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Inferensi: Meskipun berhasil mengurangi halusinasi pada RAG bahasa Arab, penelitian ini tidak mengevaluasi faithfulness atau abstention pada dokumen perbankan berbahasa Indonesia, sehingga belum menjawab fokus riset yang diusulkan.</t>
+          <t>Inferensi: Meskipun menilai kualitas jawaban, studi tidak mengevaluasi abstensi (menolak menjawab) ketika konteks tidak mengandung jawaban, dan tidak menggunakan dokumen perbankan berbahasa Indonesia, sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada dokumen bahasa Indonesia.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zhao, Y., Singh, P., Bhathena, H., et al. (2024). Optimizing LLM Based Retrieval Augmented Generation Pipelines in the Financial Domain. NAACL 2024 Industry Track, 279-294. https://doi.org/10.18653/v1/2024.naacl-industry.23</t>
+          <t>Chen, J., Zhou, P., Hua, Y., et al. (2024). FinTextQA: A Dataset for Long-form Financial Question Answering. ACL 2024 (Long Papers), 6025-6047. https://doi.org/10.18653/v1/2024.acl-long.328</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Penulis menilai faktor-faktor yang memengaruhi kualitas jawaban dalam sistem RAG LLM pada domain keuangan, termasuk sensitivitas terhadap kualitas retrieval dan dampak prompt.</t>
+          <t>Paper memperkenalkan dataset LFQA keuangan pertama dan melakukan benchmark komprehensif untuk menilai kemampuan model dalam menjawab pertanyaan keuangan.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Studi memakai dua dataset RAG di sektor perbankan: halaman web publik berisi informasi umum produk perbankan dan panduan kebijakan internal untuk customer service executive. Pertanyaan berasal dari pengguna nyata (log sistem produksi), dan 800 query di-sampling per dataset.</t>
+          <t>Dataset FinTextQA di domain keuangan berisi 1.262 pasangan QA dari buku teks keuangan (BMFS, FCF, EMBFM) serta regulasi dan kebijakan dari situs HKMA, EU, dan Federal Reserve; dari 300 pasangan regulasi/kebijakan awal, 240 dipertahankan setelah kontrol kualitas.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Retriever menggunakan OpenAI Embeddings, dokumen dipotong menjadi chunk, dan generator berupa model LLM seperti GPT-4 dan Llama-2; variasi kualitas retrieval diuji dengan manipulasi list hasil retrieval.</t>
+          <t>Menggunakan empat embedder (Bge-small-en-v1.5, Gte-large, Ember-v1, Ada), tiga retriever (AMR, SWR, vector-based), tiga reranker (LLMRerank, Bge-Reranker-Base, All-Mpnet-Base-v2), serta generator LLM termasuk Baichuan2-7B.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Evaluasi mencakup kemampuan LLM mengikuti instruksi, kualitas jawaban, serta metrik ekstraktivitas, dengan perbandingan antar model seperti GPT-4, GPT-3.5-Turbo, dan Llama-2.</t>
+          <t>Evaluasi memakai ROUGE-1/2/L dan BLEU, skor GPT-4 (Likert lima poin) atas helpfulness, relevansi, akurasi, kedalaman, dan kreativitas, rasio pertanyaan tidak terjawab, serta ranking jawaban terbaik oleh tiga anotator manusia dibandingkan ground truth.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Optimasi retrieval penting meskipun memakai GPT-4: recall retrieval perlu diprioritaskan karena LLM menunjukkan pseudo-helpfulness ketika dokumen gold tidak ter-retrieve, dan peningkatan precision diperkirakan memperbaiki performa. Model sensitif terhadap distractor; selisih besar terlihat antara LLM vendor (OpenAI) dan model open-source kecil, dan Llama-2 kecil sering gagal mengikuti instruksi panjang.</t>
+          <t>Embedder Ada mencapai skor GPT-4 tertinggi 4.586; retriever AMR memperoleh 4.492; kombinasi AMR, Ada, Bge-Reranker-Base menghasilkan skor tertinggi 4.622. Generator pada dataset regulasi memperoleh ROUGE-1 0.317 dan GPT-4 4.238.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>tidak disebut</t>
+          <t>FinTextQA memiliki jumlah pasangan QA relatif kecil dibanding dataset AI-generated yang lebih besar, sehingga dapat memengaruhi generalisasi; data berkualitas tinggi sulit diperoleh dan pembatasan hak cipta sering menghalangi berbagi data.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Inferensi: Meskipun menilai kualitas jawaban, studi tidak mengevaluasi abstensi (menolak menjawab) ketika konteks tidak mengandung jawaban, dan tidak menggunakan dokumen perbankan berbahasa Indonesia, sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada dokumen bahasa Indonesia.</t>
+          <t>Inferensi: Meskipun FinTextQA menyediakan benchmark LFQA keuangan, penelitian ini tidak mengevaluasi faithfulness atau kemampuan abstention pada dokumen produk perbankan berbahasa Indonesia, sehingga belum menjawab fokus riset yang diusulkan.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Chen, J., Zhou, P., Hua, Y., et al. (2024). FinTextQA: A Dataset for Long-form Financial Question Answering. ACL 2024 (Long Papers), 6025-6047. https://doi.org/10.18653/v1/2024.acl-long.328</t>
+          <t>Iaroshev, I., Pillai, R., Vaglietti, L., et al. (2024). Evaluating Retrieval-Augmented Generation Models for Financial Report Question and Answering. Applied Sciences 14(20), 9318. https://doi.org/10.3390/app14209318</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Paper memperkenalkan dataset LFQA keuangan pertama dan melakukan benchmark komprehensif untuk menilai kemampuan model dalam menjawab pertanyaan keuangan.</t>
+          <t>Penelitian ini mengeksplorasi penerapan retrieval-augmented generation (RAG) untuk meningkatkan akurasi dan keandalan model bahasa besar dalam analisis laporan keuangan bank.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Dataset FinTextQA di domain keuangan berisi 1.262 pasangan QA dari buku teks keuangan (BMFS, FCF, EMBFM) serta regulasi dan kebijakan dari situs HKMA, EU, dan Federal Reserve; dari 300 pasangan regulasi/kebijakan awal, 240 dipertahankan setelah kontrol kualitas.</t>
+          <t>Domainnya adalah laporan keuangan bank (setengah tahunan atau kuartalan) untuk investor pribadi; bahasa tidak disebutkan dalam abstrak.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Menggunakan empat embedder (Bge-small-en-v1.5, Gte-large, Ember-v1, Ada), tiga retriever (AMR, SWR, vector-based), tiga reranker (LLMRerank, Bge-Reranker-Base, All-Mpnet-Base-v2), serta generator LLM termasuk Baichuan2-7B.</t>
+          <t>Sistem RAG dikembangkan dengan metodologi Design Science Research; beberapa model dengan komponen RAG berbeda diuji, antara lain model satu (OpenAI ADA dan OpenAI GPT-4) dan model tiga (MiniLM Embedder dan OpenAI GPT-4).</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Evaluasi memakai ROUGE-1/2/L dan BLEU, skor GPT-4 (Likert lima poin) atas helpfulness, relevansi, akurasi, kedalaman, dan kreativitas, rasio pertanyaan tidak terjawab, serta ranking jawaban terbaik oleh tiga anotator manusia dibandingkan ground truth.</t>
+          <t>Evaluasi dilakukan dengan mengukur akurasi, relevansi jawaban, serta perbandingan kinerja pada laporan terstruktur vs tidak terstruktur dan pertanyaan kualitatif vs kuantitatif.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Embedder Ada mencapai skor GPT-4 tertinggi 4.586; retriever AMR memperoleh 4.492; kombinasi AMR, Ada, Bge-Reranker-Base menghasilkan skor tertinggi 4.622. Generator pada dataset regulasi memperoleh ROUGE-1 0.317 dan GPT-4 4.238.</t>
+          <t>Model satu (OpenAI ADA + GPT-4) memberikan performa tertinggi, sedangkan model tiga (MiniLM + GPT-4) jauh lebih rendah; laporan terstruktur meningkatkan kinerja RAG, dan pertanyaan kualitatif memperoleh skor lebih tinggi.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>FinTextQA memiliki jumlah pasangan QA relatif kecil dibanding dataset AI-generated yang lebih besar, sehingga dapat memengaruhi generalisasi; data berkualitas tinggi sulit diperoleh dan pembatasan hak cipta sering menghalangi berbagi data.</t>
+          <t>tidak disebut</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Inferensi: Meskipun FinTextQA menyediakan benchmark LFQA keuangan, penelitian ini tidak mengevaluasi faithfulness atau kemampuan abstention pada dokumen produk perbankan berbahasa Indonesia, sehingga belum menjawab fokus riset yang diusulkan.</t>
+          <t>Inferensi: Meskipun studi ini menyebutkan peningkatan answer faithfulness, tidak mengevaluasi abstention atau penggunaan dokumen bahasa Indonesia, sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada dokumen produk perbankan berbahasa Indonesia.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Iaroshev, I., Pillai, R., Vaglietti, L., et al. (2024). Evaluating Retrieval-Augmented Generation Models for Financial Report Question and Answering. Applied Sciences 14(20), 9318. https://doi.org/10.3390/app14209318</t>
+          <t>Lithgow-Serrano, O., Kletz, D., Kanjirangat, V., et al. (2025). Assessing RAG System Capabilities on Financial Documents. FinNLP 2025, 124-147. https://doi.org/10.18653/v1/2025.finnlp-2.9</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Penelitian ini mengeksplorasi penerapan retrieval-augmented generation (RAG) untuk meningkatkan akurasi dan keandalan model bahasa besar dalam analisis laporan keuangan bank.</t>
+          <t>Paper mengidentifikasi kebutuhan akan kerangka evaluasi yang memperhitungkan heterogenitas dokumen, tipe pertanyaan, dan kedalaman penalaran dalam sistem RAG pada domain keuangan.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Domainnya adalah laporan keuangan bank (setengah tahunan atau kuartalan) untuk investor pribadi; bahasa tidak disebutkan dalam abstrak.</t>
+          <t>Benchmark FinDoc-RAG mencakup 600+ pasangan QA dari 46 dokumen keuangan berbahasa Inggris, termasuk deskripsi produk, panduan investasi, kebijakan hukum, dan materi pemasaran dengan konten numerik padat.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sistem RAG dikembangkan dengan metodologi Design Science Research; beberapa model dengan komponen RAG berbeda diuji, antara lain model satu (OpenAI ADA dan OpenAI GPT-4) dan model tiga (MiniLM Embedder dan OpenAI GPT-4).</t>
+          <t>Arsitektur yang dievaluasi meliputi Vector-RAG berbasis indeks vektor dense, tanpa fine-tuning, dengan konfigurasi default serta alur lengkap retrieval-to-answer tanpa intervensi manusia.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Evaluasi dilakukan dengan mengukur akurasi, relevansi jawaban, serta perbandingan kinerja pada laporan terstruktur vs tidak terstruktur dan pertanyaan kualitatif vs kuantitatif.</t>
+          <t>Evaluasi mencakup akurasi rata-rata, LLMLogScore (L3Score) berbasis log-likelihood, serta penilaian biner CORRECT/INCORRECT oleh LLM judge pada tiga run independen.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Model satu (OpenAI ADA + GPT-4) memberikan performa tertinggi, sedangkan model tiga (MiniLM + GPT-4) jauh lebih rendah; laporan terstruktur meningkatkan kinerja RAG, dan pertanyaan kualitatif memperoleh skor lebih tinggi.</t>
+          <t>Sistem teratas mencapai akurasi 0.91 pada ekstraksi faktual, namun hanya 0.44 pada sintesis multi-dokumen; RAPTOR memperoleh skor rata-rata 0.66 (σ=0.17), sementara GFM-RAG mencapai akurasi sempurna 1.00 pada level L3.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>tidak disebut</t>
+          <t>Penulis mencatat pertanyaan yang dibangkitkan otomatis kadang kurang mendalam dibanding pertanyaan buatan manusia, koleksi dokumen hanya sebagian dari ragam dokumen keuangan, dan pendekatan evaluasi multifaset mungkin belum menangkap semua dimensi kualitas jawaban.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Inferensi: Meskipun studi ini menyebutkan peningkatan answer faithfulness, tidak mengevaluasi abstention atau penggunaan dokumen bahasa Indonesia, sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada dokumen produk perbankan berbahasa Indonesia.</t>
+          <t>Tidak ada evaluasi faithfulness atau mekanisme abstention pada dokumen perbankan berbahasa Indonesia; fokus benchmark hanya pada dokumen berbahasa Inggris dan tidak menguji penolakan jawaban ketika konteks tidak memadai. Inferensi: Penelitian selanjutnya perlu menambah bahasa Indonesia serta mengukur kemampuan sistem menolak menjawab pertanyaan di luar cakupan konteks.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P07</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wang, S., Tan, J., Dou, Z., &amp; Wen, J.-R. (2025). OmniEval: An Omnidirectional and Automatic RAG Evaluation Benchmark in Financial Domain. EMNLP 2025, 5726-5751. https://doi.org/10.18653/v1/2025.emnlp-main.292</t>
+          <t>Choi, C., Kwon, J., Ha, J., et al. (2025). FinDER: Financial Dataset for Question Answering and Evaluating Retrieval-Augmented Generation. ACM ICAIF '25. https://doi.org/10.1145/3768292.3770361</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Paper ini mengidentifikasi kebutuhan benchmark RAG yang komprehensif karena benchmark saat ini memiliki skenario sempit dan dimensi evaluasi terbatas.</t>
+          <t>Paper ini mengidentifikasi kebutuhan akan evaluasi sistem Retrieval-Augmented Generation (RAG) yang akurat dalam domain keuangan, mengingat kesalahan kecil dapat berdampak besar pada investasi dan kepatuhan.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Domain keuangan mencakup subdomain seperti perbankan investasi, asuransi, pasar modal, dan lainnya, dengan dokumen berbahasa Mandarin/Chinese yang diambil dari situs resmi dan berbagai format.</t>
+          <t>FINDER dibangun dari kueri pencarian nyata para profesional keuangan untuk menangkap ambiguitas dan ketergantungan konteks kueri keuangan. Kueri dikelompokkan per kategori (mis. Accounting 8,61%, Company Overview 18,95%, Financials 17,36%), dengan 15,48% kueri membutuhkan penalaran kuantitatif; korpus retrieval berasal dari dokumen HTML mentah yang dipecah per paragraf.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Menggunakan retriever seperti BGE-M3, BGE-large-zh, GTE-Qwen2-1.5b, dan jina-zh; generator LLM termasuk Qwen2.5-72B, Deepseek-v2-chat, Yi15-34B, Llama3.1-70B; chunking panjang 2048 dengan overlap 256.</t>
+          <t>Sistem RAG menggunakan retriever BM25 (k1=1.2, b=0.75) serta model dense seperti e5-mistral-7b-instruct, mE5, dan GTE; dokumen dipotong menjadi paragraf, dan generator meliputi GPT-o1, Claude-3.7-Sonnet, Qwen-QWQ-32B, serta DeepSeek-R1-Distill.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Evaluasi menggunakan metrik multi-aspek seperti ACC, HAL (hallucination), NAC (numerical accuracy), Rouge-L, serta MRR dan MAP untuk retriever.</t>
+          <t>Evaluasi mencakup Context Recall (RAGAS), Precision, serta metrik Response Correctness dan Faithfulness pada berbagai tugas keuangan.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>GTE-Qwen2-1.5B menunjukkan performa retrieval terbaik pada sebagian besar metrik; performa RAG bervariasi antar topik dan tugas, dan masih terdapat ruang besar untuk perbaikan.</t>
+          <t>Model e5-mistral mencapai Context Recall tertinggi dengan total 25.95, sementara Claude-3.7-Sonnet memperoleh skor Faithfulness tertinggi pada sebagian besar tugas.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Penulis mengakui distribusi korpus masih terbatas karena kendala aksesibilitas dan lisensi terbuka sumber data, sehingga berisiko memasukkan bias yang dapat memengaruhi generalisasi temuan benchmark.</t>
+          <t>Chunk tidak memuat bagian keterbatasan eksplisit paper. Penulis menyatakan tidak ada satu model pun yang unggul di semua tugas penalaran keuangan, analisis dilakukan pada subset representatif 10% dataset, dan pekerjaan lanjutan disarankan untuk mengintegrasikan sumber dokumen keuangan yang lebih beragam serta model yang memperbaiki kueri secara dinamis.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Inferensi: Paper tidak mengevaluasi kemampuan abstention atau faithfulness pada dokumen produk perbankan berbahasa Indonesia, sehingga tidak mencakup fokus riset yang diinginkan.</t>
+          <t>Inferensi: Meskipun FINDER mengevaluasi faithfulness, tidak ada pembahasan tentang kemampuan sistem menolak menjawab (abstention) ketika konteks tidak mengandung jawaban, dan dataset berbahasa Inggris tidak mencakup dokumen perbankan Indonesia.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P08</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lithgow-Serrano, O., Kletz, D., Kanjirangat, V., et al. (2025). Assessing RAG System Capabilities on Financial Documents. FinNLP 2025, 124-147. https://doi.org/10.18653/v1/2025.finnlp-2.9</t>
+          <t>Ngartera, L., Nadarajah, S., &amp; Koina, R. (2026). Bayesian RAG: Uncertainty-Aware Retrieval for Reliable Financial Question Answering. Frontiers in Artificial Intelligence 8, 1668172. https://doi.org/10.3389/frai.2025.1668172</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Paper mengidentifikasi kebutuhan akan kerangka evaluasi yang memperhitungkan heterogenitas dokumen, tipe pertanyaan, dan kedalaman penalaran dalam sistem RAG pada domain keuangan.</t>
+          <t>Paper ini mengusulkan kerangka Bayesian RAG untuk mengukur ketidakpastian pada proses retrieval demi menjamin jawaban keuangan yang dapat diandalkan.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Benchmark FinDoc-RAG mencakup 600+ pasangan QA dari 46 dokumen keuangan berbahasa Inggris, termasuk deskripsi produk, panduan investasi, kebijakan hukum, dan materi pemasaran dengan konten numerik padat.</t>
+          <t>Eksperimen dilakukan secara eksklusif pada laporan keuangan terstruktur berbahasa Inggris, dengan dataset AAPL 10-K, MSFT 10-K, dan FinSage. Ground truth disusun oleh dua pakar keuangan (Cohen's kappa = 0,87).</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Arsitektur yang dievaluasi meliputi Vector-RAG berbasis indeks vektor dense, tanpa fine-tuning, dengan konfigurasi default serta alur lengkap retrieval-to-answer tanpa intervensi manusia.</t>
+          <t>Menggunakan pipeline lima tahap dengan embedding dense, retrieval semantik via FAISS, dan Monte Carlo dropout (n=10) untuk mengkuantifikasi ketidakpastian pada tahap retrieval.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Evaluasi mencakup akurasi rata-rata, LLMLogScore (L3Score) berbasis log-likelihood, serta penilaian biner CORRECT/INCORRECT oleh LLM judge pada tiga run independen.</t>
+          <t>Dievaluasi dengan metrik faithfulness, hallucination rate, akurasi, AUC, ECE, serta Precision@3, Recall@5, dan MRR; dibandingkan dengan baseline BM25, DPR, dan ColBERT.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sistem teratas mencapai akurasi 0.91 pada ekstraksi faktual, namun hanya 0.44 pada sintesis multi-dokumen; RAPTOR memperoleh skor rata-rata 0.66 (σ=0.17), sementara GFM-RAG mencapai akurasi sempurna 1.00 pada level L3.</t>
+          <t>Bayesian RAG (lambda=0,3) menaikkan faithfulness dari 0,82 menjadi 0,87 dan menurunkan hallucination dari 0,18 menjadi 0,13 dibanding ColBERT. Bayesian RAG + GPT mencapai akurasi 93,1% dengan AUC 0,961 dan ECE 0,034, dan pada zona balanced memberi peningkatan kinerja 25% dengan overhead latency 33 ms.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Penulis mencatat pertanyaan yang dibangkitkan otomatis kadang kurang mendalam dibanding pertanyaan buatan manusia, koleksi dokumen hanya sebagian dari ragam dokumen keuangan, dan pendekatan evaluasi multifaset mungkin belum menangkap semua dimensi kualitas jawaban.</t>
+          <t>Kerangka hanya diuji pada dokumen berbahasa Inggris, tidak memodelkan ketidakpastian aleatorik, dan hasilnya terbatas pada konteks regulasi keuangan.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Tidak ada evaluasi faithfulness atau mekanisme abstention pada dokumen perbankan berbahasa Indonesia; fokus benchmark hanya pada dokumen berbahasa Inggris dan tidak menguji penolakan jawaban ketika konteks tidak memadai. Inferensi: Penelitian selanjutnya perlu menambah bahasa Indonesia serta mengukur kemampuan sistem menolak menjawab pertanyaan di luar cakupan konteks.</t>
+          <t>Inferensi: Meskipun paper menilai faithfulness, tidak ada evaluasi abstention atau analisis pada dokumen perbankan berbahasa Indonesia, sehingga belum menjawab fokus penelitian yang menuntut pengukuran abstention pada produk perbankan Indonesia.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Choi, C., Kwon, J., Ha, J., et al. (2025). FinDER: Financial Dataset for Question Answering and Evaluating Retrieval-Augmented Generation. ACM ICAIF '25. https://doi.org/10.1145/3768292.3770361</t>
+          <t>Sarmah, B., Mehta, D. B., Hall, B., et al. (2024). HybridRAG: Integrating Knowledge Graphs and Vector Retrieval Augmented Generation for Efficient Information Extraction. ACM ICAIF '24. https://doi.org/10.1145/3677052.3698671</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Paper ini mengidentifikasi kebutuhan akan evaluasi sistem Retrieval-Augmented Generation (RAG) yang akurat dalam domain keuangan, mengingat kesalahan kecil dapat berdampak besar pada investasi dan kepatuhan.</t>
+          <t>Paper memperkenalkan HybridRAG, pendekatan gabungan VectorRAG dan GraphRAG untuk meningkatkan analisis dokumen keuangan.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FINDER dibangun dari kueri pencarian nyata para profesional keuangan untuk menangkap ambiguitas dan ketergantungan konteks kueri keuangan. Kueri dikelompokkan per kategori (mis. Accounting 8,61%, Company Overview 18,95%, Financials 17,36%), dengan 15,48% kueri membutuhkan penalaran kuantitatif; korpus retrieval berasal dari dokumen HTML mentah yang dipecah per paragraf.</t>
+          <t>Menggunakan dokumen keuangan perusahaan, khususnya transkrip earnings call, dengan entitas seperti metrik keuangan, eksekutif, dan peristiwa korporasi.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sistem RAG menggunakan retriever BM25 (k1=1.2, b=0.75) serta model dense seperti e5-mistral-7b-instruct, mE5, dan GTE; dokumen dipotong menjadi paragraf, dan generator meliputi GPT-o1, Claude-3.7-Sonnet, Qwen-QWQ-32B, serta DeepSeek-R1-Distill.</t>
+          <t>HybridRAG memakai model embedding text-embedding-ada-002, chunk size 1024, Pinecone vector DB, serta integrasi GraphRAG untuk pencarian semantik dan pemrosesan KG.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Evaluasi mencakup Context Recall (RAGAS), Precision, serta metrik Response Correctness dan Faithfulness pada berbagai tugas keuangan.</t>
+          <t>Dievaluasi dengan metrik faithfulness, answer relevancy, dan context relevance untuk menilai kualitas jawaban dan relevansi konteks.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Model e5-mistral mencapai Context Recall tertinggi dengan total 25.95, sementara Claude-3.7-Sonnet memperoleh skor Faithfulness tertinggi pada sebagian besar tugas.</t>
+          <t>HybridRAG mencapai skor faithfulness 0.96, answer relevancy 0.96, dan context recall 1.0, menunjukkan kinerja seimbang dibandingkan VectorRAG dan GraphRAG.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Chunk tidak memuat bagian keterbatasan eksplisit paper. Penulis menyatakan tidak ada satu model pun yang unggul di semua tugas penalaran keuangan, analisis dilakukan pada subset representatif 10% dataset, dan pekerjaan lanjutan disarankan untuk mengintegrasikan sumber dokumen keuangan yang lebih beragam serta model yang memperbaiki kueri secara dinamis.</t>
+          <t>Chunk tidak memuat bagian keterbatasan eksplisit. Hasil menunjukkan trade-off: context precision HybridRAG (0,79) lebih rendah dari VectorRAG (0,84) dan GraphRAG (0,96). Penulis juga mencatat bahwa komponen GraphRAG lemah pada Q&amp;A abstraktif atau saat pertanyaan tidak menyebut entitas secara eksplisit.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Inferensi: Meskipun FINDER mengevaluasi faithfulness, tidak ada pembahasan tentang kemampuan sistem menolak menjawab (abstention) ketika konteks tidak mengandung jawaban, dan dataset berbahasa Inggris tidak mencakup dokumen perbankan Indonesia.</t>
+          <t>Penelitian ini tidak mengevaluasi abstention (menolak menjawab bila konteks tidak memadai) dan tidak menggunakan dokumen berbahasa Indonesia; Inferensi: sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada dokumen perbankan Indonesia.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Zhao, S., Jin, Z., Li, S., &amp; Gao, J. (2025). FinRAGBench-V: A Benchmark for Multimodal RAG with Visual Citation in the Financial Domain. EMNLP 2025, 4215-4249. https://doi.org/10.18653/v1/2025.emnlp-main.211</t>
+          <t>Wang, X., Chi, J., Tai, Z., et al. (2025). FinSage: A Multi-aspect RAG System for Financial Filings Question Answering. CIKM '25, 6144-6152. https://doi.org/10.1145/3746252.3761587</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Membangun benchmark FinRAGBench-V dan baseline RGenCite untuk RAG multimodal dengan visual citation.</t>
+          <t>Paper ini mengidentifikasi kebutuhan akan sistem QA yang dapat secara efisien mengambil dan menganalisis informasi kepatuhan dari dokumen keuangan.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Domain keuangan dengan korpus halaman dari laporan riset (mis. Qianzhan.com), laporan keuangan perusahaan dan bank (FinGLM serta situs resmi), prospektus (BSCF), makalah akademik (Journal of Financial dan CNKI), dan majalah keuangan seperti Financial Times. Benchmark memiliki subset berbahasa Mandarin dan Inggris.</t>
+          <t>Evaluasi memakai dua dataset beranotasi manual: FinanceBench (150 pertanyaan open-source tentang perusahaan publik) dan Company dataset. Dokumen sumbernya adalah SEC filings.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Menggunakan retriever teksual (Jina-ColBERT-V2, Multilingual-E5-large) dan multimodal (ColQwen2, GME-Qwen2-VL-2B, DSE-QWen2-2b-MRL-V1); chunking pada level halaman; generator memakai MLLM seperti GPT-4o, GPT-4V, Gemini-2.0-Flash, Qwen2.5-VL-72B-Instruct; visual citation diintegrasikan pada tahap generasi.</t>
+          <t>FinSage menggunakan pipeline Multi-path Retrieval dengan BM25 sparse retriever, BGE-M3 dense retriever, metadata retriever, dan HyDE retriever, serta modul chunk bundling.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Evaluasi mencakup retrieval (nDCG@k, Recall@k, MRR@k), akurasi jawaban (ROUGE, ACC), serta kualitas visual citation (precision, recall pada level halaman dan blok, IoU, dan penilaian manusia 0-5).</t>
+          <t>Evaluasi mencakup recall, precision, F1, serta metrik Normalized Recall dan penilaian faktual menggunakan GPT-4o serta evaluasi manual.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Multimodal retriever mencapai recall@10 hingga 90.13 % (Chinese) dan 85.86 % (English), jauh di atas retriever teksual (42.71 %/36.36 %). Visual citation dengan image-cropping memperoleh korelasi Pearson 65.06 dengan IoU dan 68.01 dengan penilaian manusia.</t>
+          <t>FinSage mencapai akurasi LLM 49.66% pada FinanceBench, meningkatkan recall sekitar 15% dan precision dari 5.6% menjadi 18.5% dibanding re-ranker umum.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Penulis menyatakan keterbatasan utama bahwa mereka tidak melatih model khusus untuk RAG multimodal di domain keuangan, dan pekerjaan lanjutan perlu mengembangkan model yang disesuaikan dengan tantangan RAG multimodal keuangan.</t>
+          <t>Chunk tidak memuat keterbatasan eksplisit dari penulis. Dari hasil, waktu respons FinSage paling lambat (rata-rata 19,34 detik) dibanding GraphRAG (16,90 detik) dan LightRAG (12,16 detik).</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Penulis menyatakan belum melatih model khusus RAG multimodal keuangan; benchmark hanya mencakup data berbahasa Mandarin dan Inggris. Inferensi: paper sudah mengevaluasi grounding melalui precision/recall visual citation, tetapi tidak membahas abstention dan tidak mencakup dokumen perbankan berbahasa Indonesia.</t>
+          <t>Inferensi: FinSage sudah dievaluasi untuk akurasi, recall, dan skor faithfulness (rata-rata 4,31; pass 82,67%) pada SEC filings, tetapi tidak membahas abstention dan tidak mencakup dokumen produk perbankan berbahasa Indonesia.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ngartera, L., Nadarajah, S., &amp; Koina, R. (2026). Bayesian RAG: Uncertainty-Aware Retrieval for Reliable Financial Question Answering. Frontiers in Artificial Intelligence 8, 1668172. https://doi.org/10.3389/frai.2025.1668172</t>
+          <t>Katerenchuk, D., Duboue, P., Evanini, K., et al. (2026). FinRAG-12B: A Production-Validated Recipe for Grounded Question Answering in Banking. arXiv:2605.05482. https://doi.org/10.48550/arXiv.2605.05482</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Paper ini mengusulkan kerangka Bayesian RAG untuk mengukur ketidakpastian pada proses retrieval demi menjamin jawaban keuangan yang dapat diandalkan.</t>
+          <t>Paper mengatasi kebutuhan sistem RAG yang dapat memberikan jawaban yang akurat dan menolak menjawab bila konteks tidak cukup, untuk mengurangi risiko regulasi di perbankan.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Eksperimen dilakukan secara eksklusif pada laporan keuangan terstruktur berbahasa Inggris, dengan dataset AAPL 10-K, MSFT 10-K, dan FinSage. Ground truth disusun oleh dua pakar keuangan (Cohen's kappa = 0,87).</t>
+          <t>Domain perbankan. Korpus pelatihan berisi 98.648 sampel (143M token) dari data open-source dan proprietary; evaluasi memakai data QA perbankan dengan lima passage per contoh dan label answerability, FinanceBench (150 pertanyaan atas SEC filings), serta 3.297 kueri pengguna dari sebuah credit union besar di AS.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Menggunakan pipeline lima tahap dengan embedding dense, retrieval semantik via FAISS, dan Monte Carlo dropout (n=10) untuk mengkuantifikasi ketidakpastian pada tahap retrieval.</t>
+          <t>Menggunakan model dasar Gemma 3 12B-IT dengan jendela konteks 128K, pipeline kurasi data multi-tahap, dan strategi pelatihan dua-tahap termasuk contoh tidak dapat dijawab untuk kalibrasi abstensi.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dievaluasi dengan metrik faithfulness, hallucination rate, akurasi, AUC, ECE, serta Precision@3, Recall@5, dan MRR; dibandingkan dengan baseline BM25, DPR, dan ColBERT.</t>
+          <t>Dievaluasi dengan tiga dimensi: kualitas jawaban (QA F1), kalibrasi penolakan (refusal rate), dan latency, serta metrik kualitas kutipan (Citation Quality).</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bayesian RAG (lambda=0,3) menaikkan faithfulness dari 0,82 menjadi 0,87 dan menurunkan hallucination dari 0,18 menjadi 0,13 dibanding ColBERT. Bayesian RAG + GPT mencapai akurasi 93,1% dengan AUC 0,961 dan ECE 0,034, dan pada zona balanced memberi peningkatan kinerja 25% dengan overhead latency 33 ms.</t>
+          <t>FinRAG-12B menaikkan resolution rate produksi sebesar 7,1 poin persentase dan mencapai F1 tertinggi di FinanceBench (0,284; citation rate 97,3%) di atas base model (0,249) dan GPT-4.1 (0,238). Rate 'I don't know' 12% lebih aman daripada base model (4,3%) dan menghindari over-refusal GPT-4.1 (20,2%).</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Kerangka hanya diuji pada dokumen berbahasa Inggris, tidak memodelkan ketidakpastian aleatorik, dan hasilnya terbatas pada konteks regulasi keuangan.</t>
+          <t>Rasio contoh negatif yang tidak optimal dapat menyebabkan respons tidak berdasar atau over-refusal; evaluasi penolakan tidak sepenuhnya menangkap ungkapan penolakan yang bersifat hedged atau parsial.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Inferensi: Meskipun paper menilai faithfulness, tidak ada evaluasi abstention atau analisis pada dokumen perbankan berbahasa Indonesia, sehingga belum menjawab fokus penelitian yang menuntut pengukuran abstention pada produk perbankan Indonesia.</t>
+          <t>Inferensi: Meskipun paper menilai faithfulness melalui citation quality dan abstention pada data bahasa Inggris, tidak ada evaluasi pada dokumen produk perbankan berbahasa Indonesia, sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada konteks bahasa Indonesia.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sarmah, B., Mehta, D. B., Hall, B., et al. (2024). HybridRAG: Integrating Knowledge Graphs and Vector Retrieval Augmented Generation for Efficient Information Extraction. ACM ICAIF '24. https://doi.org/10.1145/3677052.3698671</t>
+          <t>Gondhalekar, C., Patel, U., &amp; Yeh, F.-C. (2025). MultiFinRAG: An Optimized Multimodal Retrieval-Augmented Generation Framework for Financial Question Answering. IEEE International Conference on Big Data (BigData) 2025. https://doi.org/10.1109/bigdata66926.2025.11401444</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Paper memperkenalkan HybridRAG, pendekatan gabungan VectorRAG dan GraphRAG untuk meningkatkan analisis dokumen keuangan.</t>
+          <t>Dokumen keuangan seperti 10-K dan 10-Q panjangnya ratusan halaman dan memadukan teks, tabel, serta gambar, sehingga menjawab pertanyaan butuh penalaran lintas modalitas. Hal ini menyulitkan LLM dan pipeline RAG konvensional karena batas token, hilangnya layout, dan konteks lintas modal yang terfragmentasi; paper mengusulkan MultiFinRAG untuk masalah ini.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Menggunakan dokumen keuangan perusahaan, khususnya transkrip earnings call, dengan entitas seperti metrik keuangan, eksekutif, dan peristiwa korporasi.</t>
+          <t>Dataset terdiri dari 300 pertanyaan QA yang disusun manual dari dokumen SEC (Form 10-K, 10-Q, 8-K dengan EX-99.1, dan DEF 14A) yang diunduh dari EDGAR. Pertanyaan dibagi menjadi empat tipe: berbasis teks, gambar, tabel, dan gabungan teks dengan gambar/tabel.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>HybridRAG memakai model embedding text-embedding-ada-002, chunk size 1024, Pinecone vector DB, serta integrasi GraphRAG untuk pencarian semantik dan pemrosesan KG.</t>
+          <t>MultiFinRAG mengelompokkan gambar tabel dan figur ke batch untuk diproses LLM multimodal open-source terkuantisasi yang menghasilkan JSON terstruktur dan ringkasan teks. Hasilnya bersama teks naratif di-embed dan diindeks (FAISS IVF/PQ) dengan threshold kesamaan sadar-modalitas, lalu strategi tiered fallback naik dari konteks teks ke teks+tabel+gambar bila perlu.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dievaluasi dengan metrik faithfulness, answer relevancy, dan context relevance untuk menilai kualitas jawaban dan relevansi konteks.</t>
+          <t>Evaluasi dilakukan secara manual karena ukuran dataset, mengukur akurasi akhir QA tanpa metrik presisi-recall terperinci.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>HybridRAG mencapai skor faithfulness 0.96, answer relevancy 0.96, dan context recall 1.0, menunjukkan kinerja seimbang dibandingkan VectorRAG dan GraphRAG.</t>
+          <t>MultiFinRAG mencapai akurasi 90.4% pada pertanyaan berbasis teks, meningkat 15.1 poin persentase dibanding baseline.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Chunk tidak memuat bagian keterbatasan eksplisit. Hasil menunjukkan trade-off: context precision HybridRAG (0,79) lebih rendah dari VectorRAG (0,84) dan GraphRAG (0,96). Penulis juga mencatat bahwa komponen GraphRAG lemah pada Q&amp;A abstraktif atau saat pertanyaan tidak menyebut entitas secara eksplisit.</t>
+          <t>Penulis menyatakan bahwa metrik retrieval detail tidak dilaporkan dan evaluasi modul masih terbuka untuk studi lanjutan.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Penelitian ini tidak mengevaluasi abstention (menolak menjawab bila konteks tidak memadai) dan tidak menggunakan dokumen berbahasa Indonesia; Inferensi: sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada dokumen perbankan Indonesia.</t>
+          <t>Tidak disebutkan evaluasi faithfulness atau abstention pada dokumen perbankan berbahasa Indonesia. Inferensi: Karena studi hanya menggunakan dokumen SEC berbahasa Inggris dan tidak menguji kemampuan menolak pertanyaan ketika konteks tidak ada, terdapat gap dalam evaluasi faithfulness dan abstention untuk dokumen perbankan Indonesia.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Wang, X., Chi, J., Tai, Z., et al. (2025). FinSage: A Multi-aspect RAG System for Financial Filings Question Answering. CIKM '25, 6144-6152. https://doi.org/10.1145/3746252.3761587</t>
+          <t>Cheng, Z., Lai, L., &amp; Liu, Y. (2026). Sustainable Hybrid Document-Routed Retrieval for Financial RAG: Resolving the Robustness-Precision Trade-off. Intelligent Systems with Applications 32, 200720. https://doi.org/10.1016/j.iswa.2026.200720</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Paper ini mengidentifikasi kebutuhan akan sistem QA yang dapat secara efisien mengambil dan menganalisis informasi kepatuhan dari dokumen keuangan.</t>
+          <t>Masalah yang diidentifikasi adalah trade-off antara robustness dan precision pada sistem RAG untuk pertanyaan dokumen keuangan.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Evaluasi memakai dua dataset beranotasi manual: FinanceBench (150 pertanyaan open-source tentang perusahaan publik) dan Company dataset. Dokumen sumbernya adalah SEC filings.</t>
+          <t>Domain keuangan dengan benchmark FinDER sebanyak 1.500 kueri dalam lima grup; jenis dokumen, ukuran korpus, dan bahasa tidak disebut.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FinSage menggunakan pipeline Multi-path Retrieval dengan BM25 sparse retriever, BGE-M3 dense retriever, metadata retriever, dan HyDE retriever, serta modul chunk bundling.</t>
+          <t>Metode menggabungkan Semantic File Routing sebagai filter dokumen dengan retrieval berbasis chunk pada dokumen terfilter melalui arsitektur dua tahap Hybrid Document-Routed Retrieval (HDRR).</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Evaluasi mencakup recall, precision, F1, serta metrik Normalized Recall dan penilaian faktual menggunakan GPT-4o serta evaluasi manual.</t>
+          <t>Evaluasi menggunakan skor rata-rata, tingkat kegagalan, persentase jawaban benar, dan persentase jawaban sempurna, dibandingkan dengan CBR dan SFR sebagai baseline.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>FinSage mencapai akurasi LLM 49.66% pada FinanceBench, meningkatkan recall sekitar 15% dan precision dari 5.6% menjadi 18.5% dibanding re-ranker umum.</t>
+          <t>HDRR mencapai skor rata-rata 7.54, tingkat kegagalan 6.4%, correctness 67.7% (+18.7 pp), dan perfect-answer rate 20.1% (+6.3 pp).</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Chunk tidak memuat keterbatasan eksplisit dari penulis. Dari hasil, waktu respons FinSage paling lambat (rata-rata 19,34 detik) dibanding GraphRAG (16,90 detik) dan LightRAG (12,16 detik).</t>
+          <t>tidak disebut</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Inferensi: FinSage sudah dievaluasi untuk akurasi, recall, dan skor faithfulness (rata-rata 4,31; pass 82,67%) pada SEC filings, tetapi tidak membahas abstention dan tidak mencakup dokumen produk perbankan berbahasa Indonesia.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>P14</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Cho, E., Lee, Y., Kim, M., et al. (2026). K-FinHallu: A Hallucination Detection Benchmark for Multi-Turn RAG in Korean Finance. arXiv:2605.29523. https://doi.org/10.48550/arXiv.2605.29523</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Paper ini mengatasi masalah mendeteksi hallucination intrinsik pada sistem RAG multi-turn di domain keuangan Korea dengan fokus pada kesetiaan sumber.</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Benchmark K-FinHallu dibangun dari dataset publik AI-Hub 'Korean Financial and Legal Document Machine Reading Comprehension' yang difilter ke kategori keuangan. Domainnya antara lain Financial Economics (35,2%), Financial Institution Management (24,1%), dan Consumer Economics (21,4%).</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Pipeline konstruksi otomatis menghasilkan training split, dan model 8B di-fine-tune dengan rationale supervision sebagai detektor hallucination. Passage disegmentasi hingga maksimum 1.000 token dengan model embedding KURE. Alih-alih retriever, model diberi set dokumen terkontrol yang dapat dimanipulasi (mis. passage relevan diganti hard negative).</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Evaluasi menggunakan klasifikasi biner (akurasi, presisi, recall, F1) serta klasifikasi empat kelas yang mencakup kemampuan menolak (refusal) dalam dialog multi-turn.</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Model tertutup Gemini-2.5-Flash mencapai F1 tertinggi 0.860; abstention tetap menjadi aspek terlemah pada semua model yang diuji.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Abstention yang tepat masih paling lemah; temuan terbatas pada bahasa Korea sehingga transferabilitas ke bahasa atau yurisdiksi lain terbatas.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Inferensi: Meskipun menyediakan benchmark RAG multi-turn untuk bahasa Korea, penelitian ini tidak mencakup bahasa Indonesia atau dokumen produk perbankan, sehingga belum mengevaluasi faithfulness dan abstention pada konteks Indonesia. Penulis juga mencatat bahwa temuan mereka terbatas pada bahasa Korea, sehingga transferabilitas ke bahasa lain tidak dijamin.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>P15</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Katerenchuk, D., Duboue, P., Evanini, K., et al. (2026). FinRAG-12B: A Production-Validated Recipe for Grounded Question Answering in Banking. arXiv:2605.05482. https://doi.org/10.48550/arXiv.2605.05482</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Paper mengatasi kebutuhan sistem RAG yang dapat memberikan jawaban yang akurat dan menolak menjawab bila konteks tidak cukup, untuk mengurangi risiko regulasi di perbankan.</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Domain perbankan. Korpus pelatihan berisi 98.648 sampel (143M token) dari data open-source dan proprietary; evaluasi memakai data QA perbankan dengan lima passage per contoh dan label answerability, FinanceBench (150 pertanyaan atas SEC filings), serta 3.297 kueri pengguna dari sebuah credit union besar di AS.</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Menggunakan model dasar Gemma 3 12B-IT dengan jendela konteks 128K, pipeline kurasi data multi-tahap, dan strategi pelatihan dua-tahap termasuk contoh tidak dapat dijawab untuk kalibrasi abstensi.</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Dievaluasi dengan tiga dimensi: kualitas jawaban (QA F1), kalibrasi penolakan (refusal rate), dan latency, serta metrik kualitas kutipan (Citation Quality).</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>FinRAG-12B menaikkan resolution rate produksi sebesar 7,1 poin persentase dan mencapai F1 tertinggi di FinanceBench (0,284; citation rate 97,3%) di atas base model (0,249) dan GPT-4.1 (0,238). Rate 'I don't know' 12% lebih aman daripada base model (4,3%) dan menghindari over-refusal GPT-4.1 (20,2%).</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Rasio contoh negatif yang tidak optimal dapat menyebabkan respons tidak berdasar atau over-refusal; evaluasi penolakan tidak sepenuhnya menangkap ungkapan penolakan yang bersifat hedged atau parsial.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Inferensi: Meskipun paper menilai faithfulness melalui citation quality dan abstention pada data bahasa Inggris, tidak ada evaluasi pada dokumen produk perbankan berbahasa Indonesia, sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada konteks bahasa Indonesia.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>P16</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Gondhalekar, C., Patel, U., &amp; Yeh, F.-C. (2025). MultiFinRAG: An Optimized Multimodal Retrieval-Augmented Generation Framework for Financial Question Answering. IEEE International Conference on Big Data (BigData) 2025. https://doi.org/10.1109/bigdata66926.2025.11401444</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Dokumen keuangan seperti 10-K dan 10-Q panjangnya ratusan halaman dan memadukan teks, tabel, serta gambar, sehingga menjawab pertanyaan butuh penalaran lintas modalitas. Hal ini menyulitkan LLM dan pipeline RAG konvensional karena batas token, hilangnya layout, dan konteks lintas modal yang terfragmentasi; paper mengusulkan MultiFinRAG untuk masalah ini.</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Dataset terdiri dari 300 pertanyaan QA yang disusun manual dari dokumen SEC (Form 10-K, 10-Q, 8-K dengan EX-99.1, dan DEF 14A) yang diunduh dari EDGAR. Pertanyaan dibagi menjadi empat tipe: berbasis teks, gambar, tabel, dan gabungan teks dengan gambar/tabel.</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>MultiFinRAG mengelompokkan gambar tabel dan figur ke batch untuk diproses LLM multimodal open-source terkuantisasi yang menghasilkan JSON terstruktur dan ringkasan teks. Hasilnya bersama teks naratif di-embed dan diindeks (FAISS IVF/PQ) dengan threshold kesamaan sadar-modalitas, lalu strategi tiered fallback naik dari konteks teks ke teks+tabel+gambar bila perlu.</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Evaluasi dilakukan secara manual karena ukuran dataset, mengukur akurasi akhir QA tanpa metrik presisi-recall terperinci.</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>MultiFinRAG mencapai akurasi 90.4% pada pertanyaan berbasis teks, meningkat 15.1 poin persentase dibanding baseline.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Penulis menyatakan bahwa metrik retrieval detail tidak dilaporkan dan evaluasi modul masih terbuka untuk studi lanjutan.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Tidak disebutkan evaluasi faithfulness atau abstention pada dokumen perbankan berbahasa Indonesia. Inferensi: Karena studi hanya menggunakan dokumen SEC berbahasa Inggris dan tidak menguji kemampuan menolak pertanyaan ketika konteks tidak ada, terdapat gap dalam evaluasi faithfulness dan abstention untuk dokumen perbankan Indonesia.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>P17</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Cheng, Z., Lai, L., &amp; Liu, Y. (2026). Sustainable Hybrid Document-Routed Retrieval for Financial RAG: Resolving the Robustness-Precision Trade-off. Intelligent Systems with Applications 32, 200720. https://doi.org/10.1016/j.iswa.2026.200720</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Masalah yang diidentifikasi adalah trade-off antara robustness dan precision pada sistem RAG untuk pertanyaan dokumen keuangan.</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Domain keuangan dengan benchmark FinDER sebanyak 1.500 kueri dalam lima grup; jenis dokumen, ukuran korpus, dan bahasa tidak disebut.</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Metode menggabungkan Semantic File Routing sebagai filter dokumen dengan retrieval berbasis chunk pada dokumen terfilter melalui arsitektur dua tahap Hybrid Document-Routed Retrieval (HDRR).</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Evaluasi menggunakan skor rata-rata, tingkat kegagalan, persentase jawaban benar, dan persentase jawaban sempurna, dibandingkan dengan CBR dan SFR sebagai baseline.</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>HDRR mencapai skor rata-rata 7.54, tingkat kegagalan 6.4%, correctness 67.7% (+18.7 pp), dan perfect-answer rate 20.1% (+6.3 pp).</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>tidak disebut</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
           <t>Inferensi: Meskipun HDRR meningkatkan akurasi, studi tidak mengevaluasi faithfulness atau kemampuan abstain pada dokumen perbankan berbahasa Indonesia.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>P18</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Liu, Y., Shangguan, J., Wang, Q., &amp; Xu, S. (2026). MacroRisk-agent: A Retrieval-Augmented Multi-Agent Framework with Deterministic Validation Gates for Auditable Stress Testing. Scientific Reports. https://doi.org/10.1038/s41598-026-73453-3</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Makalah mengidentifikasi tiga tantangan utama LLM multi-agent dalam keputusan berisiko tinggi: kontrol halusinasi, penggabungan penalaran semantik dengan simulasi numerik deterministik, serta auditabilitas end-to-end.</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Kerangka diuji pada domain stress testing keuangan menggunakan dataset publik (FRED, Yahoo Finance), perpustakaan 150 peristiwa krisis, dan 10 portofolio institusional sintetis.</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>MacroRisk-Agent memperkenalkan pipeline retrieval-augmented generation dengan deterministic validation gates yang mengubah intent stres bahasa alami menjadi objek parameter ber-skema.</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Evaluasi mencakup tingkat validitas 92.6% vs 78.4% (p&lt;0.001), peningkatan estimasi kerugian sistemik 52%, dan tingkat keberhasilan keputusan top-1 sebesar 68.6%.</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>MacroRisk-Agent mencapai validitas 92.6% (lebih tinggi 14.2 poin persentase), menghasilkan estimasi kerugian sistemik 52% lebih tinggi, dan sukses keputusan top-1 sebesar 68.6%.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Validasi pada data institusional nyata belum dilakukan; penelitian masih bersifat proof-of-concept pada data sintetis dan publik.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Studi hanya dievaluasi sebagai proof-of-concept pada dataset keuangan publik (FRED, Yahoo Finance), 150 peristiwa krisis kurasi, dan 10 portofolio institusional sintetis; validasi pada data institusional nyata belum dilakukan. Inferensi: faithfulness dan kemampuan abstention pada dokumen perbankan berbahasa Indonesia belum dikaji.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>P19</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Beauchemin, D., &amp; Khoury, R. (2026). A Human-Centric Evaluation of a Retrieval-Augmented Generation System for Explaining Quebec Insurance Contracts. HCI International 2026 Posters (CCIS), 151-168. https://doi.org/10.1007/978-3-032-30826-9_15</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Penelitian ini mengevaluasi sistem RAG yang menjelaskan kontrak asuransi Quebec dengan fokus pada pengalaman pengguna secara manusiawi.</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Domain asuransi kendaraan bermotor di Quebec (konteks francophone). Data berupa 3.759 pasangan pesan-jawaban dari 154 peserta (mahasiswa dan karyawan Universitas Laval) selama 30 hari, ditambah survei pasca-penggunaan 21 pertanyaan.</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Sistem memakai LLM OpenAI o3-2025-04-16 dengan arsitektur RAG yang sama seperti yang dijelaskan pada referensi [5] makalah tersebut; detail retriever dan strategi chunking tidak dijelaskan dalam teks yang tersedia.</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Evaluasi mencakup survei Likert 7-point, analisis statistik t-test, Kruskal-Wallis, dan korelasi Pearson untuk mengukur kepuasan, usaha kognitif, dan kepercayaan.</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Pengguna dengan literasi rendah melaporkan kepuasan secara signifikan lebih tinggi, sementara manfaat inti sistem diakui secara universal oleh semua kelompok.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Penulis mencatat adanya kesalahan faktual, preferensi pengguna terhadap agen manusia, serta keterbatasan generalisasi karena sampel berpendidikan tinggi dan setting eksperimental.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Studi berfokus pada evaluasi human-centric (UX) RAG di konteks asuransi kendaraan Quebec yang francophone; kesalahan faktual hanya dilaporkan dari temuan pengguna, bukan diukur dengan metrik faithfulness. Inferensi: faithfulness terukur dan kemampuan abstention pada dokumen perbankan berbahasa Indonesia belum dikaji.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>P20</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Luketina, M., Benkel, A., &amp; Schuetz, C. G. (2026). Using Large Language Models for Legal Decision-Making in Austrian Value-Added Tax Law: A Comparative Study. Journal of Business Analytics, 1-25. https://doi.org/10.1080/2573234x.2026.2720626</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Penelitian ini mengevaluasi dua pendekatan peningkatan performa LLM, yaitu fine-tuning dan retrieval-augmented generation (RAG), untuk mendukung pengambilan keputusan hukum dalam konteks pajak pertambahan nilai (VAT).</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Domainnya adalah pajak nilai tambah (VAT) di Austria/EU, menggunakan kasus VAT dari buku teks serta kasus nyata dari firma konsultan pajak; bahasa tidak disebut.</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Studi menerapkan RAG dan membandingkannya dengan fine-tuning untuk mengidentifikasi konfigurasi sistem berbasis LLM yang optimal; detail retriever, chunking, dan model tidak disebut.</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>tidak disebut</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>LLM yang dikonfigurasi dengan tepat dapat mendukung profesional pajak dalam tugas VAT: mengotomatisasi pekerjaan rutin, memberikan analisis awal, dan menghasilkan justifikasi keputusan yang berlandaskan hukum (legally grounded).</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Prototipe belum siap untuk otomatisasi penuh karena sensitivitas domain hukum, serta masih terdapat keterbatasan dalam menangani pengetahuan implisit klien dan dokumentasi kontekstual.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Inferensi: Makalah ini tidak membahas faithfulness atau abstention pada sistem RAG, tidak menggunakan dokumen perbankan berbahasa Indonesia, sehingga tidak menjawab fokus penelitian yang menilai kemampuan RAG dalam konteks tersebut.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>P21</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Schmitt, K., Vial, G., &amp; Blohm, I. (2026). Alpes Bank's Journey to Creating Value at Scale with Generative AI. Journal of Information Technology Teaching Cases, 20438869261460075. https://doi.org/10.1177/20438869261460075</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Teaching case ini menggambarkan Alpes Bank, yang model layanan premium berbasis cabangnya ditantang oleh GenAI, dan mandat dewan untuk menghadirkan pilot GenAI 'no-regret' dalam satu kuartal; Part B membahas fondasi organisasi dan tata kelola untuk penskalaan GenAI.</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Studi kasus (teaching case) pada Alpes Bank, bank universal Swiss; use case berupa email assistant untuk inquiry rutin. Dataset dan bahasa tidak disebut.</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Tim membangun email assistant berbasis retrieval-augmented generation (RAG) bekerja sama dengan AILabs; detail teknis tidak disebut.</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Evaluasi dilakukan dengan mengukur pengurangan waktu penanganan inquiry rutin, tercatat penurunan 21%.</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Email assistant berbasis GenAI mengurangi waktu penanganan inquiry rutin sebesar 21%.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Pilot GenAI memunculkan sejumlah ketegangan (tensions) yang tidak terduga, dan hasil 21% hanya diperoleh dari rollout terbatas; rincian ketegangan tersebut tidak disebut.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Inferensi: Penelitian ini tidak mengevaluasi faithfulness atau abstention pada dokumen produk perbankan berbahasa Indonesia, sehingga tidak menjawab fokus riset yang diusulkan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>P22</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Opin, S. A. I., Thakur, R. A., Raiyan, A. K., et al. (2025). NextRAG: A Bilingual Retrieval-Augmented Generation Framework for Financial Question-Answering. 28th International Conference on Computer and Information Technology (ICCIT 2025), 3604-3609. IEEE. https://doi.org/10.1109/iccit68739.2025.11491522</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Penelitian ini memperkenalkan NextRAG, kerangka Retrieval-Augmented Generation bilingual untuk meningkatkan penelusuran pengetahuan keuangan dan menjawab pertanyaan.</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Fokus pada dokumen keuangan multibahasa dari institusi dan regulator di Bangladesh, serta dataset Q&amp;A keuangan bilingual yang beragam.</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Menggunakan retrieval sparse BM25 dengan smoothing Dirichlet, fusi Reciprocal Rank Fusion, re-ranking cross-encoder, serta prompting yang sadar bahasa untuk Bangla dan Inggris.</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Dievaluasi pada dataset Q&amp;A bilingual dengan metrik mean cosine similarity dan F1 score, membandingkan dengan RAG konvensional.</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>NextRAG secara konsisten mengungguli RAG konvensional, memperoleh mean cosine similarity 0.77 dan F1 68.3%.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>tidak disebut</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Inferensi: Meskipun NextRAG menangani dokumen bilingual, penelitian ini tidak mengevaluasi faithfulness atau kemampuan abstention pada dokumen perbankan berbahasa Indonesia, sehingga belum menjawab fokus riset yang diinginkan.</t>
         </is>
       </c>
     </row>
@@ -1509,7 +1086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K155"/>
+  <dimension ref="A1:K92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2282,7 +1859,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2297,17 +1874,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Penelitian ini mengatasi masalah halusinasi pada sistem Retrieval-Augmented Generation (RAG) bahasa Arab untuk analisis dokumen keuangan.</t>
+          <t>Penulis menilai faktor-faktor yang memengaruhi kualitas jawaban dalam sistem RAG LLM pada domain keuangan, termasuk sensitivitas terhadap kualitas retrieval dan dampak prompt.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>This research introduces a customized attention visualization framework for mitigating hallucinations in Arabic Retrieval-Augmented Generation (RAG) systems tailored for financial document analysis.</t>
+          <t>We comprehensively assess various factors that contribute to the answer generation quality in LLM RAG systems, ranging from sensitivity to retrieval quality to the impact of different prompts</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>P03:abstract:0</t>
+          <t>P04:pdf:9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2317,21 +1894,21 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sesuai abstract:0.</t>
+          <t>Sesuai pdf:9.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Penelitian ini mengatasi masalah halusinasi pada sistem Retrieval-Augmented Generation (RAG) bahasa Arab untuk analisis dokumen keuangan.</t>
+          <t>Penulis menilai faktor-faktor yang memengaruhi kualitas jawaban dalam sistem RAG LLM pada domain keuangan, termasuk sensitivitas terhadap kualitas retrieval dan dampak prompt.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2341,46 +1918,54 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>quote_verified</t>
+          <t>quote_not_found</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Domain keuangan, dokumen finansial berbahasa Arab, dengan dataset baru berisi 7.000 pasangan query-konteks beranotasi.</t>
+          <t>Studi menggunakan dua dataset RAG dari sektor perbankan: halaman web publik tentang produk perbankan dan panduan kebijakan internal, keduanya berbahasa Inggris.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>trained on a newly constructed dataset of 7,000 annotated Arabic financial query-context pairs</t>
+          <t>Banking webpages: Public webpages with general information on banking products, and Banking policy guides: internal guides for customer service executives</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>P03:abstract:0</t>
+          <t>P04:pdf:0; P04:pdf:1; P04:pdf:4</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7.000 pasangan query-konteks Arab beranotasi, abstract:0.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>Dua korpus (banking webpages dan banking policy guides) didukung pdf:10; klaim 'keduanya berbahasa Inggris' tidak disebut di chunk.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Studi memakai dua dataset RAG di sektor perbankan: halaman web publik berisi informasi umum produk perbankan dan panduan kebijakan internal untuk customer service executive. Pertanyaan berasal dari pengguna nyata (log sistem produksi), dan 800 query di-sampling per dataset.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>P04:pdf:10; P04:pdf:12; P04:pdf:9</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Domain keuangan, dokumen finansial berbahasa Arab, dengan dataset baru berisi 7.000 pasangan query-konteks beranotasi.</t>
+          <t>Studi memakai dua dataset RAG di sektor perbankan: halaman web publik berisi informasi umum produk perbankan dan panduan kebijakan internal untuk customer service executive. Pertanyaan berasal dari pengguna nyata (log sistem produksi), dan 800 query di-sampling per dataset.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2395,17 +1980,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Metode memperluas MarBERT dengan mekanisme supervisi perhatian dua tahap dan loss yang sadar halusinasi, serta ambang presisi dinamis untuk penolakan output.</t>
+          <t>Retriever menggunakan OpenAI Embeddings, dokumen dipotong menjadi chunk, dan generator berupa model LLM seperti GPT-4 dan Llama-2; variasi kualitas retrieval diuji dengan manipulasi list hasil retrieval.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>The proposed architecture extends MarBERT with a dual-stage attention supervision mechanism and a hallucination-aware loss formulation</t>
+          <t>We sampled 800 user queries for each dataset and obtained retrieved document chunks using a retriever(OpenAI Embeddings2)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>P03:abstract:0</t>
+          <t>P04:pdf:12; P04:pdf:29</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2415,21 +2000,21 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>MarBERT, dual-stage attention supervision, hallucination-aware loss, ambang dinamis untuk penolakan respons, abstract:0.</t>
+          <t>OpenAI Embeddings, chunk, manipulasi daftar retrieval (pdf:12); GPT-4 dan Llama-2 di antara 6 LLM (pdf:7, pdf:9).</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Metode memperluas MarBERT dengan mekanisme supervisi perhatian dua tahap dan loss yang sadar halusinasi, serta ambang presisi dinamis untuk penolakan output.</t>
+          <t>Retriever menggunakan OpenAI Embeddings, dokumen dipotong menjadi chunk, dan generator berupa model LLM seperti GPT-4 dan Llama-2; variasi kualitas retrieval diuji dengan manipulasi list hasil retrieval.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2444,17 +2029,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Dievaluasi dengan akurasi klasifikasi 95.04%, presisi 95.84%, recall 94.12%, F1 94.97%, serta deteksi halusinasi 87.63% dengan false alarm 8.91% dan latensi 3.2 token.</t>
+          <t>Evaluasi mencakup kemampuan LLM mengikuti instruksi, kualitas jawaban, serta metrik ekstraktivitas, dengan perbandingan antar model seperti GPT-4, GPT-3.5-Turbo, dan Llama-2.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>classification accuracy, 95.84% precision, 94.12% recall, and an F1 score of 94.97%... detection rate with only 8.91% false alarms and a detection latency of 3.2 tokens</t>
+          <t>Our findings reveal that generative LLMs outperform baseline models in answer quality, even on metrics emphasizing extractiveness</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>P03:abstract:1; P03:abstract:0</t>
+          <t>P04:pdf:7; P04:pdf:29</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2464,21 +2049,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Semua angka cocok dengan abstract:0-1.</t>
+          <t>Instruction following, kualitas jawaban, metrik ekstraktivitas, perbandingan GPT-4/GPT-3.5-Turbo/Llama-2, pdf:7.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Dievaluasi dengan akurasi klasifikasi 95.04%, presisi 95.84%, recall 94.12%, F1 94.97%, serta deteksi halusinasi 87.63% dengan false alarm 8.91% dan latensi 3.2 token.</t>
+          <t>Evaluasi mencakup kemampuan LLM mengikuti instruksi, kualitas jawaban, serta metrik ekstraktivitas, dengan perbandingan antar model seperti GPT-4, GPT-3.5-Turbo, dan Llama-2.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2493,17 +2078,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Model mencapai akurasi 95.04% dan F1 94.97%, mengungguli baseline AraELECTRA dan mBERT-RAG, serta mendeteksi halusinasi dengan tingkat 87.63% dan kegagalan hanya 8.91%.</t>
+          <t>Optimasi retrieval terbukti penting; peningkatan recall dan precision meningkatkan kualitas jawaban, sementara LLM cenderung memberikan jawaban meski dokumen relevan tidak ada, terutama pada model kecil.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>outperforming AraELECTRA and mBERT-RAG baselines... reaches an 87.63% detection rate with only 8.91% false alarms</t>
+          <t>We recommend prioritizing retrieval recall, while tuning retrieval systems, as LLMs exhibit pseudo-helpfulness when relevant gold document(s) are not retrieved</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>P03:abstract:1; P03:abstract:0</t>
+          <t>P04:pdf:30; P04:pdf:29; P04:pdf:22</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2513,29 +2098,29 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8,91% adalah tingkat false alarm, bukan 'kegagalan'; terjemahan mengubah makna.</t>
+          <t>'Terutama pada model kecil' tidak didukung untuk pseudo-helpfulness; chunk mengaitkan model kecil (Llama-2) dengan kegagalan mengikuti instruksi panjang, bukan pseudo-helpfulness.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Model mencapai akurasi klasifikasi 95,04% dan F1 94,97%, mengungguli baseline AraELECTRA dan mBERT-RAG. Untuk deteksi halusinasi, detection rate mencapai 87,63% dengan false alarm hanya 8,91% dan latensi deteksi 3,2 token.</t>
+          <t>Optimasi retrieval penting meskipun memakai GPT-4: recall retrieval perlu diprioritaskan karena LLM menunjukkan pseudo-helpfulness ketika dokumen gold tidak ter-retrieve, dan peningkatan precision diperkirakan memperbaiki performa. Model sensitif terhadap distractor; selisih besar terlihat antara LLM vendor (OpenAI) dan model open-source kecil, dan Llama-2 kecil sering gagal mengikuti instruksi panjang.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>P03:abstract:0; P03:abstract:1</t>
+          <t>P04:pdf:7; P04:pdf:29; P04:pdf:30; P04:pdf:22</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Model mencapai akurasi klasifikasi 95,04% dan F1 94,97%, mengungguli baseline AraELECTRA dan mBERT-RAG. Untuk deteksi halusinasi, detection rate mencapai 87,63% dengan false alarm hanya 8,91% dan latensi deteksi 3,2 token.</t>
+          <t>Optimasi retrieval penting meskipun memakai GPT-4: recall retrieval perlu diprioritaskan karena LLM menunjukkan pseudo-helpfulness ketika dokumen gold tidak ter-retrieve, dan peningkatan precision diperkirakan memperbaiki performa. Model sensitif terhadap distractor; selisih besar terlihat antara LLM vendor (OpenAI) dan model open-source kecil, dan Llama-2 kecil sering gagal mengikuti instruksi panjang.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2545,27 +2130,39 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>not_stated</t>
+          <t>quote_fuzzy</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>Penulis mengakui kurangnya investigasi sistematis pada tiap komponen RAG dan bahwa studi terbatas pada data internal serta bahasa Inggris, sehingga generalisasi masih terbatas.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>there is a lack of systematic investigations of the impact of each component (retriever, prompts, models) on answer generation quality</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>P04:pdf:2; P04:pdf:9; P04:pdf:4</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>UNSUPPORTED</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>'Kurangnya investigasi sistematis' adalah gap literatur yang memotivasi paper (pdf:1, pdf:4), bukan keterbatasan paper; data internal justru disebut kelebihan (pdf:9); bahasa Inggris tidak disebut.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>tidak disebut</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>NOT_STATED_OK</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Chunk hanya abstrak; tidak ada keterbatasan.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
@@ -2576,7 +2173,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2591,17 +2188,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Inferensi: Meskipun berhasil mengurangi halusinasi pada RAG bahasa Arab, penelitian ini tidak mengevaluasi faithfulness atau abstention pada dokumen perbankan berbahasa Indonesia, sehingga belum menjawab fokus riset yang diusulkan.</t>
+          <t>Inferensi: Meskipun menilai kualitas jawaban, studi tidak mengevaluasi abstensi (menolak menjawab) ketika konteks tidak mengandung jawaban, dan tidak menggunakan dokumen perbankan berbahasa Indonesia, sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada dokumen bahasa Indonesia.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arabic Retrieval-Augmented Generation (RAG) systems</t>
+          <t>LLMs tend to provide answers even when relevant source information is missing</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>P03:abstract:0</t>
+          <t>P04:pdf:7; P04:pdf:0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2611,21 +2208,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Inferensi konsisten dengan abstract:0 (bahasa Arab).</t>
+          <t>Inferensi konsisten dengan pdf:7 (LLM tetap menjawab saat informasi tidak ada).</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Inferensi: Meskipun berhasil mengurangi halusinasi pada RAG bahasa Arab, penelitian ini tidak mengevaluasi faithfulness atau abstention pada dokumen perbankan berbahasa Indonesia, sehingga belum menjawab fokus riset yang diusulkan.</t>
+          <t>Inferensi: Meskipun menilai kualitas jawaban, studi tidak mengevaluasi abstensi (menolak menjawab) ketika konteks tidak mengandung jawaban, dan tidak menggunakan dokumen perbankan berbahasa Indonesia, sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada dokumen bahasa Indonesia.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2640,17 +2237,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Penulis menilai faktor-faktor yang memengaruhi kualitas jawaban dalam sistem RAG LLM pada domain keuangan, termasuk sensitivitas terhadap kualitas retrieval dan dampak prompt.</t>
+          <t>Paper memperkenalkan dataset LFQA keuangan pertama dan melakukan benchmark komprehensif untuk menilai kemampuan model dalam menjawab pertanyaan keuangan.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>We comprehensively assess various factors that contribute to the answer generation quality in LLM RAG systems, ranging from sensitivity to retrieval quality to the impact of different prompts</t>
+          <t>introducing the first LFQA financial dataset and conducting comprehensive benchmark experiments</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>P04:pdf:9</t>
+          <t>P05:pdf:10</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2660,21 +2257,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sesuai pdf:9.</t>
+          <t>Sesuai pdf:10.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Penulis menilai faktor-faktor yang memengaruhi kualitas jawaban dalam sistem RAG LLM pada domain keuangan, termasuk sensitivitas terhadap kualitas retrieval dan dampak prompt.</t>
+          <t>Paper memperkenalkan dataset LFQA keuangan pertama dan melakukan benchmark komprehensif untuk menilai kemampuan model dalam menjawab pertanyaan keuangan.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2689,17 +2286,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Studi menggunakan dua dataset RAG dari sektor perbankan: halaman web publik tentang produk perbankan dan panduan kebijakan internal, keduanya berbahasa Inggris.</t>
+          <t>Dataset berfokus pada domain keuangan, mencakup dokumen teks buku, regulasi, dan kebijakan dari sumber seperti HKMA, EU, dan Federal Reserve; berisi 1.262 pasangan QA dalam bahasa Inggris.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Banking webpages: Public webpages with general information on banking products, and Banking policy guides: internal guides for customer service executives</t>
+          <t>FinTextQA contains 1,262 QA pairs</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>P04:pdf:0; P04:pdf:1; P04:pdf:4</t>
+          <t>P05:pdf:5; P05:pdf:16; P05:pdf:4</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2709,29 +2306,29 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Dua korpus (banking webpages dan banking policy guides) didukung pdf:10; klaim 'keduanya berbahasa Inggris' tidak disebut di chunk.</t>
+          <t>Sumber (buku teks, HKMA, EU, Federal Reserve) dan 1.262 pasangan QA didukung pdf:16, pdf:19; 'bahasa Inggris' tidak dinyatakan eksplisit.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Studi memakai dua dataset RAG di sektor perbankan: halaman web publik berisi informasi umum produk perbankan dan panduan kebijakan internal untuk customer service executive. Pertanyaan berasal dari pengguna nyata (log sistem produksi), dan 800 query di-sampling per dataset.</t>
+          <t>Dataset FinTextQA di domain keuangan berisi 1.262 pasangan QA dari buku teks keuangan (BMFS, FCF, EMBFM) serta regulasi dan kebijakan dari situs HKMA, EU, dan Federal Reserve; dari 300 pasangan regulasi/kebijakan awal, 240 dipertahankan setelah kontrol kualitas.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>P04:pdf:10; P04:pdf:12; P04:pdf:9</t>
+          <t>P05:pdf:16; P05:pdf:19</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Studi memakai dua dataset RAG di sektor perbankan: halaman web publik berisi informasi umum produk perbankan dan panduan kebijakan internal untuk customer service executive. Pertanyaan berasal dari pengguna nyata (log sistem produksi), dan 800 query di-sampling per dataset.</t>
+          <t>Dataset FinTextQA di domain keuangan berisi 1.262 pasangan QA dari buku teks keuangan (BMFS, FCF, EMBFM) serta regulasi dan kebijakan dari situs HKMA, EU, dan Federal Reserve; dari 300 pasangan regulasi/kebijakan awal, 240 dipertahankan setelah kontrol kualitas.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2746,17 +2343,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Retriever menggunakan OpenAI Embeddings, dokumen dipotong menjadi chunk, dan generator berupa model LLM seperti GPT-4 dan Llama-2; variasi kualitas retrieval diuji dengan manipulasi list hasil retrieval.</t>
+          <t>Menggunakan empat embedder (Bge-small-en-v1.5, Gte-large, Ember-v1, Ada), tiga retriever (AMR, SWR, vector-based), tiga reranker (LLMRerank, Bge-Reranker-Base, All-Mpnet-Base-v2), serta generator LLM termasuk Baichuan2-7B.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>We sampled 800 user queries for each dataset and obtained retrieved document chunks using a retriever(OpenAI Embeddings2)</t>
+          <t>We adopt four popular embedding models... We explore three retriever methods... examine the influence of three rerankers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>P04:pdf:12; P04:pdf:29</t>
+          <t>P05:pdf:14; P05:pdf:28; P05:pdf:31</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2766,21 +2363,21 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>OpenAI Embeddings, chunk, manipulasi daftar retrieval (pdf:12); GPT-4 dan Llama-2 di antara 6 LLM (pdf:7, pdf:9).</t>
+          <t>Embedder, retriever, reranker sesuai pdf:28, pdf:31; Baichuan2-7B ada di pdf:49.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Retriever menggunakan OpenAI Embeddings, dokumen dipotong menjadi chunk, dan generator berupa model LLM seperti GPT-4 dan Llama-2; variasi kualitas retrieval diuji dengan manipulasi list hasil retrieval.</t>
+          <t>Menggunakan empat embedder (Bge-small-en-v1.5, Gte-large, Ember-v1, Ada), tiga retriever (AMR, SWR, vector-based), tiga reranker (LLMRerank, Bge-Reranker-Base, All-Mpnet-Base-v2), serta generator LLM termasuk Baichuan2-7B.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2795,41 +2392,49 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Evaluasi mencakup kemampuan LLM mengikuti instruksi, kualitas jawaban, serta metrik ekstraktivitas, dengan perbandingan antar model seperti GPT-4, GPT-3.5-Turbo, dan Llama-2.</t>
+          <t>Evaluasi menggunakan metrik otomatis ROUGE-1/2/L, BLEU, serta skor GPT-4 yang menilai kegunaan, relevansi, akurasi, kedalaman, dan kreativitas; juga melibatkan penilaian manusia dengan skala 1-5.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Our findings reveal that generative LLMs outperform baseline models in answer quality, even on metrics emphasizing extractiveness</t>
+          <t>ROUGE and BLEU are used to automatically measure... GPT‑4 scoring method is used to evaluate the answers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>P04:pdf:7; P04:pdf:29</t>
+          <t>P05:pdf:38; P05:pdf:19; P05:pdf:37</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Instruction following, kualitas jawaban, metrik ekstraktivitas, perbandingan GPT-4/GPT-3.5-Turbo/Llama-2, pdf:7.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>Skala 1-5 di pdf:19 dipakai untuk kontrol kualitas dataset, bukan evaluasi jawaban; evaluasi manusia berupa ranking oleh tiga anotator (pdf:38).</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Evaluasi memakai ROUGE-1/2/L dan BLEU, skor GPT-4 (Likert lima poin) atas helpfulness, relevansi, akurasi, kedalaman, dan kreativitas, rasio pertanyaan tidak terjawab, serta ranking jawaban terbaik oleh tiga anotator manusia dibandingkan ground truth.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>P05:pdf:37; P05:pdf:38</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Evaluasi mencakup kemampuan LLM mengikuti instruksi, kualitas jawaban, serta metrik ekstraktivitas, dengan perbandingan antar model seperti GPT-4, GPT-3.5-Turbo, dan Llama-2.</t>
+          <t>Evaluasi memakai ROUGE-1/2/L dan BLEU, skor GPT-4 (Likert lima poin) atas helpfulness, relevansi, akurasi, kedalaman, dan kreativitas, rasio pertanyaan tidak terjawab, serta ranking jawaban terbaik oleh tiga anotator manusia dibandingkan ground truth.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2844,49 +2449,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Optimasi retrieval terbukti penting; peningkatan recall dan precision meningkatkan kualitas jawaban, sementara LLM cenderung memberikan jawaban meski dokumen relevan tidak ada, terutama pada model kecil.</t>
+          <t>Embedder Ada mencapai skor GPT-4 tertinggi 4.586; retriever AMR memperoleh 4.492; kombinasi AMR, Ada, Bge-Reranker-Base menghasilkan skor tertinggi 4.622. Generator pada dataset regulasi memperoleh ROUGE-1 0.317 dan GPT-4 4.238.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>We recommend prioritizing retrieval recall, while tuning retrieval systems, as LLMs exhibit pseudo-helpfulness when relevant gold document(s) are not retrieved</t>
+          <t>Ada2, achieving a score of 4.586... AMR outperforms the rest with an impressive score of 4.492... ROUGE‑1 scores are 0.317 and 0.270, respectively; the GPT‑4 scores are 4.238 and 4.293</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>P04:pdf:30; P04:pdf:29; P04:pdf:22</t>
+          <t>P05:pdf:39; P05:pdf:40; P05:pdf:46</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>SUPPORTED</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>'Terutama pada model kecil' tidak didukung untuk pseudo-helpfulness; chunk mengaitkan model kecil (Llama-2) dengan kegagalan mengikuti instruksi panjang, bukan pseudo-helpfulness.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Optimasi retrieval penting meskipun memakai GPT-4: recall retrieval perlu diprioritaskan karena LLM menunjukkan pseudo-helpfulness ketika dokumen gold tidak ter-retrieve, dan peningkatan precision diperkirakan memperbaiki performa. Model sensitif terhadap distractor; selisih besar terlihat antara LLM vendor (OpenAI) dan model open-source kecil, dan Llama-2 kecil sering gagal mengikuti instruksi panjang.</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>P04:pdf:7; P04:pdf:29; P04:pdf:30; P04:pdf:22</t>
-        </is>
-      </c>
+          <t>Semua angka cocok dengan pdf:39, pdf:40, pdf:46.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Optimasi retrieval penting meskipun memakai GPT-4: recall retrieval perlu diprioritaskan karena LLM menunjukkan pseudo-helpfulness ketika dokumen gold tidak ter-retrieve, dan peningkatan precision diperkirakan memperbaiki performa. Model sensitif terhadap distractor; selisih besar terlihat antara LLM vendor (OpenAI) dan model open-source kecil, dan Llama-2 kecil sering gagal mengikuti instruksi panjang.</t>
+          <t>Embedder Ada mencapai skor GPT-4 tertinggi 4.586; retriever AMR memperoleh 4.492; kombinasi AMR, Ada, Bge-Reranker-Base menghasilkan skor tertinggi 4.622. Generator pada dataset regulasi memperoleh ROUGE-1 0.317 dan GPT-4 4.238.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2896,50 +2493,54 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>quote_fuzzy</t>
+          <t>quote_verified</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Penulis mengakui kurangnya investigasi sistematis pada tiap komponen RAG dan bahwa studi terbatas pada data internal serta bahasa Inggris, sehingga generalisasi masih terbatas.</t>
+          <t>Dataset memiliki jumlah pasangan QA yang relatif kecil dibandingkan dataset AI-generated besar, sehingga dapat memengaruhi generalisasi; data berkualitas tinggi sulit diperoleh karena hak cipta; belum ada dataset LFQA khusus untuk bahasa Indonesia.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>there is a lack of systematic investigations of the impact of each component (retriever, prompts, models) on answer generation quality</t>
+          <t>FinTextQA contains a relatively smaller number of QA pairs... High‑quality data are challenging to acquire... none of them addresses LFQA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>P04:pdf:2; P04:pdf:9; P04:pdf:4</t>
+          <t>P05:pdf:49; P05:pdf:10; P05:pdf:12</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>UNSUPPORTED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>'Kurangnya investigasi sistematis' adalah gap literatur yang memotivasi paper (pdf:1, pdf:4), bukan keterbatasan paper; data internal justru disebut kelebihan (pdf:9); bahasa Inggris tidak disebut.</t>
+          <t>Ukuran dataset kecil dan hambatan hak cipta didukung pdf:49; 'belum ada dataset LFQA bahasa Indonesia' tidak disebut (pdf:12 hanya menyebut dataset QA keuangan terdahulu tidak menangani LFQA).</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>tidak disebut</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>FinTextQA memiliki jumlah pasangan QA relatif kecil dibanding dataset AI-generated yang lebih besar, sehingga dapat memengaruhi generalisasi; data berkualitas tinggi sulit diperoleh dan pembatasan hak cipta sering menghalangi berbagi data.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>P05:pdf:49</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>tidak disebut</t>
+          <t>FinTextQA memiliki jumlah pasangan QA relatif kecil dibanding dataset AI-generated yang lebih besar, sehingga dapat memengaruhi generalisasi; data berkualitas tinggi sulit diperoleh dan pembatasan hak cipta sering menghalangi berbagi data.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2954,17 +2555,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Inferensi: Meskipun menilai kualitas jawaban, studi tidak mengevaluasi abstensi (menolak menjawab) ketika konteks tidak mengandung jawaban, dan tidak menggunakan dokumen perbankan berbahasa Indonesia, sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada dokumen bahasa Indonesia.</t>
+          <t>Inferensi: Meskipun FinTextQA menyediakan benchmark LFQA keuangan, penelitian ini tidak mengevaluasi faithfulness atau kemampuan abstention pada dokumen produk perbankan berbahasa Indonesia, sehingga belum menjawab fokus riset yang diusulkan.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>LLMs tend to provide answers even when relevant source information is missing</t>
+          <t>none of them addresses LFQA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>P04:pdf:7; P04:pdf:0</t>
+          <t>P05:pdf:12; P05:pdf:4; P05:pdf:11</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2974,21 +2575,21 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Inferensi konsisten dengan pdf:7 (LLM tetap menjawab saat informasi tidak ada).</t>
+          <t>Inferensi tidak bertentangan dengan chunk.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Inferensi: Meskipun menilai kualitas jawaban, studi tidak mengevaluasi abstensi (menolak menjawab) ketika konteks tidak mengandung jawaban, dan tidak menggunakan dokumen perbankan berbahasa Indonesia, sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada dokumen bahasa Indonesia.</t>
+          <t>Inferensi: Meskipun FinTextQA menyediakan benchmark LFQA keuangan, penelitian ini tidak mengevaluasi faithfulness atau kemampuan abstention pada dokumen produk perbankan berbahasa Indonesia, sehingga belum menjawab fokus riset yang diusulkan.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3003,17 +2604,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Paper memperkenalkan dataset LFQA keuangan pertama dan melakukan benchmark komprehensif untuk menilai kemampuan model dalam menjawab pertanyaan keuangan.</t>
+          <t>Penelitian ini mengeksplorasi penerapan retrieval-augmented generation (RAG) untuk meningkatkan akurasi dan keandalan model bahasa besar dalam analisis laporan keuangan bank.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>introducing the first LFQA financial dataset and conducting comprehensive benchmark experiments</t>
+          <t>This study explores the application of retrieval-augmented generation (RAG) to improve the accuracy and reliability of large language models (LLMs) in the context of financial report analysis.</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>P05:pdf:10</t>
+          <t>P06:abstract:0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3023,21 +2624,21 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sesuai pdf:10.</t>
+          <t>Sesuai abstract:0.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Paper memperkenalkan dataset LFQA keuangan pertama dan melakukan benchmark komprehensif untuk menilai kemampuan model dalam menjawab pertanyaan keuangan.</t>
+          <t>Penelitian ini mengeksplorasi penerapan retrieval-augmented generation (RAG) untuk meningkatkan akurasi dan keandalan model bahasa besar dalam analisis laporan keuangan bank.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3047,54 +2648,46 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>quote_not_found</t>
+          <t>quote_verified</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Dataset berfokus pada domain keuangan, mencakup dokumen teks buku, regulasi, dan kebijakan dari sumber seperti HKMA, EU, dan Federal Reserve; berisi 1.262 pasangan QA dalam bahasa Inggris.</t>
+          <t>Domainnya adalah laporan keuangan bank (setengah tahunan atau kuartalan) untuk investor pribadi; bahasa tidak disebutkan dalam abstrak.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FinTextQA contains 1,262 QA pairs</t>
+          <t>enhancing the question-and-answering capabilities regarding the half-yearly or quarterly financial reports of banks.</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>P05:pdf:5; P05:pdf:16; P05:pdf:4</t>
+          <t>P06:abstract:0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>SUPPORTED</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Sumber (buku teks, HKMA, EU, Federal Reserve) dan 1.262 pasangan QA didukung pdf:16, pdf:19; 'bahasa Inggris' tidak dinyatakan eksplisit.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Dataset FinTextQA di domain keuangan berisi 1.262 pasangan QA dari buku teks keuangan (BMFS, FCF, EMBFM) serta regulasi dan kebijakan dari situs HKMA, EU, dan Federal Reserve; dari 300 pasangan regulasi/kebijakan awal, 240 dipertahankan setelah kontrol kualitas.</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>P05:pdf:16; P05:pdf:19</t>
-        </is>
-      </c>
+          <t>Sesuai abstract:0.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Dataset FinTextQA di domain keuangan berisi 1.262 pasangan QA dari buku teks keuangan (BMFS, FCF, EMBFM) serta regulasi dan kebijakan dari situs HKMA, EU, dan Federal Reserve; dari 300 pasangan regulasi/kebijakan awal, 240 dipertahankan setelah kontrol kualitas.</t>
+          <t>Domainnya adalah laporan keuangan bank (setengah tahunan atau kuartalan) untuk investor pribadi; bahasa tidak disebutkan dalam abstrak.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3109,41 +2702,49 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Menggunakan empat embedder (Bge-small-en-v1.5, Gte-large, Ember-v1, Ada), tiga retriever (AMR, SWR, vector-based), tiga reranker (LLMRerank, Bge-Reranker-Base, All-Mpnet-Base-v2), serta generator LLM termasuk Baichuan2-7B.</t>
+          <t>Sistem RAG menggunakan retriever OpenAI ADA, embedder MiniLM pada model tiga, dan generator OpenAI GPT-4; variasi komponen diuji dalam beberapa model.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>We adopt four popular embedding models... We explore three retriever methods... examine the influence of three rerankers</t>
+          <t>model one (OpenAI ADA and OpenAI GPT-4) achieved the highest performance</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>P05:pdf:14; P05:pdf:28; P05:pdf:31</t>
+          <t>P06:abstract:0; P06:abstract:1</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Embedder, retriever, reranker sesuai pdf:28, pdf:31; Baichuan2-7B ada di pdf:49.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>Abstrak menyebut OpenAI ADA sebagai pasangan komponen model satu dan MiniLM sebagai embedder; ADA tidak disebut sebagai 'retriever'.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Sistem RAG dikembangkan dengan metodologi Design Science Research; beberapa model dengan komponen RAG berbeda diuji, antara lain model satu (OpenAI ADA dan OpenAI GPT-4) dan model tiga (MiniLM Embedder dan OpenAI GPT-4).</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>P06:abstract:0; P06:abstract:1</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Menggunakan empat embedder (Bge-small-en-v1.5, Gte-large, Ember-v1, Ada), tiga retriever (AMR, SWR, vector-based), tiga reranker (LLMRerank, Bge-Reranker-Base, All-Mpnet-Base-v2), serta generator LLM termasuk Baichuan2-7B.</t>
+          <t>Sistem RAG dikembangkan dengan metodologi Design Science Research; beberapa model dengan komponen RAG berbeda diuji, antara lain model satu (OpenAI ADA dan OpenAI GPT-4) dan model tiga (MiniLM Embedder dan OpenAI GPT-4).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3158,49 +2759,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Evaluasi menggunakan metrik otomatis ROUGE-1/2/L, BLEU, serta skor GPT-4 yang menilai kegunaan, relevansi, akurasi, kedalaman, dan kreativitas; juga melibatkan penilaian manusia dengan skala 1-5.</t>
+          <t>Evaluasi dilakukan dengan mengukur akurasi, relevansi jawaban, serta perbandingan kinerja pada laporan terstruktur vs tidak terstruktur dan pertanyaan kualitatif vs kuantitatif.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ROUGE and BLEU are used to automatically measure... GPT‑4 scoring method is used to evaluate the answers</t>
+          <t>showing robust accuracy and relevance in response</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>P05:pdf:38; P05:pdf:19; P05:pdf:37</t>
+          <t>P06:abstract:1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>SUPPORTED</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Skala 1-5 di pdf:19 dipakai untuk kontrol kualitas dataset, bukan evaluasi jawaban; evaluasi manusia berupa ranking oleh tiga anotator (pdf:38).</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Evaluasi memakai ROUGE-1/2/L dan BLEU, skor GPT-4 (Likert lima poin) atas helpfulness, relevansi, akurasi, kedalaman, dan kreativitas, rasio pertanyaan tidak terjawab, serta ranking jawaban terbaik oleh tiga anotator manusia dibandingkan ground truth.</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>P05:pdf:37; P05:pdf:38</t>
-        </is>
-      </c>
+          <t>Akurasi/relevansi dan perbandingan laporan terstruktur serta pertanyaan kualitatif vs kuantitatif ada di abstract:1 (abstract:0 juga menyebut context relevance dan answer faithfulness).</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Evaluasi memakai ROUGE-1/2/L dan BLEU, skor GPT-4 (Likert lima poin) atas helpfulness, relevansi, akurasi, kedalaman, dan kreativitas, rasio pertanyaan tidak terjawab, serta ranking jawaban terbaik oleh tiga anotator manusia dibandingkan ground truth.</t>
+          <t>Evaluasi dilakukan dengan mengukur akurasi, relevansi jawaban, serta perbandingan kinerja pada laporan terstruktur vs tidak terstruktur dan pertanyaan kualitatif vs kuantitatif.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3215,17 +2808,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Embedder Ada mencapai skor GPT-4 tertinggi 4.586; retriever AMR memperoleh 4.492; kombinasi AMR, Ada, Bge-Reranker-Base menghasilkan skor tertinggi 4.622. Generator pada dataset regulasi memperoleh ROUGE-1 0.317 dan GPT-4 4.238.</t>
+          <t>Model satu (OpenAI ADA + GPT-4) memberikan performa tertinggi, sedangkan model tiga (MiniLM + GPT-4) jauh lebih rendah; laporan terstruktur meningkatkan kinerja RAG, dan pertanyaan kualitatif memperoleh skor lebih tinggi.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ada2, achieving a score of 4.586... AMR outperforms the rest with an impressive score of 4.492... ROUGE‑1 scores are 0.317 and 0.270, respectively; the GPT‑4 scores are 4.238 and 4.293</t>
+          <t>Model three (MiniLM Embedder and OpenAI GPT-4) scored significantly lower, indicating the importance of high-quality components.</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>P05:pdf:39; P05:pdf:40; P05:pdf:46</t>
+          <t>P06:abstract:1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3235,21 +2828,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Semua angka cocok dengan pdf:39, pdf:40, pdf:46.</t>
+          <t>Sesuai abstract:1.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Embedder Ada mencapai skor GPT-4 tertinggi 4.586; retriever AMR memperoleh 4.492; kombinasi AMR, Ada, Bge-Reranker-Base menghasilkan skor tertinggi 4.622. Generator pada dataset regulasi memperoleh ROUGE-1 0.317 dan GPT-4 4.238.</t>
+          <t>Model satu (OpenAI ADA + GPT-4) memberikan performa tertinggi, sedangkan model tiga (MiniLM + GPT-4) jauh lebih rendah; laporan terstruktur meningkatkan kinerja RAG, dan pertanyaan kualitatif memperoleh skor lebih tinggi.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3259,54 +2852,38 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>quote_verified</t>
+          <t>not_stated</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Dataset memiliki jumlah pasangan QA yang relatif kecil dibandingkan dataset AI-generated besar, sehingga dapat memengaruhi generalisasi; data berkualitas tinggi sulit diperoleh karena hak cipta; belum ada dataset LFQA khusus untuk bahasa Indonesia.</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>FinTextQA contains a relatively smaller number of QA pairs... High‑quality data are challenging to acquire... none of them addresses LFQA</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>P05:pdf:49; P05:pdf:10; P05:pdf:12</t>
-        </is>
-      </c>
+          <t>tidak disebut</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>NOT_STATED_OK</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Ukuran dataset kecil dan hambatan hak cipta didukung pdf:49; 'belum ada dataset LFQA bahasa Indonesia' tidak disebut (pdf:12 hanya menyebut dataset QA keuangan terdahulu tidak menangani LFQA).</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>FinTextQA memiliki jumlah pasangan QA relatif kecil dibanding dataset AI-generated yang lebih besar, sehingga dapat memengaruhi generalisasi; data berkualitas tinggi sulit diperoleh dan pembatasan hak cipta sering menghalangi berbagi data.</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>P05:pdf:49</t>
-        </is>
-      </c>
+          <t>Chunk hanya abstrak.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>FinTextQA memiliki jumlah pasangan QA relatif kecil dibanding dataset AI-generated yang lebih besar, sehingga dapat memengaruhi generalisasi; data berkualitas tinggi sulit diperoleh dan pembatasan hak cipta sering menghalangi berbagi data.</t>
+          <t>tidak disebut</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3321,17 +2898,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Inferensi: Meskipun FinTextQA menyediakan benchmark LFQA keuangan, penelitian ini tidak mengevaluasi faithfulness atau kemampuan abstention pada dokumen produk perbankan berbahasa Indonesia, sehingga belum menjawab fokus riset yang diusulkan.</t>
+          <t>Inferensi: Meskipun studi ini menyebutkan peningkatan answer faithfulness, tidak mengevaluasi abstention atau penggunaan dokumen bahasa Indonesia, sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada dokumen produk perbankan berbahasa Indonesia.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>none of them addresses LFQA</t>
+          <t>aim is to enhance context relevance, answer faithfulness, and answer relevance</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>P05:pdf:12; P05:pdf:4; P05:pdf:11</t>
+          <t>P06:abstract:0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3341,21 +2918,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Inferensi tidak bertentangan dengan chunk.</t>
+          <t>Inferensi konsisten; catatan: abstract:0 menyebut faithfulness sebagai tujuan, bukan hasil terukur.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Inferensi: Meskipun FinTextQA menyediakan benchmark LFQA keuangan, penelitian ini tidak mengevaluasi faithfulness atau kemampuan abstention pada dokumen produk perbankan berbahasa Indonesia, sehingga belum menjawab fokus riset yang diusulkan.</t>
+          <t>Inferensi: Meskipun studi ini menyebutkan peningkatan answer faithfulness, tidak mengevaluasi abstention atau penggunaan dokumen bahasa Indonesia, sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada dokumen produk perbankan berbahasa Indonesia.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3370,17 +2947,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Penelitian ini mengeksplorasi penerapan retrieval-augmented generation (RAG) untuk meningkatkan akurasi dan keandalan model bahasa besar dalam analisis laporan keuangan bank.</t>
+          <t>Paper mengidentifikasi kebutuhan akan kerangka evaluasi yang memperhitungkan heterogenitas dokumen, tipe pertanyaan, dan kedalaman penalaran dalam sistem RAG pada domain keuangan.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>This study explores the application of retrieval-augmented generation (RAG) to improve the accuracy and reliability of large language models (LLMs) in the context of financial report analysis.</t>
+          <t>These insights emphasize the importance of benchmarks that capture real-world document heterogeneity while enabling multifaceted evaluations aligned with the strengths and trade-offs of both models and methodologies.</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>P06:abstract:0</t>
+          <t>P08:pdf:12; P08:pdf:8; P08:pdf:11</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3390,21 +2967,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Sesuai abstract:0.</t>
+          <t>Sesuai pdf:12.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Penelitian ini mengeksplorasi penerapan retrieval-augmented generation (RAG) untuk meningkatkan akurasi dan keandalan model bahasa besar dalam analisis laporan keuangan bank.</t>
+          <t>Paper mengidentifikasi kebutuhan akan kerangka evaluasi yang memperhitungkan heterogenitas dokumen, tipe pertanyaan, dan kedalaman penalaran dalam sistem RAG pada domain keuangan.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3414,22 +2991,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>quote_verified</t>
+          <t>quote_fuzzy</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Domainnya adalah laporan keuangan bank (setengah tahunan atau kuartalan) untuk investor pribadi; bahasa tidak disebutkan dalam abstrak.</t>
+          <t>Benchmark FinDoc-RAG mencakup 600+ pasangan QA dari 46 dokumen keuangan berbahasa Inggris, termasuk deskripsi produk, panduan investasi, kebijakan hukum, dan materi pemasaran dengan konten numerik padat.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>enhancing the question-and-answering capabilities regarding the half-yearly or quarterly financial reports of banks.</t>
+          <t>FinDoc-RAG comprises 600+ QA pairs extracted from 46 documents in English from UBS AG and other UBS entities.</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>P06:abstract:0</t>
+          <t>P08:pdf:5; P08:pdf:7; P08:pdf:4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3439,21 +3016,21 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Sesuai abstract:0.</t>
+          <t>Sesuai pdf:4, pdf:12 (dokumen UBS).</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Domainnya adalah laporan keuangan bank (setengah tahunan atau kuartalan) untuk investor pribadi; bahasa tidak disebutkan dalam abstrak.</t>
+          <t>Benchmark FinDoc-RAG mencakup 600+ pasangan QA dari 46 dokumen keuangan berbahasa Inggris, termasuk deskripsi produk, panduan investasi, kebijakan hukum, dan materi pemasaran dengan konten numerik padat.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3468,49 +3045,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Sistem RAG menggunakan retriever OpenAI ADA, embedder MiniLM pada model tiga, dan generator OpenAI GPT-4; variasi komponen diuji dalam beberapa model.</t>
+          <t>Arsitektur yang dievaluasi meliputi Vector-RAG berbasis indeks vektor dense, tanpa fine-tuning, dengan konfigurasi default serta alur lengkap retrieval-to-answer tanpa intervensi manusia.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>model one (OpenAI ADA and OpenAI GPT-4) achieved the highest performance</t>
+          <t>Vector-based (Vector-RAG) ... using cosine as the similarity metric.</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>P06:abstract:0; P06:abstract:1</t>
+          <t>P08:pdf:50; P08:pdf:27; P08:pdf:25</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>SUPPORTED</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Abstrak menyebut OpenAI ADA sebagai pasangan komponen model satu dan MiniLM sebagai embedder; ADA tidak disebut sebagai 'retriever'.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Sistem RAG dikembangkan dengan metodologi Design Science Research; beberapa model dengan komponen RAG berbeda diuji, antara lain model satu (OpenAI ADA dan OpenAI GPT-4) dan model tiga (MiniLM Embedder dan OpenAI GPT-4).</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>P06:abstract:0; P06:abstract:1</t>
-        </is>
-      </c>
+          <t>Vector-RAG, zero-shot tanpa fine-tuning, default config, end-to-end didukung pdf:25-27; arsitektur lain (graph, RAPTOR, KG) tidak disebut tetapi tidak salah.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Sistem RAG dikembangkan dengan metodologi Design Science Research; beberapa model dengan komponen RAG berbeda diuji, antara lain model satu (OpenAI ADA dan OpenAI GPT-4) dan model tiga (MiniLM Embedder dan OpenAI GPT-4).</t>
+          <t>Arsitektur yang dievaluasi meliputi Vector-RAG berbasis indeks vektor dense, tanpa fine-tuning, dengan konfigurasi default serta alur lengkap retrieval-to-answer tanpa intervensi manusia.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3525,17 +3094,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Evaluasi dilakukan dengan mengukur akurasi, relevansi jawaban, serta perbandingan kinerja pada laporan terstruktur vs tidak terstruktur dan pertanyaan kualitatif vs kuantitatif.</t>
+          <t>Evaluasi mencakup akurasi rata-rata, LLMLogScore (L3Score) berbasis log-likelihood, serta penilaian biner CORRECT/INCORRECT oleh LLM judge pada tiga run independen.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>showing robust accuracy and relevance in response</t>
+          <t>We computed accuracy as the mean proportion of CORRECT responses per question ... adopt the LLMLogScore (L3Score) metric.</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>P06:abstract:1</t>
+          <t>P08:pdf:22; P08:pdf:36; P08:pdf:35</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3545,21 +3114,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Akurasi/relevansi dan perbandingan laporan terstruktur serta pertanyaan kualitatif vs kuantitatif ada di abstract:1 (abstract:0 juga menyebut context relevance dan answer faithfulness).</t>
+          <t>Sesuai pdf:35, pdf:36.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Evaluasi dilakukan dengan mengukur akurasi, relevansi jawaban, serta perbandingan kinerja pada laporan terstruktur vs tidak terstruktur dan pertanyaan kualitatif vs kuantitatif.</t>
+          <t>Evaluasi mencakup akurasi rata-rata, LLMLogScore (L3Score) berbasis log-likelihood, serta penilaian biner CORRECT/INCORRECT oleh LLM judge pada tiga run independen.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3569,22 +3138,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>quote_verified</t>
+          <t>quote_not_found</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Model satu (OpenAI ADA + GPT-4) memberikan performa tertinggi, sedangkan model tiga (MiniLM + GPT-4) jauh lebih rendah; laporan terstruktur meningkatkan kinerja RAG, dan pertanyaan kualitatif memperoleh skor lebih tinggi.</t>
+          <t>Sistem teratas mencapai akurasi 0.91 pada ekstraksi faktual, namun hanya 0.44 pada sintesis multi-dokumen; RAPTOR memperoleh skor rata-rata 0.66 (σ=0.17), sementara GFM-RAG mencapai akurasi sempurna 1.00 pada level L3.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Model three (MiniLM Embedder and OpenAI GPT-4) scored significantly lower, indicating the importance of high-quality components.</t>
+          <t>leading systems achieve 0.91 accuracy in factual extraction but only 0.44 on multi-document synthesis tasks.</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>P06:abstract:1</t>
+          <t>P08:pdf:12; P08:pdf:26; P08:pdf:40</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3594,21 +3163,21 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Sesuai abstract:1.</t>
+          <t>0,91/0,44 (pdf:5), RAPTOR 0,66 sigma=0,17 dan GFM-RAG 1,00 pada L3 (pdf:40) cocok.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Model satu (OpenAI ADA + GPT-4) memberikan performa tertinggi, sedangkan model tiga (MiniLM + GPT-4) jauh lebih rendah; laporan terstruktur meningkatkan kinerja RAG, dan pertanyaan kualitatif memperoleh skor lebih tinggi.</t>
+          <t>Sistem teratas mencapai akurasi 0.91 pada ekstraksi faktual, namun hanya 0.44 pada sintesis multi-dokumen; RAPTOR memperoleh skor rata-rata 0.66 (σ=0.17), sementara GFM-RAG mencapai akurasi sempurna 1.00 pada level L3.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3618,38 +3187,54 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>not_stated</t>
+          <t>quote_verified</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>tidak disebut</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
+          <t>Penulis mencatat keterbatasan LLM dalam penalaran kuantitatif, cakupan dokumen yang hanya sebagian dari keseluruhan domain, serta metrik yang belum sepenuhnya menangkap semua dimensi kualitas jawaban.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Current LLMs show limitations in quantitative reasoning and cross-document synthesis essential for financial applications.</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>P08:pdf:2; P08:pdf:49; P08:pdf:6</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>NOT_STATED_OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Chunk hanya abstrak.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>'Keterbatasan LLM dalam penalaran kuantitatif' (pdf:2) adalah konteks umum di pendahuluan, bukan keterbatasan paper; cakupan dokumen dan metrik didukung pdf:49; keterbatasan pertanyaan auto-generated terlewat.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Penulis mencatat pertanyaan yang dibangkitkan otomatis kadang kurang mendalam dibanding pertanyaan buatan manusia, koleksi dokumen hanya sebagian dari ragam dokumen keuangan, dan pendekatan evaluasi multifaset mungkin belum menangkap semua dimensi kualitas jawaban.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>P08:pdf:49</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>tidak disebut</t>
+          <t>Penulis mencatat pertanyaan yang dibangkitkan otomatis kadang kurang mendalam dibanding pertanyaan buatan manusia, koleksi dokumen hanya sebagian dari ragam dokumen keuangan, dan pendekatan evaluasi multifaset mungkin belum menangkap semua dimensi kualitas jawaban.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3664,17 +3249,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Inferensi: Meskipun studi ini menyebutkan peningkatan answer faithfulness, tidak mengevaluasi abstention atau penggunaan dokumen bahasa Indonesia, sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada dokumen produk perbankan berbahasa Indonesia.</t>
+          <t>Tidak ada evaluasi faithfulness atau mekanisme abstention pada dokumen perbankan berbahasa Indonesia; fokus benchmark hanya pada dokumen berbahasa Inggris dan tidak menguji penolakan jawaban ketika konteks tidak memadai. Inferensi: Penelitian selanjutnya perlu menambah bahasa Indonesia serta mengukur kemampuan sistem menolak menjawab pertanyaan di luar cakupan konteks.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>aim is to enhance context relevance, answer faithfulness, and answer relevance</t>
+          <t>Finally, our metrics comparison reveals challenges in accurately measuring RAG system performance, suggesting that even our multifaceted evaluation approach may not capture all dimensions of answer quality relevant to financial domain experts.</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>P06:abstract:0</t>
+          <t>P08:pdf:49; P08:pdf:14; P08:pdf:35</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3684,21 +3269,21 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Inferensi konsisten; catatan: abstract:0 menyebut faithfulness sebagai tujuan, bukan hasil terukur.</t>
+          <t>Premis bahasa Inggris didukung pdf:4/pdf:12; ketiadaan faithfulness/abstention konsisten dengan metrik di pdf:35-36 (argumen dari ketiadaan).</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Inferensi: Meskipun studi ini menyebutkan peningkatan answer faithfulness, tidak mengevaluasi abstention atau penggunaan dokumen bahasa Indonesia, sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada dokumen produk perbankan berbahasa Indonesia.</t>
+          <t>Tidak ada evaluasi faithfulness atau mekanisme abstention pada dokumen perbankan berbahasa Indonesia; fokus benchmark hanya pada dokumen berbahasa Inggris dan tidak menguji penolakan jawaban ketika konteks tidak memadai. Inferensi: Penelitian selanjutnya perlu menambah bahasa Indonesia serta mengukur kemampuan sistem menolak menjawab pertanyaan di luar cakupan konteks.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>P07</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3713,17 +3298,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Paper ini mengidentifikasi kebutuhan benchmark RAG yang komprehensif karena benchmark saat ini memiliki skenario sempit dan dimensi evaluasi terbatas.</t>
+          <t>Paper ini mengidentifikasi kebutuhan akan evaluasi sistem Retrieval-Augmented Generation (RAG) yang akurat dalam domain keuangan, mengingat kesalahan kecil dapat berdampak besar pada investasi dan kepatuhan.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>current RAG benchmarks often suffer from narrow scenarios and limited evaluation dimensions</t>
+          <t>Accurate information retrieval is critical in financial Question-Answering (QA)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>P07:pdf:0</t>
+          <t>P09:pdf:2</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3733,21 +3318,25 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sesuai pdf:0.</t>
+          <t>Kebutuhan presisi QA keuangan dan dampak kesalahan pada investasi, risk management, compliance ada di chunk 2.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>P09:pdf:2</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Paper ini mengidentifikasi kebutuhan benchmark RAG yang komprehensif karena benchmark saat ini memiliki skenario sempit dan dimensi evaluasi terbatas.</t>
+          <t>Paper ini mengidentifikasi kebutuhan akan evaluasi sistem Retrieval-Augmented Generation (RAG) yang akurat dalam domain keuangan, mengingat kesalahan kecil dapat berdampak besar pada investasi dan kepatuhan.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>P07</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3762,41 +3351,49 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Domain keuangan mencakup subdomain seperti perbankan investasi, asuransi, pasar modal, dan lainnya, dengan dokumen berbahasa Mandarin/Chinese yang diambil dari situs resmi dan berbagai format.</t>
+          <t>Dataset FINDER mencakup dokumen keuangan seperti artikel berita, filing, dan basis pengetahuan, berfokus pada bahasa Inggris dan tidak menyebutkan dokumen perbankan Indonesia.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>finance is one of the most widespread vertical domains, comprising a wealth of professional knowledge</t>
+          <t>retrieving relevant documents (e.g., news articles, filings, and knowledge bases)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>P07:pdf:17; P07:pdf:14</t>
+          <t>P09:pdf:12; P09:pdf:10; P09:pdf:3</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Subdomain dari pdf:17; korpus berbahasa Mandarin (wikipedia-zh, BAAI-Fin zh, situs agensi resmi Tiongkok) dan format PDF/SQLite di pdf:16-17. Sumber juga mencakup BSCF dan FinGLM, tidak hanya situs resmi.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t>Daftar 'artikel berita, filing, basis pengetahuan' di chunk 12 menjelaskan apa yang diambil RAG secara umum, bukan isi FINDER; klaim berbahasa Inggris tidak dinyatakan di chunk.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>FINDER dibangun dari kueri pencarian nyata para profesional keuangan untuk menangkap ambiguitas dan ketergantungan konteks kueri keuangan. Kueri dikelompokkan per kategori (mis. Accounting 8,61%, Company Overview 18,95%, Financials 17,36%), dengan 15,48% kueri membutuhkan penalaran kuantitatif; korpus retrieval berasal dari dokumen HTML mentah yang dipecah per paragraf.</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>P09:pdf:6; P09:pdf:25; P09:pdf:30</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Domain keuangan mencakup subdomain seperti perbankan investasi, asuransi, pasar modal, dan lainnya, dengan dokumen berbahasa Mandarin/Chinese yang diambil dari situs resmi dan berbagai format.</t>
+          <t>FINDER dibangun dari kueri pencarian nyata para profesional keuangan untuk menangkap ambiguitas dan ketergantungan konteks kueri keuangan. Kueri dikelompokkan per kategori (mis. Accounting 8,61%, Company Overview 18,95%, Financials 17,36%), dengan 15,48% kueri membutuhkan penalaran kuantitatif; korpus retrieval berasal dari dokumen HTML mentah yang dipecah per paragraf.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>P07</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3811,17 +3408,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Menggunakan retriever seperti BGE-M3, BGE-large-zh, GTE-Qwen2-1.5b, dan jina-zh; generator LLM termasuk Qwen2.5-72B, Deepseek-v2-chat, Yi15-34B, Llama3.1-70B; chunking panjang 2048 dengan overlap 256.</t>
+          <t>Sistem RAG menggunakan retriever BM25 (k1=1.2, b=0.75) serta model dense seperti e5-mistral-7b-instruct, mE5, dan GTE; dokumen dipotong menjadi paragraf, dan generator meliputi GPT-o1, Claude-3.7-Sonnet, Qwen-QWQ-32B, serta DeepSeek-R1-Distill.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>We set the retrieved document number as 5 to ensure a fair comparison</t>
+          <t>We use BM25 with standard parameters k1 = 1.2 and b = 0.75</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>P07:pdf:35; P07:pdf:10; P07:pdf:2</t>
+          <t>P09:pdf:30; P09:pdf:31; P09:pdf:28</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3831,21 +3428,25 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Retriever dan LLM sesuai pdf:10, pdf:35; chunk 2048/overlap 256 di pdf:17.</t>
+          <t>BM25 (k1=1.2, b=0.75), E5-Mistral, mE5, GTE, segmentasi paragraf, dan keempat generator ada di chunk 30-31.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>P09:pdf:30; P09:pdf:31</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Menggunakan retriever seperti BGE-M3, BGE-large-zh, GTE-Qwen2-1.5b, dan jina-zh; generator LLM termasuk Qwen2.5-72B, Deepseek-v2-chat, Yi15-34B, Llama3.1-70B; chunking panjang 2048 dengan overlap 256.</t>
+          <t>Sistem RAG menggunakan retriever BM25 (k1=1.2, b=0.75) serta model dense seperti e5-mistral-7b-instruct, mE5, dan GTE; dokumen dipotong menjadi paragraf, dan generator meliputi GPT-o1, Claude-3.7-Sonnet, Qwen-QWQ-32B, serta DeepSeek-R1-Distill.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>P07</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3855,22 +3456,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>quote_verified</t>
+          <t>quote_not_found</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Evaluasi menggunakan metrik multi-aspek seperti ACC, HAL (hallucination), NAC (numerical accuracy), Rouge-L, serta MRR dan MAP untuk retriever.</t>
+          <t>Evaluasi mencakup Context Recall (RAGAS), Precision, serta metrik Response Correctness dan Faithfulness pada berbagai tugas keuangan.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hallucination (HAL). It assesses hallucinations in generated responses</t>
+          <t>Context Recall metric from RAGAS</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>P07:pdf:29; P07:pdf:33; P07:pdf:26</t>
+          <t>P09:pdf:40; P09:pdf:2; P09:pdf:42</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3880,21 +3481,25 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Metrik ada di tabel pdf:29 dan definisi pdf:29, pdf:33.</t>
+          <t>Context Recall RAGAS dan precision (chunk 31, 35), Response Correctness dan Faithfulness (chunk 40, 42). Quote tidak ditemukan verbatim tetapi isinya didukung.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>P09:pdf:31; P09:pdf:35; P09:pdf:40; P09:pdf:42</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Evaluasi menggunakan metrik multi-aspek seperti ACC, HAL (hallucination), NAC (numerical accuracy), Rouge-L, serta MRR dan MAP untuk retriever.</t>
+          <t>Evaluasi mencakup Context Recall (RAGAS), Precision, serta metrik Response Correctness dan Faithfulness pada berbagai tugas keuangan.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>P07</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3909,17 +3514,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>GTE-Qwen2-1.5B menunjukkan performa retrieval terbaik pada sebagian besar metrik; performa RAG bervariasi antar topik dan tugas, dan masih terdapat ruang besar untuk perbaikan.</t>
+          <t>Model e5-mistral mencapai Context Recall tertinggi dengan total 25.95, sementara Claude-3.7-Sonnet memperoleh skor Faithfulness tertinggi pada sebagian besar tugas.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>there remains a large space to improve RAG systems in vertical domains</t>
+          <t>E5-mistral demonstrates the best performance in all categories in terms of Context Recall</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>P07:pdf:36; P07:pdf:10; P07:pdf:2</t>
+          <t>P09:pdf:35; P09:pdf:39; P09:pdf:42</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3929,21 +3534,25 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sesuai pdf:36, pdf:10.</t>
+          <t>E5-Mistral total Context Recall 25.95 (Tabel 4) dan Claude-3.7-Sonnet konsisten tertinggi pada Faithfulness ada di chunk 35 dan 42.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>P09:pdf:35; P09:pdf:42</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>GTE-Qwen2-1.5B menunjukkan performa retrieval terbaik pada sebagian besar metrik; performa RAG bervariasi antar topik dan tugas, dan masih terdapat ruang besar untuk perbaikan.</t>
+          <t>Model e5-mistral mencapai Context Recall tertinggi dengan total 25.95, sementara Claude-3.7-Sonnet memperoleh skor Faithfulness tertinggi pada sebagian besar tugas.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>P07</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3953,22 +3562,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>quote_not_found</t>
+          <t>quote_verified</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Keterbatasan meliputi kegagalan retriever pada topik ekor panjang, kegagalan generator dalam perhitungan keuangan, serta distribusi data yang masih terbatas dan berpotensi bias.</t>
+          <t>Penulis mencatat bahwa dataset sebelumnya tidak mencerminkan ambiguitas kueri dan proses retrieval yang penting untuk QA keuangan.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>the distribution remains somewhat limited</t>
+          <t>prior datasets ... failed to reflect the importance of ambiguous queries and the retrieval process</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>P07:pdf:47; P07:pdf:38; P07:pdf:14</t>
+          <t>P09:pdf:6; P09:pdf:29; P09:pdf:2</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3978,29 +3587,29 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Kegagalan retriever long-tail dan perhitungan keuangan (pdf:47) adalah failure case model yang dievaluasi, bukan keterbatasan paper; keterbatasan distribusi data dan risiko bias didukung pdf:50 (bukan pdf:14).</t>
+          <t>Kutipan menggambarkan kelemahan dataset terdahulu (motivasi), bukan keterbatasan FINDER/paper ini; salah atribusi.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Penulis mengakui distribusi korpus masih terbatas karena kendala aksesibilitas dan lisensi terbuka sumber data, sehingga berisiko memasukkan bias yang dapat memengaruhi generalisasi temuan benchmark.</t>
+          <t>Chunk tidak memuat bagian keterbatasan eksplisit paper. Penulis menyatakan tidak ada satu model pun yang unggul di semua tugas penalaran keuangan, analisis dilakukan pada subset representatif 10% dataset, dan pekerjaan lanjutan disarankan untuk mengintegrasikan sumber dokumen keuangan yang lebih beragam serta model yang memperbaiki kueri secara dinamis.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>P07:pdf:50</t>
+          <t>P09:pdf:47; P09:pdf:28</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Penulis mengakui distribusi korpus masih terbatas karena kendala aksesibilitas dan lisensi terbuka sumber data, sehingga berisiko memasukkan bias yang dapat memengaruhi generalisasi temuan benchmark.</t>
+          <t>Chunk tidak memuat bagian keterbatasan eksplisit paper. Penulis menyatakan tidak ada satu model pun yang unggul di semua tugas penalaran keuangan, analisis dilakukan pada subset representatif 10% dataset, dan pekerjaan lanjutan disarankan untuk mengintegrasikan sumber dokumen keuangan yang lebih beragam serta model yang memperbaiki kueri secara dinamis.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>P07</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4015,17 +3624,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Inferensi: Paper tidak mengevaluasi kemampuan abstention atau faithfulness pada dokumen produk perbankan berbahasa Indonesia, sehingga tidak mencakup fokus riset yang diinginkan.</t>
+          <t>Inferensi: Meskipun FINDER mengevaluasi faithfulness, tidak ada pembahasan tentang kemampuan sistem menolak menjawab (abstention) ketika konteks tidak mengandung jawaban, dan dataset berbahasa Inggris tidak mencakup dokumen perbankan Indonesia.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>current RAG benchmarks often suffer from narrow scenarios and limited evaluation dimensions</t>
+          <t>Even state-of-the-art Large Language Models (LLMs) struggle with factual correctness in financial queries without proper context</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>P07:pdf:0</t>
+          <t>P09:pdf:4; P09:pdf:6</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -4035,21 +3644,25 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Inferensi tidak bertentangan; catatan: paper memiliki metrik HAL (pdf:29) yang dekat dengan faithfulness, tetapi pada korpus Mandarin.</t>
+          <t>Premis bahwa FINDER mengevaluasi faithfulness didukung (chunk 42); tidak ada chunk yang membahas abstention. Klaim bahasa Inggris berada setelah 'Inferensi:' dan tidak bertentangan dengan chunk, tetapi tidak dinyatakan eksplisit.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>P09:pdf:42; P09:pdf:4</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Inferensi: Paper tidak mengevaluasi kemampuan abstention atau faithfulness pada dokumen produk perbankan berbahasa Indonesia, sehingga tidak mencakup fokus riset yang diinginkan.</t>
+          <t>Inferensi: Meskipun FINDER mengevaluasi faithfulness, tidak ada pembahasan tentang kemampuan sistem menolak menjawab (abstention) ketika konteks tidak mengandung jawaban, dan dataset berbahasa Inggris tidak mencakup dokumen perbankan Indonesia.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>P08</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4059,22 +3672,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>quote_verified</t>
+          <t>quote_fuzzy</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Paper mengidentifikasi kebutuhan akan kerangka evaluasi yang memperhitungkan heterogenitas dokumen, tipe pertanyaan, dan kedalaman penalaran dalam sistem RAG pada domain keuangan.</t>
+          <t>Paper ini mengusulkan kerangka Bayesian RAG untuk mengukur ketidakpastian pada proses retrieval demi menjamin jawaban keuangan yang dapat diandalkan.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>These insights emphasize the importance of benchmarks that capture real-world document heterogeneity while enabling multifaceted evaluations aligned with the strengths and trade-offs of both models and methodologies.</t>
+          <t>Bayesian RAG: uncertainty-aware retrieval for reliable financial question answering</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>P08:pdf:12; P08:pdf:8; P08:pdf:11</t>
+          <t>P11:pdf:0</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4084,21 +3697,25 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Sesuai pdf:12.</t>
+          <t>Judul dan chunk 23 mendukung Bayesian RAG untuk kuantifikasi ketidakpastian retrieval demi QA keuangan yang andal.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>P11:pdf:0; P11:pdf:23</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Paper mengidentifikasi kebutuhan akan kerangka evaluasi yang memperhitungkan heterogenitas dokumen, tipe pertanyaan, dan kedalaman penalaran dalam sistem RAG pada domain keuangan.</t>
+          <t>Paper ini mengusulkan kerangka Bayesian RAG untuk mengukur ketidakpastian pada proses retrieval demi menjamin jawaban keuangan yang dapat diandalkan.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>P08</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4113,41 +3730,49 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Benchmark FinDoc-RAG mencakup 600+ pasangan QA dari 46 dokumen keuangan berbahasa Inggris, termasuk deskripsi produk, panduan investasi, kebijakan hukum, dan materi pemasaran dengan konten numerik padat.</t>
+          <t>Fokus pada analisis dokumen keuangan regulasi berbahasa Inggris, menggunakan dataset seperti FinanceBench dengan dokumen laporan tahunan perusahaan.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>FinDoc-RAG comprises 600+ QA pairs extracted from 46 documents in English from UBS AG and other UBS entities.</t>
+          <t>Financial document analysis demands precise factual extraction from complex regulatory filings</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>P08:pdf:5; P08:pdf:7; P08:pdf:4</t>
+          <t>P11:pdf:16; P11:pdf:2</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Sesuai pdf:4, pdf:12 (dokumen UBS).</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+          <t>Laporan keuangan terstruktur berbahasa Inggris didukung chunk 113, tetapi FinanceBench di chunk 16 adalah dataset yang dipakai FinSage/FinRAG (related work), bukan dataset paper ini; salah atribusi.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Eksperimen dilakukan secara eksklusif pada laporan keuangan terstruktur berbahasa Inggris, dengan dataset AAPL 10-K, MSFT 10-K, dan FinSage. Ground truth disusun oleh dua pakar keuangan (Cohen's kappa = 0,87).</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>P11:pdf:113; P11:pdf:52; P11:pdf:50</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Benchmark FinDoc-RAG mencakup 600+ pasangan QA dari 46 dokumen keuangan berbahasa Inggris, termasuk deskripsi produk, panduan investasi, kebijakan hukum, dan materi pemasaran dengan konten numerik padat.</t>
+          <t>Eksperimen dilakukan secara eksklusif pada laporan keuangan terstruktur berbahasa Inggris, dengan dataset AAPL 10-K, MSFT 10-K, dan FinSage. Ground truth disusun oleh dua pakar keuangan (Cohen's kappa = 0,87).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>P08</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4157,22 +3782,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>quote_verified</t>
+          <t>quote_fuzzy</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Arsitektur yang dievaluasi meliputi Vector-RAG berbasis indeks vektor dense, tanpa fine-tuning, dengan konfigurasi default serta alur lengkap retrieval-to-answer tanpa intervensi manusia.</t>
+          <t>Menggunakan pipeline lima tahap dengan embedding dense, retrieval semantik via FAISS, dan Monte Carlo dropout (n=10) untuk mengkuantifikasi ketidakpastian pada tahap retrieval.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Vector-based (Vector-RAG) ... using cosine as the similarity metric.</t>
+          <t>Traditional RAG systems use deterministic embeddings that cannot quantify retrieval confidence</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>P08:pdf:50; P08:pdf:27; P08:pdf:25</t>
+          <t>P11:pdf:30; P11:pdf:23; P11:pdf:80</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -4182,21 +3807,25 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Vector-RAG, zero-shot tanpa fine-tuning, default config, end-to-end didukung pdf:25-27; arsitektur lain (graph, RAPTOR, KG) tidak disebut tetapi tidak salah.</t>
+          <t>Pipeline lima tahap, dense embedding, retrieval semantik dengan FAISS, dan Monte Carlo dropout n=10 ada di chunk 30, 23, 80, 50.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>P11:pdf:30; P11:pdf:23; P11:pdf:80; P11:pdf:50</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Arsitektur yang dievaluasi meliputi Vector-RAG berbasis indeks vektor dense, tanpa fine-tuning, dengan konfigurasi default serta alur lengkap retrieval-to-answer tanpa intervensi manusia.</t>
+          <t>Menggunakan pipeline lima tahap dengan embedding dense, retrieval semantik via FAISS, dan Monte Carlo dropout (n=10) untuk mengkuantifikasi ketidakpastian pada tahap retrieval.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>P08</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4211,17 +3840,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Evaluasi mencakup akurasi rata-rata, LLMLogScore (L3Score) berbasis log-likelihood, serta penilaian biner CORRECT/INCORRECT oleh LLM judge pada tiga run independen.</t>
+          <t>Dievaluasi dengan metrik faithfulness, hallucination rate, akurasi, AUC, ECE, serta Precision@3, Recall@5, dan MRR; dibandingkan dengan baseline BM25, DPR, dan ColBERT.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>We computed accuracy as the mean proportion of CORRECT responses per question ... adopt the LLMLogScore (L3Score) metric.</t>
+          <t>Bayesian RAG reduces hallucination by 27.8% (from 0.18 to 0.13) and improves faithfulness by 6.1% (from 0.82 to 0.87)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>P08:pdf:22; P08:pdf:36; P08:pdf:35</t>
+          <t>P11:pdf:76; P11:pdf:75; P11:pdf:77</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4231,21 +3860,25 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Sesuai pdf:35, pdf:36.</t>
+          <t>Faithfulness, hallucination rate, akurasi, AUC, ECE, P@3, R@5, MRR, dan baseline BM25/DPR/ColBERT ada di chunk 50, 52, 75-77 (GPT-5 zero-shot juga baseline).</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>P11:pdf:50; P11:pdf:52; P11:pdf:75; P11:pdf:76; P11:pdf:77</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Evaluasi mencakup akurasi rata-rata, LLMLogScore (L3Score) berbasis log-likelihood, serta penilaian biner CORRECT/INCORRECT oleh LLM judge pada tiga run independen.</t>
+          <t>Dievaluasi dengan metrik faithfulness, hallucination rate, akurasi, AUC, ECE, serta Precision@3, Recall@5, dan MRR; dibandingkan dengan baseline BM25, DPR, dan ColBERT.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>P08</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4255,46 +3888,54 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>quote_not_found</t>
+          <t>quote_verified</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Sistem teratas mencapai akurasi 0.91 pada ekstraksi faktual, namun hanya 0.44 pada sintesis multi-dokumen; RAPTOR memperoleh skor rata-rata 0.66 (σ=0.17), sementara GFM-RAG mencapai akurasi sempurna 1.00 pada level L3.</t>
+          <t>Bayesian RAG meningkatkan faithfulness menjadi 0.87, menurunkan hallucination menjadi 0.13, dan memberikan kenaikan akurasi 25% dengan overhead latency 33 ms.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>leading systems achieve 0.91 accuracy in factual extraction but only 0.44 on multi-document synthesis tasks.</t>
+          <t>achieving 25% performance gains with 33 ms latency overhead</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>P08:pdf:12; P08:pdf:26; P08:pdf:40</t>
+          <t>P11:pdf:52; P11:pdf:102; P11:pdf:50</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>0,91/0,44 (pdf:5), RAPTOR 0,66 sigma=0,17 dan GFM-RAG 1,00 pada L3 (pdf:40) cocok.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+          <t>Faithfulness 0.87 dan hallucination 0.13 benar. Angka 25% di chunk 102 adalah 'performance gains' pada zona balanced (lambda=0.3), bukan secara khusus kenaikan akurasi; akurasi yang dilaporkan adalah 93.1%.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Bayesian RAG (lambda=0,3) menaikkan faithfulness dari 0,82 menjadi 0,87 dan menurunkan hallucination dari 0,18 menjadi 0,13 dibanding ColBERT. Bayesian RAG + GPT mencapai akurasi 93,1% dengan AUC 0,961 dan ECE 0,034, dan pada zona balanced memberi peningkatan kinerja 25% dengan overhead latency 33 ms.</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>P11:pdf:76; P11:pdf:75; P11:pdf:102</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Sistem teratas mencapai akurasi 0.91 pada ekstraksi faktual, namun hanya 0.44 pada sintesis multi-dokumen; RAPTOR memperoleh skor rata-rata 0.66 (σ=0.17), sementara GFM-RAG mencapai akurasi sempurna 1.00 pada level L3.</t>
+          <t>Bayesian RAG (lambda=0,3) menaikkan faithfulness dari 0,82 menjadi 0,87 dan menurunkan hallucination dari 0,18 menjadi 0,13 dibanding ColBERT. Bayesian RAG + GPT mencapai akurasi 93,1% dengan AUC 0,961 dan ECE 0,034, dan pada zona balanced memberi peningkatan kinerja 25% dengan overhead latency 33 ms.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>P08</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4304,54 +3945,50 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>quote_verified</t>
+          <t>quote_not_found</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Penulis mencatat keterbatasan LLM dalam penalaran kuantitatif, cakupan dokumen yang hanya sebagian dari keseluruhan domain, serta metrik yang belum sepenuhnya menangkap semua dimensi kualitas jawaban.</t>
+          <t>Kerangka hanya diuji pada dokumen berbahasa Inggris, tidak memodelkan ketidakpastian aleatorik, dan hasilnya terbatas pada konteks regulasi keuangan.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Current LLMs show limitations in quantitative reasoning and cross-document synthesis essential for financial applications.</t>
+          <t>Single language and format: Experiments are conducted exclusively on English-language structured financial reports</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>P08:pdf:2; P08:pdf:49; P08:pdf:6</t>
+          <t>P11:pdf:116; P11:pdf:2; P11:pdf:50</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>SUPPORTED</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>'Keterbatasan LLM dalam penalaran kuantitatif' (pdf:2) adalah konteks umum di pendahuluan, bukan keterbatasan paper; cakupan dokumen dan metrik didukung pdf:49; keterbatasan pertanyaan auto-generated terlewat.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Penulis mencatat pertanyaan yang dibangkitkan otomatis kadang kurang mendalam dibanding pertanyaan buatan manusia, koleksi dokumen hanya sebagian dari ragam dokumen keuangan, dan pendekatan evaluasi multifaset mungkin belum menangkap semua dimensi kualitas jawaban.</t>
-        </is>
-      </c>
+          <t>Isi didukung chunk 113 (hanya bahasa Inggris) dan 111 (tidak memodelkan aleatoric uncertainty; generalisasi ke domain lain perlu validasi). Catatan: CITED (116, 2, 50) tidak memuat klaim ini; sumber yang benar 111 dan 113.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>P08:pdf:49</t>
+          <t>P11:pdf:111; P11:pdf:113</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Penulis mencatat pertanyaan yang dibangkitkan otomatis kadang kurang mendalam dibanding pertanyaan buatan manusia, koleksi dokumen hanya sebagian dari ragam dokumen keuangan, dan pendekatan evaluasi multifaset mungkin belum menangkap semua dimensi kualitas jawaban.</t>
+          <t>Kerangka hanya diuji pada dokumen berbahasa Inggris, tidak memodelkan ketidakpastian aleatorik, dan hasilnya terbatas pada konteks regulasi keuangan.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>P08</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4361,22 +3998,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>quote_verified</t>
+          <t>quote_fuzzy</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Tidak ada evaluasi faithfulness atau mekanisme abstention pada dokumen perbankan berbahasa Indonesia; fokus benchmark hanya pada dokumen berbahasa Inggris dan tidak menguji penolakan jawaban ketika konteks tidak memadai. Inferensi: Penelitian selanjutnya perlu menambah bahasa Indonesia serta mengukur kemampuan sistem menolak menjawab pertanyaan di luar cakupan konteks.</t>
+          <t>Inferensi: Meskipun paper menilai faithfulness, tidak ada evaluasi abstention atau analisis pada dokumen perbankan berbahasa Indonesia, sehingga belum menjawab fokus penelitian yang menuntut pengukuran abstention pada produk perbankan Indonesia.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Finally, our metrics comparison reveals challenges in accurately measuring RAG system performance, suggesting that even our multifaceted evaluation approach may not capture all dimensions of answer quality relevant to financial domain experts.</t>
+          <t>Single language and format: Experiments are conducted exclusively on English-language structured financial reports</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>P08:pdf:49; P08:pdf:14; P08:pdf:35</t>
+          <t>P11:pdf:113; P11:pdf:2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4386,21 +4023,25 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Premis bahasa Inggris didukung pdf:4/pdf:12; ketiadaan faithfulness/abstention konsisten dengan metrik di pdf:35-36 (argumen dari ketiadaan).</t>
+          <t>Faithfulness dinilai (chunk 76); tidak ada chunk tentang abstention; eksperimen hanya bahasa Inggris (chunk 113).</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>P11:pdf:76; P11:pdf:113</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Tidak ada evaluasi faithfulness atau mekanisme abstention pada dokumen perbankan berbahasa Indonesia; fokus benchmark hanya pada dokumen berbahasa Inggris dan tidak menguji penolakan jawaban ketika konteks tidak memadai. Inferensi: Penelitian selanjutnya perlu menambah bahasa Indonesia serta mengukur kemampuan sistem menolak menjawab pertanyaan di luar cakupan konteks.</t>
+          <t>Inferensi: Meskipun paper menilai faithfulness, tidak ada evaluasi abstention atau analisis pada dokumen perbankan berbahasa Indonesia, sehingga belum menjawab fokus penelitian yang menuntut pengukuran abstention pada produk perbankan Indonesia.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4415,17 +4056,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Paper ini mengidentifikasi kebutuhan akan evaluasi sistem Retrieval-Augmented Generation (RAG) yang akurat dalam domain keuangan, mengingat kesalahan kecil dapat berdampak besar pada investasi dan kepatuhan.</t>
+          <t>Paper memperkenalkan HybridRAG, pendekatan gabungan VectorRAG dan GraphRAG untuk meningkatkan analisis dokumen keuangan.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Accurate information retrieval is critical in financial Question-Answering (QA)</t>
+          <t>To the best of our knowledge the present work is the first work that proposes a RAG approach that is hybrid of both VectorRAG and GraphRAG and demonstrates its potential of more effective analysis and utilization of financial documents</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>P09:pdf:2</t>
+          <t>P12:pdf:12</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4435,25 +4076,25 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Kebutuhan presisi QA keuangan dan dampak kesalahan pada investasi, risk management, compliance ada di chunk 2.</t>
+          <t>Klaim HybridRAG gabungan VectorRAG dan GraphRAG untuk dokumen keuangan ada di chunk 12.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>P09:pdf:2</t>
+          <t>P12:pdf:12</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Paper ini mengidentifikasi kebutuhan akan evaluasi sistem Retrieval-Augmented Generation (RAG) yang akurat dalam domain keuangan, mengingat kesalahan kecil dapat berdampak besar pada investasi dan kepatuhan.</t>
+          <t>Paper memperkenalkan HybridRAG, pendekatan gabungan VectorRAG dan GraphRAG untuk meningkatkan analisis dokumen keuangan.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4468,49 +4109,45 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Dataset FINDER mencakup dokumen keuangan seperti artikel berita, filing, dan basis pengetahuan, berfokus pada bahasa Inggris dan tidak menyebutkan dokumen perbankan Indonesia.</t>
+          <t>Menggunakan dokumen keuangan perusahaan, khususnya transkrip earnings call, dengan entitas seperti metrik keuangan, eksekutif, dan peristiwa korporasi.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>retrieving relevant documents (e.g., news articles, filings, and knowledge bases)</t>
+          <t>Our methodology builds upon the concept of RAG ... leveraging both the power of large language models and the efficiency of semantic search.</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>P09:pdf:12; P09:pdf:10; P09:pdf:3</t>
+          <t>P12:pdf:45; P12:pdf:41; P12:pdf:33</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>SUPPORTED</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Daftar 'artikel berita, filing, basis pengetahuan' di chunk 12 menjelaskan apa yang diambil RAG secara umum, bukan isi FINDER; klaim berbahasa Inggris tidak dinyatakan di chunk.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>FINDER dibangun dari kueri pencarian nyata para profesional keuangan untuk menangkap ambiguitas dan ketergantungan konteks kueri keuangan. Kueri dikelompokkan per kategori (mis. Accounting 8,61%, Company Overview 18,95%, Financials 17,36%), dengan 15,48% kueri membutuhkan penalaran kuantitatif; korpus retrieval berasal dari dokumen HTML mentah yang dipecah per paragraf.</t>
-        </is>
-      </c>
+          <t>Transkrip earnings call dan jenis entitas (metrik keuangan, eksekutif, peristiwa korporasi) ada di chunk 41 dan 46.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>P09:pdf:6; P09:pdf:25; P09:pdf:30</t>
+          <t>P12:pdf:41; P12:pdf:46; P12:pdf:12</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>FINDER dibangun dari kueri pencarian nyata para profesional keuangan untuk menangkap ambiguitas dan ketergantungan konteks kueri keuangan. Kueri dikelompokkan per kategori (mis. Accounting 8,61%, Company Overview 18,95%, Financials 17,36%), dengan 15,48% kueri membutuhkan penalaran kuantitatif; korpus retrieval berasal dari dokumen HTML mentah yang dipecah per paragraf.</t>
+          <t>Menggunakan dokumen keuangan perusahaan, khususnya transkrip earnings call, dengan entitas seperti metrik keuangan, eksekutif, dan peristiwa korporasi.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4520,22 +4157,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>quote_verified</t>
+          <t>quote_fuzzy</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Sistem RAG menggunakan retriever BM25 (k1=1.2, b=0.75) serta model dense seperti e5-mistral-7b-instruct, mE5, dan GTE; dokumen dipotong menjadi paragraf, dan generator meliputi GPT-o1, Claude-3.7-Sonnet, Qwen-QWQ-32B, serta DeepSeek-R1-Distill.</t>
+          <t>HybridRAG memakai model embedding text-embedding-ada-002, chunk size 1024, Pinecone vector DB, serta integrasi GraphRAG untuk pencarian semantik dan pemrosesan KG.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>We use BM25 with standard parameters k1 = 1.2 and b = 0.75</t>
+          <t>We employ OpenAI’s text-embedding-ada-002 model to transform textual data ... Chunk Size 1024</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>P09:pdf:30; P09:pdf:31; P09:pdf:28</t>
+          <t>P12:pdf:46; P12:pdf:6; P12:pdf:15</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4545,25 +4182,25 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>BM25 (k1=1.2, b=0.75), E5-Mistral, mE5, GTE, segmentasi paragraf, dan keempat generator ada di chunk 30-31.</t>
+          <t>text-embedding-ada-002, chunk size 1024, Pinecone, dan integrasi GraphRAG ada di chunk 45-46, 12.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>P09:pdf:30; P09:pdf:31</t>
+          <t>P12:pdf:46; P12:pdf:45; P12:pdf:12</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Sistem RAG menggunakan retriever BM25 (k1=1.2, b=0.75) serta model dense seperti e5-mistral-7b-instruct, mE5, dan GTE; dokumen dipotong menjadi paragraf, dan generator meliputi GPT-o1, Claude-3.7-Sonnet, Qwen-QWQ-32B, serta DeepSeek-R1-Distill.</t>
+          <t>HybridRAG memakai model embedding text-embedding-ada-002, chunk size 1024, Pinecone vector DB, serta integrasi GraphRAG untuk pencarian semantik dan pemrosesan KG.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4573,22 +4210,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>quote_not_found</t>
+          <t>quote_verified</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Evaluasi mencakup Context Recall (RAGAS), Precision, serta metrik Response Correctness dan Faithfulness pada berbagai tugas keuangan.</t>
+          <t>Dievaluasi dengan metrik faithfulness, answer relevancy, dan context relevance untuk menilai kualitas jawaban dan relevansi konteks.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Context Recall metric from RAGAS</t>
+          <t>These metrics ... focus on faithfulness, answer relevance, and context relevance</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>P09:pdf:40; P09:pdf:2; P09:pdf:42</t>
+          <t>P12:pdf:27; P12:pdf:26; P12:pdf:33</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4598,25 +4235,25 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Context Recall RAGAS dan precision (chunk 31, 35), Response Correctness dan Faithfulness (chunk 40, 42). Quote tidak ditemukan verbatim tetapi isinya didukung.</t>
+          <t>Faithfulness, answer relevance, context relevance ada di chunk 27; context precision/recall juga dilaporkan (chunk 33, 56).</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>P09:pdf:31; P09:pdf:35; P09:pdf:40; P09:pdf:42</t>
+          <t>P12:pdf:27; P12:pdf:33; P12:pdf:56</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Evaluasi mencakup Context Recall (RAGAS), Precision, serta metrik Response Correctness dan Faithfulness pada berbagai tugas keuangan.</t>
+          <t>Dievaluasi dengan metrik faithfulness, answer relevancy, dan context relevance untuk menilai kualitas jawaban dan relevansi konteks.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4631,17 +4268,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Model e5-mistral mencapai Context Recall tertinggi dengan total 25.95, sementara Claude-3.7-Sonnet memperoleh skor Faithfulness tertinggi pada sebagian besar tugas.</t>
+          <t>HybridRAG mencapai skor faithfulness 0.96, answer relevancy 0.96, dan context recall 1.0, menunjukkan kinerja seimbang dibandingkan VectorRAG dan GraphRAG.</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>E5-mistral demonstrates the best performance in all categories in terms of Context Recall</t>
+          <t>HybridRAG ... excels in faithfulness, answer relevancy, and context recall</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>P09:pdf:35; P09:pdf:39; P09:pdf:42</t>
+          <t>P12:pdf:56; P12:pdf:60; P12:pdf:62</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4651,25 +4288,25 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>E5-Mistral total Context Recall 25.95 (Tabel 4) dan Claude-3.7-Sonnet konsisten tertinggi pada Faithfulness ada di chunk 35 dan 42.</t>
+          <t>Faithfulness 0.96, answer relevancy 0.96, context recall 1 untuk HybridRAG ada di chunk 56 dan 62.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>P09:pdf:35; P09:pdf:42</t>
+          <t>P12:pdf:56; P12:pdf:62</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Model e5-mistral mencapai Context Recall tertinggi dengan total 25.95, sementara Claude-3.7-Sonnet memperoleh skor Faithfulness tertinggi pada sebagian besar tugas.</t>
+          <t>HybridRAG mencapai skor faithfulness 0.96, answer relevancy 0.96, dan context recall 1.0, menunjukkan kinerja seimbang dibandingkan VectorRAG dan GraphRAG.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4684,17 +4321,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Penulis mencatat bahwa dataset sebelumnya tidak mencerminkan ambiguitas kueri dan proses retrieval yang penting untuk QA keuangan.</t>
+          <t>GraphRAG kurang baik pada tugas Q&amp;A abstraktif dan ketika entitas tidak eksplisit; tantangan pada konteks panjang dan kualitas konteks yang tidak konsisten.</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>prior datasets ... failed to reflect the importance of ambiguous queries and the retrieval process</t>
+          <t>GraphRAG generally underperforms in abstractive Q&amp;A tasks or when there is not explicit entity mentioned in the question</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>P09:pdf:6; P09:pdf:29; P09:pdf:2</t>
+          <t>P12:pdf:11; P12:pdf:12; P12:pdf:60</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4704,29 +4341,29 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Kutipan menggambarkan kelemahan dataset terdahulu (motivasi), bukan keterbatasan FINDER/paper ini; salah atribusi.</t>
+          <t>Kelemahan GraphRAG pada abstractive Q&amp;A dan tantangan konteks panjang/kualitas konteks adalah motivasi tentang metode yang ada, bukan keterbatasan HybridRAG. Keterbatasan hasil yang tampak di chunk (context precision HybridRAG terendah, 0.79) tidak disebut.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Chunk tidak memuat bagian keterbatasan eksplisit paper. Penulis menyatakan tidak ada satu model pun yang unggul di semua tugas penalaran keuangan, analisis dilakukan pada subset representatif 10% dataset, dan pekerjaan lanjutan disarankan untuk mengintegrasikan sumber dokumen keuangan yang lebih beragam serta model yang memperbaiki kueri secara dinamis.</t>
+          <t>Chunk tidak memuat bagian keterbatasan eksplisit. Hasil menunjukkan trade-off: context precision HybridRAG (0,79) lebih rendah dari VectorRAG (0,84) dan GraphRAG (0,96). Penulis juga mencatat bahwa komponen GraphRAG lemah pada Q&amp;A abstraktif atau saat pertanyaan tidak menyebut entitas secara eksplisit.</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>P09:pdf:47; P09:pdf:28</t>
+          <t>P12:pdf:56; P12:pdf:62; P12:pdf:11</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Chunk tidak memuat bagian keterbatasan eksplisit paper. Penulis menyatakan tidak ada satu model pun yang unggul di semua tugas penalaran keuangan, analisis dilakukan pada subset representatif 10% dataset, dan pekerjaan lanjutan disarankan untuk mengintegrasikan sumber dokumen keuangan yang lebih beragam serta model yang memperbaiki kueri secara dinamis.</t>
+          <t>Chunk tidak memuat bagian keterbatasan eksplisit. Hasil menunjukkan trade-off: context precision HybridRAG (0,79) lebih rendah dari VectorRAG (0,84) dan GraphRAG (0,96). Penulis juga mencatat bahwa komponen GraphRAG lemah pada Q&amp;A abstraktif atau saat pertanyaan tidak menyebut entitas secara eksplisit.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4741,17 +4378,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Inferensi: Meskipun FINDER mengevaluasi faithfulness, tidak ada pembahasan tentang kemampuan sistem menolak menjawab (abstention) ketika konteks tidak mengandung jawaban, dan dataset berbahasa Inggris tidak mencakup dokumen perbankan Indonesia.</t>
+          <t>Penelitian ini tidak mengevaluasi abstention (menolak menjawab bila konteks tidak memadai) dan tidak menggunakan dokumen berbahasa Indonesia; Inferensi: sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada dokumen perbankan Indonesia.</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Even state-of-the-art Large Language Models (LLMs) struggle with factual correctness in financial queries without proper context</t>
+          <t>These metrics ... focus on faithfulness, answer relevance, and context relevance</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>P09:pdf:4; P09:pdf:6</t>
+          <t>P12:pdf:27</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4761,25 +4398,25 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Premis bahwa FINDER mengevaluasi faithfulness didukung (chunk 42); tidak ada chunk yang membahas abstention. Klaim bahasa Inggris berada setelah 'Inferensi:' dan tidak bertentangan dengan chunk, tetapi tidak dinyatakan eksplisit.</t>
+          <t>Metrik yang dipakai (chunk 27, 56) tidak mencakup abstention. Bahasa dokumen tidak dinyatakan di chunk, tetapi klaim tidak bertentangan.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
-          <t>P09:pdf:42; P09:pdf:4</t>
+          <t>P12:pdf:27; P12:pdf:56</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Inferensi: Meskipun FINDER mengevaluasi faithfulness, tidak ada pembahasan tentang kemampuan sistem menolak menjawab (abstention) ketika konteks tidak mengandung jawaban, dan dataset berbahasa Inggris tidak mencakup dokumen perbankan Indonesia.</t>
+          <t>Penelitian ini tidak mengevaluasi abstention (menolak menjawab bila konteks tidak memadai) dan tidak menggunakan dokumen berbahasa Indonesia; Inferensi: sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada dokumen perbankan Indonesia.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4794,17 +4431,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Membangun benchmark FinRAGBench-V dan baseline RGenCite untuk RAG multimodal dengan visual citation.</t>
+          <t>Paper ini mengidentifikasi kebutuhan akan sistem QA yang dapat secara efisien mengambil dan menganalisis informasi kepatuhan dari dokumen keuangan.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Our task contains two main phases: the construction of FinRAGBench-V, and the implementation of the RGenCite baseline</t>
+          <t>demand for a Question Answering (QA) system capable of efficiently retrieving and analyzing compliance-related information</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>P10:pdf:17; P10:pdf:13</t>
+          <t>P13:pdf:5</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4814,25 +4451,25 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Dua fase (konstruksi FinRAGBench-V dan baseline RGenCite) serta visual citation ada di chunk 17 dan 13.</t>
+          <t>Kebutuhan sistem QA untuk informasi kepatuhan dari financial filings ada di chunk 5.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t>P10:pdf:17; P10:pdf:13</t>
+          <t>P13:pdf:5</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Membangun benchmark FinRAGBench-V dan baseline RGenCite untuk RAG multimodal dengan visual citation.</t>
+          <t>Paper ini mengidentifikasi kebutuhan akan sistem QA yang dapat secara efisien mengambil dan menganalisis informasi kepatuhan dari dokumen keuangan.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4847,17 +4484,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Domain keuangan, mencakup laporan riset, laporan keuangan, prospektus, makalah akademik, dan majalah finansial; data dikumpulkan dari Qianzhan.com, FinGLM, BSCF, jurnal, dan Financial Times; ukuran besar dan berbahasa Inggris serta Mandarin.</t>
+          <t>Sistem diuji pada FinanceBench, dataset QA keuangan berbahasa Inggris dengan 150 pertanyaan tentang perusahaan publik, serta dokumen filing SEC.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Financial statements of companies and banks collected from the FinGLM dataset and official company and bank websites</t>
+          <t>FinanceBench ... includes 150 open-source questions relating to traded companies</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>P10:pdf:22; P10:pdf:13; P10:pdf:15</t>
+          <t>P13:pdf:42; P13:abstract:0; P13:pdf:0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4867,29 +4504,29 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Lima jenis sumber didukung chunk 22; data Mandarin dan Inggris didukung chunk 45-46; klaim 'ukuran besar' tidak didukung karena tidak ada angka ukuran di chunk.</t>
+          <t>FinanceBench 150 pertanyaan dan SEC filings didukung (chunk 42, 48), tetapi bahasa Inggris tidak dinyatakan dan dataset kedua (Company dataset) tidak disebut.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Domain keuangan dengan korpus halaman dari laporan riset (mis. Qianzhan.com), laporan keuangan perusahaan dan bank (FinGLM serta situs resmi), prospektus (BSCF), makalah akademik (Journal of Financial dan CNKI), dan majalah keuangan seperti Financial Times. Benchmark memiliki subset berbahasa Mandarin dan Inggris.</t>
+          <t>Evaluasi memakai dua dataset beranotasi manual: FinanceBench (150 pertanyaan open-source tentang perusahaan publik) dan Company dataset. Dokumen sumbernya adalah SEC filings.</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>P10:pdf:22; P10:pdf:45; P10:pdf:46</t>
+          <t>P13:pdf:42; P13:pdf:48; P13:pdf:61</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Domain keuangan dengan korpus halaman dari laporan riset (mis. Qianzhan.com), laporan keuangan perusahaan dan bank (FinGLM serta situs resmi), prospektus (BSCF), makalah akademik (Journal of Financial dan CNKI), dan majalah keuangan seperti Financial Times. Benchmark memiliki subset berbahasa Mandarin dan Inggris.</t>
+          <t>Evaluasi memakai dua dataset beranotasi manual: FinanceBench (150 pertanyaan open-source tentang perusahaan publik) dan Company dataset. Dokumen sumbernya adalah SEC filings.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4904,17 +4541,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Menggunakan retriever teksual (Jina-ColBERT-V2, Multilingual-E5-large) dan multimodal (ColQwen2, GME-Qwen2-VL-2B, DSE-QWen2-2b-MRL-V1); chunking pada level halaman; generator memakai MLLM seperti GPT-4o, GPT-4V, Gemini-2.0-Flash, Qwen2.5-VL-72B-Instruct; visual citation diintegrasikan pada tahap generasi.</t>
+          <t>FinSage menggunakan pipeline Multi-path Retrieval dengan BM25 sparse retriever, BGE-M3 dense retriever, metadata retriever, dan HyDE retriever, serta modul chunk bundling.</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>we develop the baseline system RGenCite, which covers both retrieval and generation, with visual citation seamlessly integrated into the generation stage</t>
+          <t>BM25 Sparse Retriever: ... BGE-M3 Dense Retriever: ... Metadata Retriever: ... HyDE Retriever</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>P10:pdf:10; P10:pdf:46; P10:pdf:30</t>
+          <t>P13:pdf:32; P13:pdf:29; P13:pdf:35</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4924,25 +4561,25 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Retriever tekstual dan multimodal, korpus berbasis halaman, generator MLLM, serta visual citation pada tahap generasi ada di chunk 10, 11, 17, 30, 46.</t>
+          <t>Empat komponen MPR dan Chunk Bundling Module ada di chunk 32 dan 35.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t>P10:pdf:11; P10:pdf:17; P10:pdf:30; P10:pdf:46</t>
+          <t>P13:pdf:32; P13:pdf:35; P13:pdf:29</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Menggunakan retriever teksual (Jina-ColBERT-V2, Multilingual-E5-large) dan multimodal (ColQwen2, GME-Qwen2-VL-2B, DSE-QWen2-2b-MRL-V1); chunking pada level halaman; generator memakai MLLM seperti GPT-4o, GPT-4V, Gemini-2.0-Flash, Qwen2.5-VL-72B-Instruct; visual citation diintegrasikan pada tahap generasi.</t>
+          <t>FinSage menggunakan pipeline Multi-path Retrieval dengan BM25 sparse retriever, BGE-M3 dense retriever, metadata retriever, dan HyDE retriever, serta modul chunk bundling.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4957,17 +4594,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Evaluasi mencakup retrieval (nDCG@k, Recall@k, MRR@k), akurasi jawaban (ROUGE, ACC), serta kualitas visual citation (precision, recall pada level halaman dan blok, IoU, dan penilaian manusia 0-5).</t>
+          <t>Evaluasi mencakup recall, precision, F1, serta metrik Normalized Recall dan penilaian faktual menggunakan GPT-4o serta evaluasi manual.</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>we adopt several evaluation metrics, namely nDCG@k (for k = 5, 10), Recall@k (for k = 5, 10), and MRR@k (k = 10)</t>
+          <t>adjusted Normalized Recall metric</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>P10:pdf:34; P10:pdf:50; P10:pdf:49</t>
+          <t>P13:pdf:53; P13:pdf:54; P13:pdf:50</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4977,25 +4614,25 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>nDCG@k, Recall@k, MRR@10, ROUGE, Acc (GPT-4o), precision/recall citation page dan block, IoU, rating manusia 0-5 ada di chunk 10, 34, 49, 50.</t>
+          <t>Recall/Precision/F1, Normalized Recall, GPT-4o CorrectnessEvaluator, dan evaluasi manual ada di chunk 50, 53, 54.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>P10:pdf:34; P10:pdf:10; P10:pdf:49; P10:pdf:50</t>
+          <t>P13:pdf:50; P13:pdf:53; P13:pdf:54</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Evaluasi mencakup retrieval (nDCG@k, Recall@k, MRR@k), akurasi jawaban (ROUGE, ACC), serta kualitas visual citation (precision, recall pada level halaman dan blok, IoU, dan penilaian manusia 0-5).</t>
+          <t>Evaluasi mencakup recall, precision, F1, serta metrik Normalized Recall dan penilaian faktual menggunakan GPT-4o serta evaluasi manual.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5010,17 +4647,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Multimodal retriever mencapai recall@10 hingga 90.13 % (Chinese) dan 85.86 % (English), jauh di atas retriever teksual (42.71 %/36.36 %). Visual citation dengan image-cropping memperoleh korelasi Pearson 65.06 dengan IoU dan 68.01 dengan penilaian manusia.</t>
+          <t>FinSage mencapai akurasi LLM 49.66% pada FinanceBench, meningkatkan recall sekitar 15% dan precision dari 5.6% menjadi 18.5% dibanding re-ranker umum.</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ColQwen2 achieves a recall@10 of 90.13 (Chinese) and 85.86 (English)</t>
+          <t>FinSage achieves a significant improvement ... LLM accuracy of 49.66%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>P10:pdf:45; P10:pdf:51; P10:pdf:32</t>
+          <t>P13:pdf:61; P13:pdf:59; P13:pdf:62</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5030,25 +4667,25 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>ColQwen2 recall@10 90.13/85.86 vs BGE-M3 42.71/36.36, Pearson 65.06 (IoU) dan 68.01 (human) ada di chunk 45, 50, 51.</t>
+          <t>Akurasi LLM 49.66%, recall +~15%, precision 5.6%-&gt;18.5% (Document Re-ranker vs re-ranker umum) ada di chunk 59, 61-62.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>P10:pdf:45; P10:pdf:51</t>
+          <t>P13:pdf:59; P13:pdf:61; P13:pdf:62</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Multimodal retriever mencapai recall@10 hingga 90.13 % (Chinese) dan 85.86 % (English), jauh di atas retriever teksual (42.71 %/36.36 %). Visual citation dengan image-cropping memperoleh korelasi Pearson 65.06 dengan IoU dan 68.01 dengan penilaian manusia.</t>
+          <t>FinSage mencapai akurasi LLM 49.66% pada FinanceBench, meningkatkan recall sekitar 15% dan precision dari 5.6% menjadi 18.5% dibanding re-ranker umum.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5063,17 +4700,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Tidak melatih model khusus multimodal RAG untuk domain keuangan; benchmark berbahasa Inggris dan Mandarin, tidak mencakup bahasa Indonesia; belum mengatasi kebutuhan abstention.</t>
+          <t>Penulis mencatat kesulitan integrasi RAG ke dalam tugas kepatuhan keuangan karena keterbatasan domain dan tantangan multi-modalitas.</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>we did not train a dedicated model for multimodal RAG in the financial domain</t>
+          <t>integration into financial compliance tasks can be difficult due to inherent domain-related limitations</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>P10:pdf:52; P10:pdf:15; P10:pdf:4</t>
+          <t>P13:pdf:5; P13:pdf:15; P13:pdf:9</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5083,29 +4720,29 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Penulis hanya menyatakan satu keterbatasan (tidak melatih model khusus). Ketiadaan bahasa Indonesia dan abstention adalah inferensi reviewer, bukan keterbatasan yang dinyatakan; abstention tidak dibahas di chunk.</t>
+          <t>Kutipan menjelaskan tantangan umum integrasi RAG ke kepatuhan keuangan (motivasi), bukan keterbatasan FinSage; chunk tidak memuat bagian keterbatasan penulis.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Penulis menyatakan keterbatasan utama bahwa mereka tidak melatih model khusus untuk RAG multimodal di domain keuangan, dan pekerjaan lanjutan perlu mengembangkan model yang disesuaikan dengan tantangan RAG multimodal keuangan.</t>
+          <t>Chunk tidak memuat keterbatasan eksplisit dari penulis. Dari hasil, waktu respons FinSage paling lambat (rata-rata 19,34 detik) dibanding GraphRAG (16,90 detik) dan LightRAG (12,16 detik).</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>P10:pdf:52</t>
+          <t>P13:pdf:61</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Penulis menyatakan keterbatasan utama bahwa mereka tidak melatih model khusus untuk RAG multimodal di domain keuangan, dan pekerjaan lanjutan perlu mengembangkan model yang disesuaikan dengan tantangan RAG multimodal keuangan.</t>
+          <t>Chunk tidak memuat keterbatasan eksplisit dari penulis. Dari hasil, waktu respons FinSage paling lambat (rata-rata 19,34 detik) dibanding GraphRAG (16,90 detik) dan LightRAG (12,16 detik).</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5120,17 +4757,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Penulis menyatakan belum melatih model khusus untuk RAG multimodal keuangan dan benchmark berbahasa Inggris/Mandarin, sehingga tidak mencakup dokumen perbankan berbahasa Indonesia atau evaluasi abstention. Inferensi: Karena tidak ada evaluasi faithfulness atau mekanisme abstention pada dokumen perbankan berbahasa Indonesia, gap penelitian tetap ada.</t>
+          <t>Inferensi: Meskipun FinSage meningkatkan akurasi dan recall pada dokumen filing berbahasa Inggris, tidak mengevaluasi faithfulness atau kemampuan abstention pada dokumen produk perbankan berbahasa Indonesia, sehingga masih ada celah untuk menilai keandalan sistem RAG dalam konteks bahasa dan domain tersebut.</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>we did not train a dedicated model for multimodal RAG in the financial domain</t>
+          <t>financial filings combine unstructured text ... conventional text-centric retrieval architectures fail to process cohesively</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>P10:pdf:52; P10:pdf:15</t>
+          <t>P13:pdf:5; P13:pdf:6</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5140,29 +4777,29 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Premis bahasa Mandarin/Inggris didukung (chunk 45), tetapi itu bukan pernyataan penulis sebagai keterbatasan. Inferensi 'tidak ada evaluasi faithfulness' bertentangan dengan chunk: evaluasi visual citation menilai apakah halaman/blok yang dikutip mendukung jawaban (chunk 32) dan Acc menilai konsistensi jawaban (chunk 34).</t>
+          <t>Klaim 'tidak mengevaluasi faithfulness' bertentangan dengan Tabel 4 (Faithful Evaluation Score: FinSage rata-rata 4.31, pass 82.67%). Bahasa Inggris tidak dinyatakan di chunk.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Penulis menyatakan belum melatih model khusus RAG multimodal keuangan; benchmark hanya mencakup data berbahasa Mandarin dan Inggris. Inferensi: paper sudah mengevaluasi grounding melalui precision/recall visual citation, tetapi tidak membahas abstention dan tidak mencakup dokumen perbankan berbahasa Indonesia.</t>
+          <t>Inferensi: FinSage sudah dievaluasi untuk akurasi, recall, dan skor faithfulness (rata-rata 4,31; pass 82,67%) pada SEC filings, tetapi tidak membahas abstention dan tidak mencakup dokumen produk perbankan berbahasa Indonesia.</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>P10:pdf:52; P10:pdf:45; P10:pdf:32; P10:pdf:10</t>
+          <t>P13:pdf:61; P13:pdf:62; P13:pdf:48</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Penulis menyatakan belum melatih model khusus RAG multimodal keuangan; benchmark hanya mencakup data berbahasa Mandarin dan Inggris. Inferensi: paper sudah mengevaluasi grounding melalui precision/recall visual citation, tetapi tidak membahas abstention dan tidak mencakup dokumen perbankan berbahasa Indonesia.</t>
+          <t>Inferensi: FinSage sudah dievaluasi untuk akurasi, recall, dan skor faithfulness (rata-rata 4,31; pass 82,67%) pada SEC filings, tetapi tidak membahas abstention dan tidak mencakup dokumen produk perbankan berbahasa Indonesia.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5172,22 +4809,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>quote_fuzzy</t>
+          <t>quote_verified</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Paper ini mengusulkan kerangka Bayesian RAG untuk mengukur ketidakpastian pada proses retrieval demi menjamin jawaban keuangan yang dapat diandalkan.</t>
+          <t>Paper mengatasi kebutuhan sistem RAG yang dapat memberikan jawaban yang akurat dan menolak menjawab bila konteks tidak cukup, untuk mengurangi risiko regulasi di perbankan.</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bayesian RAG: uncertainty-aware retrieval for reliable financial question answering</t>
+          <t>model must explicitly refrain from answering rather than fabricate an answer</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>P11:pdf:0</t>
+          <t>P15:pdf:4</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5197,25 +4834,25 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Judul dan chunk 23 mendukung Bayesian RAG untuk kuantifikasi ketidakpastian retrieval demi QA keuangan yang andal.</t>
+          <t>Kebutuhan menolak menjawab saat informasi tidak tersedia demi menghindari risiko regulasi di perbankan ada di chunk 4 dan 0.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
-          <t>P11:pdf:0; P11:pdf:23</t>
+          <t>P15:pdf:4; P15:pdf:0</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Paper ini mengusulkan kerangka Bayesian RAG untuk mengukur ketidakpastian pada proses retrieval demi menjamin jawaban keuangan yang dapat diandalkan.</t>
+          <t>Paper mengatasi kebutuhan sistem RAG yang dapat memberikan jawaban yang akurat dan menolak menjawab bila konteks tidak cukup, untuk mengurangi risiko regulasi di perbankan.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5225,54 +4862,46 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>quote_fuzzy</t>
+          <t>not_stated</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Fokus pada analisis dokumen keuangan regulasi berbahasa Inggris, menggunakan dataset seperti FinanceBench dengan dokumen laporan tahunan perusahaan.</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Financial document analysis demands precise factual extraction from complex regulatory filings</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>P11:pdf:16; P11:pdf:2</t>
-        </is>
-      </c>
+          <t>tidak disebut</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>NOT_STATED_WRONG</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Laporan keuangan terstruktur berbahasa Inggris didukung chunk 113, tetapi FinanceBench di chunk 16 adalah dataset yang dipakai FinSage/FinRAG (related work), bukan dataset paper ini; salah atribusi.</t>
+          <t>Chunk memuat data: korpus pelatihan 98.648 sampel (143M token), evaluasi internal perbankan, FinanceBench 150 pertanyaan SEC, dan 3.297 kueri produksi dari credit union AS.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Eksperimen dilakukan secara eksklusif pada laporan keuangan terstruktur berbahasa Inggris, dengan dataset AAPL 10-K, MSFT 10-K, dan FinSage. Ground truth disusun oleh dua pakar keuangan (Cohen's kappa = 0,87).</t>
+          <t>Domain perbankan. Korpus pelatihan berisi 98.648 sampel (143M token) dari data open-source dan proprietary; evaluasi memakai data QA perbankan dengan lima passage per contoh dan label answerability, FinanceBench (150 pertanyaan atas SEC filings), serta 3.297 kueri pengguna dari sebuah credit union besar di AS.</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>P11:pdf:113; P11:pdf:52; P11:pdf:50</t>
+          <t>P15:pdf:12; P15:pdf:30; P15:pdf:38; P15:pdf:35</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Eksperimen dilakukan secara eksklusif pada laporan keuangan terstruktur berbahasa Inggris, dengan dataset AAPL 10-K, MSFT 10-K, dan FinSage. Ground truth disusun oleh dua pakar keuangan (Cohen's kappa = 0,87).</t>
+          <t>Domain perbankan. Korpus pelatihan berisi 98.648 sampel (143M token) dari data open-source dan proprietary; evaluasi memakai data QA perbankan dengan lima passage per contoh dan label answerability, FinanceBench (150 pertanyaan atas SEC filings), serta 3.297 kueri pengguna dari sebuah credit union besar di AS.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5282,22 +4911,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>quote_fuzzy</t>
+          <t>quote_verified</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Menggunakan pipeline lima tahap dengan embedding dense, retrieval semantik via FAISS, dan Monte Carlo dropout (n=10) untuk mengkuantifikasi ketidakpastian pada tahap retrieval.</t>
+          <t>Menggunakan model dasar Gemma 3 12B-IT dengan jendela konteks 128K, pipeline kurasi data multi-tahap, dan strategi pelatihan dua-tahap termasuk contoh tidak dapat dijawab untuk kalibrasi abstensi.</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Traditional RAG systems use deterministic embeddings that cannot quantify retrieval confidence</t>
+          <t>we select Gemma 3 12B-IT ... 128K context window</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>P11:pdf:30; P11:pdf:23; P11:pdf:80</t>
+          <t>P15:pdf:11; P15:pdf:12; P15:pdf:1</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5307,25 +4936,25 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Pipeline lima tahap, dense embedding, retrieval semantik dengan FAISS, dan Monte Carlo dropout n=10 ada di chunk 30, 23, 80, 50.</t>
+          <t>Gemma 3 12B-IT dengan 128K context, pipeline kurasi multi-tahap, curriculum dua tahap, dan 22% contoh unanswerable ada di chunk 11, 12, 23, 26, 1.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
-          <t>P11:pdf:30; P11:pdf:23; P11:pdf:80; P11:pdf:50</t>
+          <t>P15:pdf:11; P15:pdf:12; P15:pdf:26; P15:pdf:1</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Menggunakan pipeline lima tahap dengan embedding dense, retrieval semantik via FAISS, dan Monte Carlo dropout (n=10) untuk mengkuantifikasi ketidakpastian pada tahap retrieval.</t>
+          <t>Menggunakan model dasar Gemma 3 12B-IT dengan jendela konteks 128K, pipeline kurasi data multi-tahap, dan strategi pelatihan dua-tahap termasuk contoh tidak dapat dijawab untuk kalibrasi abstensi.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5340,17 +4969,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Dievaluasi dengan metrik faithfulness, hallucination rate, akurasi, AUC, ECE, serta Precision@3, Recall@5, dan MRR; dibandingkan dengan baseline BM25, DPR, dan ColBERT.</t>
+          <t>Dievaluasi dengan tiga dimensi: kualitas jawaban (QA F1), kalibrasi penolakan (refusal rate), dan latency, serta metrik kualitas kutipan (Citation Quality).</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bayesian RAG reduces hallucination by 27.8% (from 0.18 to 0.13) and improves faithfulness by 6.1% (from 0.82 to 0.87)</t>
+          <t>We evaluate along three dimensions: answer quality, refusal calibration, and latency</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>P11:pdf:76; P11:pdf:75; P11:pdf:77</t>
+          <t>P15:pdf:31; P15:pdf:5; P15:pdf:45</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5360,25 +4989,25 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Faithfulness, hallucination rate, akurasi, AUC, ECE, P@3, R@5, MRR, dan baseline BM25/DPR/ColBERT ada di chunk 50, 52, 75-77 (GPT-5 zero-shot juga baseline).</t>
+          <t>Tiga dimensi, QA F1, refusal rate, Citation Quality (dan JudgeLM) ada di chunk 31.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>P11:pdf:50; P11:pdf:52; P11:pdf:75; P11:pdf:76; P11:pdf:77</t>
+          <t>P15:pdf:31</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Dievaluasi dengan metrik faithfulness, hallucination rate, akurasi, AUC, ECE, serta Precision@3, Recall@5, dan MRR; dibandingkan dengan baseline BM25, DPR, dan ColBERT.</t>
+          <t>Dievaluasi dengan tiga dimensi: kualitas jawaban (QA F1), kalibrasi penolakan (refusal rate), dan latency, serta metrik kualitas kutipan (Citation Quality).</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5393,17 +5022,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Bayesian RAG meningkatkan faithfulness menjadi 0.87, menurunkan hallucination menjadi 0.13, dan memberikan kenaikan akurasi 25% dengan overhead latency 33 ms.</t>
+          <t>FinRAG-12B meningkatkan resolution rate sebesar 7.1 poin persentase, mencapai F1 0.284 pada FinanceBench dengan tingkat kutipan 97.3%, serta menurunkan tingkat penolakan yang tidak tepat.</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>achieving 25% performance gains with 33 ms latency overhead</t>
+          <t>FinRAG-12B improves the resolution rate by 7.1 percentage points</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>P11:pdf:52; P11:pdf:102; P11:pdf:50</t>
+          <t>P15:pdf:38; P15:pdf:40; P15:pdf:34</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5413,29 +5042,29 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Faithfulness 0.87 dan hallucination 0.13 benar. Angka 25% di chunk 102 adalah 'performance gains' pada zona balanced (lambda=0.3), bukan secara khusus kenaikan akurasi; akurasi yang dilaporkan adalah 93.1%.</t>
+          <t>Resolution rate +7.1 pp, F1 0.284, citation rate 97.3% benar. Klaim 'menurunkan penolakan tidak tepat' ambigu: dibanding base model, rate 'I don't know' justru naik dari 4.3% ke 12%; penurunan over-refusal hanya relatif terhadap GPT-4.1 (20.2%).</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Bayesian RAG (lambda=0,3) menaikkan faithfulness dari 0,82 menjadi 0,87 dan menurunkan hallucination dari 0,18 menjadi 0,13 dibanding ColBERT. Bayesian RAG + GPT mencapai akurasi 93,1% dengan AUC 0,961 dan ECE 0,034, dan pada zona balanced memberi peningkatan kinerja 25% dengan overhead latency 33 ms.</t>
+          <t>FinRAG-12B menaikkan resolution rate produksi sebesar 7,1 poin persentase dan mencapai F1 tertinggi di FinanceBench (0,284; citation rate 97,3%) di atas base model (0,249) dan GPT-4.1 (0,238). Rate 'I don't know' 12% lebih aman daripada base model (4,3%) dan menghindari over-refusal GPT-4.1 (20,2%).</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>P11:pdf:76; P11:pdf:75; P11:pdf:102</t>
+          <t>P15:pdf:38; P15:pdf:34; P15:pdf:1</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Bayesian RAG (lambda=0,3) menaikkan faithfulness dari 0,82 menjadi 0,87 dan menurunkan hallucination dari 0,18 menjadi 0,13 dibanding ColBERT. Bayesian RAG + GPT mencapai akurasi 93,1% dengan AUC 0,961 dan ECE 0,034, dan pada zona balanced memberi peningkatan kinerja 25% dengan overhead latency 33 ms.</t>
+          <t>FinRAG-12B menaikkan resolution rate produksi sebesar 7,1 poin persentase dan mencapai F1 tertinggi di FinanceBench (0,284; citation rate 97,3%) di atas base model (0,249) dan GPT-4.1 (0,238). Rate 'I don't know' 12% lebih aman daripada base model (4,3%) dan menghindari over-refusal GPT-4.1 (20,2%).</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5445,22 +5074,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>quote_not_found</t>
+          <t>quote_verified</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Kerangka hanya diuji pada dokumen berbahasa Inggris, tidak memodelkan ketidakpastian aleatorik, dan hasilnya terbatas pada konteks regulasi keuangan.</t>
+          <t>Rasio contoh negatif yang tidak optimal dapat menyebabkan respons tidak berdasar atau over-refusal; evaluasi penolakan tidak sepenuhnya menangkap ungkapan penolakan yang bersifat hedged atau parsial.</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Single language and format: Experiments are conducted exclusively on English-language structured financial reports</t>
+          <t>An insufficient proportion of negative samples causes the model to default to its sycophantic prior</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>P11:pdf:116; P11:pdf:2; P11:pdf:50</t>
+          <t>P15:pdf:26; P15:pdf:35; P15:pdf:38</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5470,25 +5099,25 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Isi didukung chunk 113 (hanya bahasa Inggris) dan 111 (tidak memodelkan aleatoric uncertainty; generalisasi ke domain lain perlu validasi). Catatan: CITED (116, 2, 50) tidak memuat klaim ini; sumber yang benar 111 dan 113.</t>
+          <t>Efek rasio contoh negatif didukung chunk 26 (dari bagian metode) dan keterbatasan evaluasi refusal untuk ungkapan hedged dinyatakan di chunk 43.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
-          <t>P11:pdf:111; P11:pdf:113</t>
+          <t>P15:pdf:26; P15:pdf:43</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Kerangka hanya diuji pada dokumen berbahasa Inggris, tidak memodelkan ketidakpastian aleatorik, dan hasilnya terbatas pada konteks regulasi keuangan.</t>
+          <t>Rasio contoh negatif yang tidak optimal dapat menyebabkan respons tidak berdasar atau over-refusal; evaluasi penolakan tidak sepenuhnya menangkap ungkapan penolakan yang bersifat hedged atau parsial.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5498,22 +5127,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>quote_fuzzy</t>
+          <t>quote_verified</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Inferensi: Meskipun paper menilai faithfulness, tidak ada evaluasi abstention atau analisis pada dokumen perbankan berbahasa Indonesia, sehingga belum menjawab fokus penelitian yang menuntut pengukuran abstention pada produk perbankan Indonesia.</t>
+          <t>Inferensi: Meskipun paper menilai faithfulness melalui citation quality dan abstention pada data bahasa Inggris, tidak ada evaluasi pada dokumen produk perbankan berbahasa Indonesia, sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada konteks bahasa Indonesia.</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Single language and format: Experiments are conducted exclusively on English-language structured financial reports</t>
+          <t>our refusal evaluation captures explicit “I don’t know” responses and close variants, but may not fully account for hedged or partial uncertainty expressions</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>P11:pdf:113; P11:pdf:2</t>
+          <t>P15:pdf:43; P15:pdf:46; P15:pdf:30</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5523,25 +5152,25 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Faithfulness dinilai (chunk 76); tidak ada chunk tentang abstention; eksperimen hanya bahasa Inggris (chunk 113).</t>
+          <t>Citation Quality mencakup faithfulness (chunk 31) dan abstention dievaluasi (chunk 1, 31). Bahasa Inggris tidak dinyatakan eksplisit tetapi tidak bertentangan.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
-          <t>P11:pdf:76; P11:pdf:113</t>
+          <t>P15:pdf:31; P15:pdf:1; P15:pdf:43</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Inferensi: Meskipun paper menilai faithfulness, tidak ada evaluasi abstention atau analisis pada dokumen perbankan berbahasa Indonesia, sehingga belum menjawab fokus penelitian yang menuntut pengukuran abstention pada produk perbankan Indonesia.</t>
+          <t>Inferensi: Meskipun paper menilai faithfulness melalui citation quality dan abstention pada data bahasa Inggris, tidak ada evaluasi pada dokumen produk perbankan berbahasa Indonesia, sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada konteks bahasa Indonesia.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5556,45 +5185,49 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Paper memperkenalkan HybridRAG, pendekatan gabungan VectorRAG dan GraphRAG untuk meningkatkan analisis dokumen keuangan.</t>
+          <t>Masalahnya adalah mengevaluasi output LLM pada dokumen keuangan multimodal dengan metrik yang tepat.</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>To the best of our knowledge the present work is the first work that proposes a RAG approach that is hybrid of both VectorRAG and GraphRAG and demonstrates its potential of more effective analysis and utilization of financial documents</t>
+          <t>Evaluating the output of LLM frameworks remains a significant open research area.</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>P12:pdf:12</t>
+          <t>P16:pdf:32</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>UNSUPPORTED</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Klaim HybridRAG gabungan VectorRAG dan GraphRAG untuk dokumen keuangan ada di chunk 12.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>Kutipan berasal dari subbagian strategi evaluasi; masalah utama paper menurut abstrak adalah QA atas dokumen keuangan multimodal yang menyulitkan LLM/RAG, bukan pemilihan metrik evaluasi.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Dokumen keuangan seperti 10-K dan 10-Q panjangnya ratusan halaman dan memadukan teks, tabel, serta gambar, sehingga menjawab pertanyaan butuh penalaran lintas modalitas. Hal ini menyulitkan LLM dan pipeline RAG konvensional karena batas token, hilangnya layout, dan konteks lintas modal yang terfragmentasi; paper mengusulkan MultiFinRAG untuk masalah ini.</t>
+        </is>
+      </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>P12:pdf:12</t>
+          <t>P16:abstract:0; P16:pdf:1</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Paper memperkenalkan HybridRAG, pendekatan gabungan VectorRAG dan GraphRAG untuk meningkatkan analisis dokumen keuangan.</t>
+          <t>Dokumen keuangan seperti 10-K dan 10-Q panjangnya ratusan halaman dan memadukan teks, tabel, serta gambar, sehingga menjawab pertanyaan butuh penalaran lintas modalitas. Hal ini menyulitkan LLM dan pipeline RAG konvensional karena batas token, hilangnya layout, dan konteks lintas modal yang terfragmentasi; paper mengusulkan MultiFinRAG untuk masalah ini.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5609,45 +5242,49 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Menggunakan dokumen keuangan perusahaan, khususnya transkrip earnings call, dengan entitas seperti metrik keuangan, eksekutif, dan peristiwa korporasi.</t>
+          <t>Dataset terdiri dari 300 pertanyaan QA yang dibuat dari dokumen keuangan SEC seperti Form 10-K, 10-Q, 8-K, dan DEF 14A, semuanya berbahasa Inggris.</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Our methodology builds upon the concept of RAG ... leveraging both the power of large language models and the efficiency of semantic search.</t>
+          <t>For our evaluation, we collected financial documents from various companies, including Form 10-Q (Quarterly Report), Form 10-K (Annual Report), Form 8-K with EX-99.1 (Current Report), and DEF 14A (Proxy Statement).</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>P12:pdf:45; P12:pdf:41; P12:pdf:33</t>
+          <t>P16:pdf:25</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Transkrip earnings call dan jenis entitas (metrik keuangan, eksekutif, peristiwa korporasi) ada di chunk 41 dan 46.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>300 pertanyaan dan jenis formulir SEC didukung (chunk 25-26), tetapi klaim 'semuanya berbahasa Inggris' tidak dinyatakan di chunk.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Dataset terdiri dari 300 pertanyaan QA yang disusun manual dari dokumen SEC (Form 10-K, 10-Q, 8-K dengan EX-99.1, dan DEF 14A) yang diunduh dari EDGAR. Pertanyaan dibagi menjadi empat tipe: berbasis teks, gambar, tabel, dan gabungan teks dengan gambar/tabel.</t>
+        </is>
+      </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>P12:pdf:41; P12:pdf:46; P12:pdf:12</t>
+          <t>P16:pdf:25; P16:pdf:26</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Menggunakan dokumen keuangan perusahaan, khususnya transkrip earnings call, dengan entitas seperti metrik keuangan, eksekutif, dan peristiwa korporasi.</t>
+          <t>Dataset terdiri dari 300 pertanyaan QA yang disusun manual dari dokumen SEC (Form 10-K, 10-Q, 8-K dengan EX-99.1, dan DEF 14A) yang diunduh dari EDGAR. Pertanyaan dibagi menjadi empat tipe: berbasis teks, gambar, tabel, dan gabungan teks dengan gambar/tabel.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5657,50 +5294,54 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>quote_fuzzy</t>
+          <t>quote_verified</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>HybridRAG memakai model embedding text-embedding-ada-002, chunk size 1024, Pinecone vector DB, serta integrasi GraphRAG untuk pencarian semantik dan pemrosesan KG.</t>
+          <t>MultiFinRAG menggunakan ekstraksi multimodal, embedding dengan threshold kesamaan modalitas, dan strategi fallback bertingkat dari teks ke tabel/gambar, serta DPR sebagai retriever.</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>We employ OpenAI’s text-embedding-ada-002 model to transform textual data ... Chunk Size 1024</t>
+          <t>These outputs, along with narrative text, are embedded and indexed with modality-aware similarity thresholds for precise retrieval.</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>P12:pdf:46; P12:pdf:6; P12:pdf:15</t>
+          <t>P16:pdf:1</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>text-embedding-ada-002, chunk size 1024, Pinecone, dan integrasi GraphRAG ada di chunk 45-46, 12.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>Ekstraksi multimodal, threshold kesamaan sadar-modalitas, dan tiered fallback didukung; DPR hanya muncul di related work (chunk 8), bukan retriever MultiFinRAG, yang memakai indeks FAISS IVF/PQ.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>MultiFinRAG mengelompokkan gambar tabel dan figur ke batch untuk diproses LLM multimodal open-source terkuantisasi yang menghasilkan JSON terstruktur dan ringkasan teks. Hasilnya bersama teks naratif di-embed dan diindeks (FAISS IVF/PQ) dengan threshold kesamaan sadar-modalitas, lalu strategi tiered fallback naik dari konteks teks ke teks+tabel+gambar bila perlu.</t>
+        </is>
+      </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>P12:pdf:46; P12:pdf:45; P12:pdf:12</t>
+          <t>P16:pdf:1; P16:pdf:34</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>HybridRAG memakai model embedding text-embedding-ada-002, chunk size 1024, Pinecone vector DB, serta integrasi GraphRAG untuk pencarian semantik dan pemrosesan KG.</t>
+          <t>MultiFinRAG mengelompokkan gambar tabel dan figur ke batch untuk diproses LLM multimodal open-source terkuantisasi yang menghasilkan JSON terstruktur dan ringkasan teks. Hasilnya bersama teks naratif di-embed dan diindeks (FAISS IVF/PQ) dengan threshold kesamaan sadar-modalitas, lalu strategi tiered fallback naik dari konteks teks ke teks+tabel+gambar bila perlu.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5710,22 +5351,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>quote_verified</t>
+          <t>quote_fuzzy</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Dievaluasi dengan metrik faithfulness, answer relevancy, dan context relevance untuk menilai kualitas jawaban dan relevansi konteks.</t>
+          <t>Evaluasi dilakukan secara manual karena ukuran dataset, mengukur akurasi akhir QA tanpa metrik presisi-recall terperinci.</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>These metrics ... focus on faithfulness, answer relevance, and context relevance</t>
+          <t>we opt for manual evaluations. This approach ensures more accurate assessments and minimizes the risk of misjudgments.</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>P12:pdf:27; P12:pdf:26; P12:pdf:33</t>
+          <t>P16:pdf:34</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -5735,25 +5376,25 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Faithfulness, answer relevance, context relevance ada di chunk 27; context precision/recall juga dilaporkan (chunk 33, 56).</t>
+          <t>Evaluasi manual karena ukuran dataset dan keterbatasan sumber daya (chunk 34), fokus akurasi QA end-to-end tanpa statistik retrieval (chunk 25).</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
-          <t>P12:pdf:27; P12:pdf:33; P12:pdf:56</t>
+          <t>P16:pdf:34; P16:pdf:25</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Dievaluasi dengan metrik faithfulness, answer relevancy, dan context relevance untuk menilai kualitas jawaban dan relevansi konteks.</t>
+          <t>Evaluasi dilakukan secara manual karena ukuran dataset, mengukur akurasi akhir QA tanpa metrik presisi-recall terperinci.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5768,17 +5409,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>HybridRAG mencapai skor faithfulness 0.96, answer relevancy 0.96, dan context recall 1.0, menunjukkan kinerja seimbang dibandingkan VectorRAG dan GraphRAG.</t>
+          <t>MultiFinRAG mencapai akurasi 90.4% pada pertanyaan berbasis teks, meningkat 15.1 poin persentase dibanding baseline.</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>HybridRAG ... excels in faithfulness, answer relevancy, and context recall</t>
+          <t>accuracy for text-based questions using MultiFinRAG with Gemma 3 is 90.4%, representing an improvement of 15.1% compared to the Baseline framework</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>P12:pdf:56; P12:pdf:60; P12:pdf:62</t>
+          <t>P16:pdf:34</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -5788,25 +5429,25 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Faithfulness 0.96, answer relevancy 0.96, context recall 1 untuk HybridRAG ada di chunk 56 dan 62.</t>
+          <t>Akurasi 90.4% teks-based vs baseline Gemma 3 75.3% (selisih 15.1 poin) ada di chunk 34.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
-          <t>P12:pdf:56; P12:pdf:62</t>
+          <t>P16:pdf:34</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>HybridRAG mencapai skor faithfulness 0.96, answer relevancy 0.96, dan context recall 1.0, menunjukkan kinerja seimbang dibandingkan VectorRAG dan GraphRAG.</t>
+          <t>MultiFinRAG mencapai akurasi 90.4% pada pertanyaan berbasis teks, meningkat 15.1 poin persentase dibanding baseline.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5816,54 +5457,50 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>quote_verified</t>
+          <t>quote_not_found</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>GraphRAG kurang baik pada tugas Q&amp;A abstraktif dan ketika entitas tidak eksplisit; tantangan pada konteks panjang dan kualitas konteks yang tidak konsisten.</t>
+          <t>Penulis menyatakan bahwa metrik retrieval detail tidak dilaporkan dan evaluasi modul masih terbuka untuk studi lanjutan.</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>GraphRAG generally underperforms in abstractive Q&amp;A tasks or when there is not explicit entity mentioned in the question</t>
+          <t>Detailed information-retrieval statistics (precision, recall, etc.) for the retrieval components were collected during development but are omitted here due to space constraints</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>P12:pdf:11; P12:pdf:12; P12:pdf:60</t>
+          <t>P16:pdf:32</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>SUPPORTED</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Kelemahan GraphRAG pada abstractive Q&amp;A dan tantangan konteks panjang/kualitas konteks adalah motivasi tentang metode yang ada, bukan keterbatasan HybridRAG. Keterbatasan hasil yang tampak di chunk (context precision HybridRAG terendah, 0.79) tidak disebut.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>Chunk tidak memuat bagian keterbatasan eksplisit. Hasil menunjukkan trade-off: context precision HybridRAG (0,79) lebih rendah dari VectorRAG (0,84) dan GraphRAG (0,96). Penulis juga mencatat bahwa komponen GraphRAG lemah pada Q&amp;A abstraktif atau saat pertanyaan tidak menyebut entitas secara eksplisit.</t>
-        </is>
-      </c>
+          <t>Statistik retrieval dihilangkan karena keterbatasan ruang (chunk 25) dan evaluasi per modul sebagai pekerjaan lanjutan (chunk 45). Catatan: CITED 32 tidak memuat klaim ini; sumbernya chunk 25 dan 45.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t>P12:pdf:56; P12:pdf:62; P12:pdf:11</t>
+          <t>P16:pdf:25; P16:pdf:45</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Chunk tidak memuat bagian keterbatasan eksplisit. Hasil menunjukkan trade-off: context precision HybridRAG (0,79) lebih rendah dari VectorRAG (0,84) dan GraphRAG (0,96). Penulis juga mencatat bahwa komponen GraphRAG lemah pada Q&amp;A abstraktif atau saat pertanyaan tidak menyebut entitas secara eksplisit.</t>
+          <t>Penulis menyatakan bahwa metrik retrieval detail tidak dilaporkan dan evaluasi modul masih terbuka untuk studi lanjutan.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5878,17 +5515,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Penelitian ini tidak mengevaluasi abstention (menolak menjawab bila konteks tidak memadai) dan tidak menggunakan dokumen berbahasa Indonesia; Inferensi: sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada dokumen perbankan Indonesia.</t>
+          <t>Tidak disebutkan evaluasi faithfulness atau abstention pada dokumen perbankan berbahasa Indonesia. Inferensi: Karena studi hanya menggunakan dokumen SEC berbahasa Inggris dan tidak menguji kemampuan menolak pertanyaan ketika konteks tidak ada, terdapat gap dalam evaluasi faithfulness dan abstention untuk dokumen perbankan Indonesia.</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>These metrics ... focus on faithfulness, answer relevance, and context relevance</t>
+          <t>Questions require both text and image/table are the most challenging, as they require information from both text and images or tables.</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>P12:pdf:27</t>
+          <t>P16:pdf:31</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5898,25 +5535,25 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Metrik yang dipakai (chunk 27, 56) tidak mencakup abstention. Bahasa dokumen tidak dinyatakan di chunk, tetapi klaim tidak bertentangan.</t>
+          <t>Dokumen SEC didukung (chunk 25); tidak ada chunk tentang abstention. Klaim bahasa Inggris tidak eksplisit tetapi tidak bertentangan.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
-          <t>P12:pdf:27; P12:pdf:56</t>
+          <t>P16:pdf:25</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Penelitian ini tidak mengevaluasi abstention (menolak menjawab bila konteks tidak memadai) dan tidak menggunakan dokumen berbahasa Indonesia; Inferensi: sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada dokumen perbankan Indonesia.</t>
+          <t>Tidak disebutkan evaluasi faithfulness atau abstention pada dokumen perbankan berbahasa Indonesia. Inferensi: Karena studi hanya menggunakan dokumen SEC berbahasa Inggris dan tidak menguji kemampuan menolak pertanyaan ketika konteks tidak ada, terdapat gap dalam evaluasi faithfulness dan abstention untuk dokumen perbankan Indonesia.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5931,17 +5568,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Paper ini mengidentifikasi kebutuhan akan sistem QA yang dapat secara efisien mengambil dan menganalisis informasi kepatuhan dari dokumen keuangan.</t>
+          <t>Masalah yang diidentifikasi adalah trade-off antara robustness dan precision pada sistem RAG untuk pertanyaan dokumen keuangan.</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>demand for a Question Answering (QA) system capable of efficiently retrieving and analyzing compliance-related information</t>
+          <t>robustness-precision trade-off</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>P13:pdf:5</t>
+          <t>P17:abstract:0; P17:abstract:1; P17:abstract:2</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5951,25 +5588,25 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Kebutuhan sistem QA untuk informasi kepatuhan dari financial filings ada di chunk 5.</t>
+          <t>Trade-off robustness-precision dinyatakan eksplisit di abstract:0.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
-          <t>P13:pdf:5</t>
+          <t>P17:abstract:0</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Paper ini mengidentifikasi kebutuhan akan sistem QA yang dapat secara efisien mengambil dan menganalisis informasi kepatuhan dari dokumen keuangan.</t>
+          <t>Masalah yang diidentifikasi adalah trade-off antara robustness dan precision pada sistem RAG untuk pertanyaan dokumen keuangan.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5984,17 +5621,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Sistem diuji pada FinanceBench, dataset QA keuangan berbahasa Inggris dengan 150 pertanyaan tentang perusahaan publik, serta dokumen filing SEC.</t>
+          <t>Domain keuangan, menggunakan benchmark FinDER dengan 1.500 kueri pada lima grup; tipe dokumen regulasi, ukuran tidak disebut, bahasa tidak disebut.</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>FinanceBench ... includes 150 open-source questions relating to traded companies</t>
+          <t>FinDER benchmark (1,500 queries across five groups)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>P13:pdf:42; P13:abstract:0; P13:pdf:0</t>
+          <t>P17:abstract:0; P17:abstract:1; P17:abstract:2</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -6004,29 +5641,29 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>FinanceBench 150 pertanyaan dan SEC filings didukung (chunk 42, 48), tetapi bahasa Inggris tidak dinyatakan dan dataset kedua (Company dataset) tidak disebut.</t>
+          <t>Regulatory filings are only an example of a homogeneous corpus in the chunks; the document type of FinDER is not stated.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Evaluasi memakai dua dataset beranotasi manual: FinanceBench (150 pertanyaan open-source tentang perusahaan publik) dan Company dataset. Dokumen sumbernya adalah SEC filings.</t>
+          <t>Domain keuangan dengan benchmark FinDER sebanyak 1.500 kueri dalam lima grup; jenis dokumen, ukuran korpus, dan bahasa tidak disebut.</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>P13:pdf:42; P13:pdf:48; P13:pdf:61</t>
+          <t>P17:abstract:0</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Evaluasi memakai dua dataset beranotasi manual: FinanceBench (150 pertanyaan open-source tentang perusahaan publik) dan Company dataset. Dokumen sumbernya adalah SEC filings.</t>
+          <t>Domain keuangan dengan benchmark FinDER sebanyak 1.500 kueri dalam lima grup; jenis dokumen, ukuran korpus, dan bahasa tidak disebut.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6041,17 +5678,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>FinSage menggunakan pipeline Multi-path Retrieval dengan BM25 sparse retriever, BGE-M3 dense retriever, metadata retriever, dan HyDE retriever, serta modul chunk bundling.</t>
+          <t>Metode menggabungkan Semantic File Routing sebagai filter dokumen dengan retrieval berbasis chunk pada dokumen terfilter melalui arsitektur dua tahap Hybrid Document-Routed Retrieval (HDRR).</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>BM25 Sparse Retriever: ... BGE-M3 Dense Retriever: ... Metadata Retriever: ... HyDE Retriever</t>
+          <t>Hybrid Document-Routed Retrieval (HDRR), a two-stage architecture that uses SFR as a document filter followed by chunk retrieval</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>P13:pdf:32; P13:pdf:29; P13:pdf:35</t>
+          <t>P17:abstract:0; P17:abstract:1; P17:abstract:2</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -6061,25 +5698,25 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Empat komponen MPR dan Chunk Bundling Module ada di chunk 32 dan 35.</t>
+          <t>HDRR dua tahap: SFR sebagai filter dokumen lalu chunk retrieval.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
-          <t>P13:pdf:32; P13:pdf:35; P13:pdf:29</t>
+          <t>P17:abstract:1</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>FinSage menggunakan pipeline Multi-path Retrieval dengan BM25 sparse retriever, BGE-M3 dense retriever, metadata retriever, dan HyDE retriever, serta modul chunk bundling.</t>
+          <t>Metode menggabungkan Semantic File Routing sebagai filter dokumen dengan retrieval berbasis chunk pada dokumen terfilter melalui arsitektur dua tahap Hybrid Document-Routed Retrieval (HDRR).</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6094,17 +5731,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Evaluasi mencakup recall, precision, F1, serta metrik Normalized Recall dan penilaian faktual menggunakan GPT-4o serta evaluasi manual.</t>
+          <t>Evaluasi menggunakan skor rata-rata, tingkat kegagalan, persentase jawaban benar, dan persentase jawaban sempurna, dibandingkan dengan CBR dan SFR sebagai baseline.</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>adjusted Normalized Recall metric</t>
+          <t>average score of 7.54 (25.2% above CBR, 16.9% above SFR)</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>P13:pdf:53; P13:pdf:54; P13:pdf:50</t>
+          <t>P17:abstract:0; P17:abstract:1; P17:abstract:2</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6114,25 +5751,25 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Recall/Precision/F1, Normalized Recall, GPT-4o CorrectnessEvaluator, dan evaluasi manual ada di chunk 50, 53, 54.</t>
+          <t>Metrik average score, failure rate, correctness, perfect-answer rate dan baseline CBR/SFR ada di chunk.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
-          <t>P13:pdf:50; P13:pdf:53; P13:pdf:54</t>
+          <t>P17:abstract:0; P17:abstract:1</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Evaluasi mencakup recall, precision, F1, serta metrik Normalized Recall dan penilaian faktual menggunakan GPT-4o serta evaluasi manual.</t>
+          <t>Evaluasi menggunakan skor rata-rata, tingkat kegagalan, persentase jawaban benar, dan persentase jawaban sempurna, dibandingkan dengan CBR dan SFR sebagai baseline.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6147,17 +5784,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>FinSage mencapai akurasi LLM 49.66% pada FinanceBench, meningkatkan recall sekitar 15% dan precision dari 5.6% menjadi 18.5% dibanding re-ranker umum.</t>
+          <t>HDRR mencapai skor rata-rata 7.54, tingkat kegagalan 6.4%, correctness 67.7% (+18.7 pp), dan perfect-answer rate 20.1% (+6.3 pp).</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>FinSage achieves a significant improvement ... LLM accuracy of 49.66%</t>
+          <t>6.4% failure rate, 67.7% correctness (+18.7 pp over CBR)</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>P13:pdf:61; P13:pdf:59; P13:pdf:62</t>
+          <t>P17:abstract:1; P17:abstract:2</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6167,25 +5804,25 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Akurasi LLM 49.66%, recall +~15%, precision 5.6%-&gt;18.5% (Document Re-ranker vs re-ranker umum) ada di chunk 59, 61-62.</t>
+          <t>Semua angka (7.54, 6.4%, 67.7% +18.7 pp, 20.1% +6.3 pp) cocok dengan abstract:1 (pp relatif terhadap CBR).</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
-          <t>P13:pdf:59; P13:pdf:61; P13:pdf:62</t>
+          <t>P17:abstract:1</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>FinSage mencapai akurasi LLM 49.66% pada FinanceBench, meningkatkan recall sekitar 15% dan precision dari 5.6% menjadi 18.5% dibanding re-ranker umum.</t>
+          <t>HDRR mencapai skor rata-rata 7.54, tingkat kegagalan 6.4%, correctness 67.7% (+18.7 pp), dan perfect-answer rate 20.1% (+6.3 pp).</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6195,54 +5832,38 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>quote_verified</t>
+          <t>not_stated</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Penulis mencatat kesulitan integrasi RAG ke dalam tugas kepatuhan keuangan karena keterbatasan domain dan tantangan multi-modalitas.</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>integration into financial compliance tasks can be difficult due to inherent domain-related limitations</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>P13:pdf:5; P13:pdf:15; P13:pdf:9</t>
-        </is>
-      </c>
+          <t>tidak disebut</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>NOT_STATED_OK</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Kutipan menjelaskan tantangan umum integrasi RAG ke kepatuhan keuangan (motivasi), bukan keterbatasan FinSage; chunk tidak memuat bagian keterbatasan penulis.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>Chunk tidak memuat keterbatasan eksplisit dari penulis. Dari hasil, waktu respons FinSage paling lambat (rata-rata 19,34 detik) dibanding GraphRAG (16,90 detik) dan LightRAG (12,16 detik).</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>P13:pdf:61</t>
-        </is>
-      </c>
+          <t>Chunk tidak memuat keterbatasan.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Chunk tidak memuat keterbatasan eksplisit dari penulis. Dari hasil, waktu respons FinSage paling lambat (rata-rata 19,34 detik) dibanding GraphRAG (16,90 detik) dan LightRAG (12,16 detik).</t>
+          <t>tidak disebut</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6257,3389 +5878,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Inferensi: Meskipun FinSage meningkatkan akurasi dan recall pada dokumen filing berbahasa Inggris, tidak mengevaluasi faithfulness atau kemampuan abstention pada dokumen produk perbankan berbahasa Indonesia, sehingga masih ada celah untuk menilai keandalan sistem RAG dalam konteks bahasa dan domain tersebut.</t>
+          <t>Inferensi: Meskipun HDRR meningkatkan akurasi, studi tidak mengevaluasi faithfulness atau kemampuan abstain pada dokumen perbankan berbahasa Indonesia.</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>financial filings combine unstructured text ... conventional text-centric retrieval architectures fail to process cohesively</t>
+          <t>Hybrid Document-Routed Retrieval (HDRR) ... achieves the best performance on every metric</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>P13:pdf:5; P13:pdf:6</t>
+          <t>P17:abstract:0; P17:abstract:1; P17:abstract:2</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>SUPPORTED</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Klaim 'tidak mengevaluasi faithfulness' bertentangan dengan Tabel 4 (Faithful Evaluation Score: FinSage rata-rata 4.31, pass 82.67%). Bahasa Inggris tidak dinyatakan di chunk.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>Inferensi: FinSage sudah dievaluasi untuk akurasi, recall, dan skor faithfulness (rata-rata 4,31; pass 82,67%) pada SEC filings, tetapi tidak membahas abstention dan tidak mencakup dokumen produk perbankan berbahasa Indonesia.</t>
-        </is>
-      </c>
+          <t>Seluruhnya inferensi; tidak bertentangan dengan chunk.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
-          <t>P13:pdf:61; P13:pdf:62; P13:pdf:48</t>
+          <t>P17:abstract:1</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Inferensi: FinSage sudah dievaluasi untuk akurasi, recall, dan skor faithfulness (rata-rata 4,31; pass 82,67%) pada SEC filings, tetapi tidak membahas abstention dan tidak mencakup dokumen produk perbankan berbahasa Indonesia.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>P14</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Problem</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Paper ini mengatasi masalah mendeteksi hallucination intrinsik pada sistem RAG multi-turn di domain keuangan Korea dengan fokus pada kesetiaan sumber.</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>we focus exclusively on detecting intrinsic hallucinations based on source faithfulness</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>P14:abstract:1; P14:pdf:15</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Deteksi intrinsic hallucination berbasis source faithfulness pada RAG keuangan Korea multi-turn ada di chunk 15, 7, abstract:1.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>P14:pdf:15; P14:pdf:7; P14:abstract:1</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>Paper ini mengatasi masalah mendeteksi hallucination intrinsik pada sistem RAG multi-turn di domain keuangan Korea dengan fokus pada kesetiaan sumber.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>P14</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Domain &amp; Data</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Domainnya adalah keuangan Korea; menggunakan dataset “Korean Financial and Legal Document Machine Reading Comprehension” yang berisi dokumen keuangan dan hukum berbahasa Korea.</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>We use the publicly available “Korean Financial and Legal Document Machine Reading Comprehension” dataset</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>P14:pdf:10; P14:pdf:18</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Nama dataset benar, tetapi korpus difilter hanya ke kategori keuangan; dokumen hukum tidak dipakai.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>Benchmark K-FinHallu dibangun dari dataset publik AI-Hub 'Korean Financial and Legal Document Machine Reading Comprehension' yang difilter ke kategori keuangan. Domainnya antara lain Financial Economics (35,2%), Financial Institution Management (24,1%), dan Consumer Economics (21,4%).</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>P14:pdf:18; P14:pdf:32</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>Benchmark K-FinHallu dibangun dari dataset publik AI-Hub 'Korean Financial and Legal Document Machine Reading Comprehension' yang difilter ke kategori keuangan. Domainnya antara lain Financial Economics (35,2%), Financial Institution Management (24,1%), dan Consumer Economics (21,4%).</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>P14</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>RAG Method</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Pipeline otomatis menghasilkan split pelatihan; model generator 8B di-fine-tune dengan supervisi rasional, menggunakan embedding KURE Korean untuk chunking, dan retriever berbasis dokumen sumber.</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>our construction pipeline can automatically generate a training split, on which a fine-tuned 8B model with rationale supervision</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>P14:pdf:8; P14:pdf:7; P14:pdf:18</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Model 8B yang di-fine-tune adalah detektor hallucination, bukan generator; tidak ada retriever, karena model diberi set dokumen terkontrol. Penggunaan KURE untuk segmentasi passage (maks 1.000 token) benar.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>Pipeline konstruksi otomatis menghasilkan training split, dan model 8B di-fine-tune dengan rationale supervision sebagai detektor hallucination. Passage disegmentasi hingga maksimum 1.000 token dengan model embedding KURE. Alih-alih retriever, model diberi set dokumen terkontrol yang dapat dimanipulasi (mis. passage relevan diganti hard negative).</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>P14:pdf:8; P14:pdf:18; P14:pdf:15</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>Pipeline konstruksi otomatis menghasilkan training split, dan model 8B di-fine-tune dengan rationale supervision sebagai detektor hallucination. Passage disegmentasi hingga maksimum 1.000 token dengan model embedding KURE. Alih-alih retriever, model diberi set dokumen terkontrol yang dapat dimanipulasi (mis. passage relevan diganti hard negative).</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>P14</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Evaluation &amp; Metrics</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Evaluasi menggunakan klasifikasi biner (akurasi, presisi, recall, F1) serta klasifikasi empat kelas yang mencakup kemampuan menolak (refusal) dalam dialog multi-turn.</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Binary classification determines the presence of a hallucination, reporting accuracy, precision, recall, and F1</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>P14:pdf:31; P14:pdf:12</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Klasifikasi biner (accuracy, precision, recall, F1) dan empat kelas termasuk refusal ada di chunk 31.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>P14:pdf:31</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>Evaluasi menggunakan klasifikasi biner (akurasi, presisi, recall, F1) serta klasifikasi empat kelas yang mencakup kemampuan menolak (refusal) dalam dialog multi-turn.</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>P14</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Main Results</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Model tertutup Gemini-2.5-Flash mencapai F1 tertinggi 0.860; abstention tetap menjadi aspek terlemah pada semua model yang diuji.</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Gemini-2.5-Flash achieving the highest F1 of 0.860</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>P14:pdf:35; P14:abstract:1</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Gemini-2.5-Flash F1 0.860 (chunk 35) dan abstention sebagai aspek terlemah (abstract:1).</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>P14:pdf:35; P14:abstract:1</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>Model tertutup Gemini-2.5-Flash mencapai F1 tertinggi 0.860; abstention tetap menjadi aspek terlemah pada semua model yang diuji.</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>P14</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Limitations</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Abstention yang tepat masih paling lemah; temuan terbatas pada bahasa Korea sehingga transferabilitas ke bahasa atau yurisdiksi lain terbatas.</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>justified abstention remains the weakest axis across all evaluated models</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>P14:abstract:1; P14:pdf:32; P14:pdf:46</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Abstention terlemah (abstract:1) dan keterbatasan transfer ke bahasa/yurisdiksi lain (chunk 46) didukung; chunk 46 menyebut khusus temuan terkait terminologi.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>P14:abstract:1; P14:pdf:46</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>Abstention yang tepat masih paling lemah; temuan terbatas pada bahasa Korea sehingga transferabilitas ke bahasa atau yurisdiksi lain terbatas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>P14</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Gap</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Inferensi: Meskipun menyediakan benchmark RAG multi-turn untuk bahasa Korea, penelitian ini tidak mencakup bahasa Indonesia atau dokumen produk perbankan, sehingga belum mengevaluasi faithfulness dan abstention pada konteks Indonesia. Penulis juga mencatat bahwa temuan mereka terbatas pada bahasa Korea, sehingga transferabilitas ke bahasa lain tidak dijamin.</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>the unique nature of the Korean</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>P14:pdf:4; P14:pdf:9; P14:pdf:10</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Fokus Korea didukung (chunk 4, 7, 18); pernyataan transferabilitas terbatas didukung chunk 46, meski di sana dibatasi pada temuan terminologi.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>P14:pdf:4; P14:pdf:7; P14:pdf:46</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>Inferensi: Meskipun menyediakan benchmark RAG multi-turn untuk bahasa Korea, penelitian ini tidak mencakup bahasa Indonesia atau dokumen produk perbankan, sehingga belum mengevaluasi faithfulness dan abstention pada konteks Indonesia. Penulis juga mencatat bahwa temuan mereka terbatas pada bahasa Korea, sehingga transferabilitas ke bahasa lain tidak dijamin.</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>P15</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Problem</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Paper mengatasi kebutuhan sistem RAG yang dapat memberikan jawaban yang akurat dan menolak menjawab bila konteks tidak cukup, untuk mengurangi risiko regulasi di perbankan.</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>model must explicitly refrain from answering rather than fabricate an answer</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>P15:pdf:4</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Kebutuhan menolak menjawab saat informasi tidak tersedia demi menghindari risiko regulasi di perbankan ada di chunk 4 dan 0.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>P15:pdf:4; P15:pdf:0</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>Paper mengatasi kebutuhan sistem RAG yang dapat memberikan jawaban yang akurat dan menolak menjawab bila konteks tidak cukup, untuk mengurangi risiko regulasi di perbankan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>P15</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Domain &amp; Data</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>tidak disebut</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>NOT_STATED_WRONG</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Chunk memuat data: korpus pelatihan 98.648 sampel (143M token), evaluasi internal perbankan, FinanceBench 150 pertanyaan SEC, dan 3.297 kueri produksi dari credit union AS.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>Domain perbankan. Korpus pelatihan berisi 98.648 sampel (143M token) dari data open-source dan proprietary; evaluasi memakai data QA perbankan dengan lima passage per contoh dan label answerability, FinanceBench (150 pertanyaan atas SEC filings), serta 3.297 kueri pengguna dari sebuah credit union besar di AS.</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>P15:pdf:12; P15:pdf:30; P15:pdf:38; P15:pdf:35</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>Domain perbankan. Korpus pelatihan berisi 98.648 sampel (143M token) dari data open-source dan proprietary; evaluasi memakai data QA perbankan dengan lima passage per contoh dan label answerability, FinanceBench (150 pertanyaan atas SEC filings), serta 3.297 kueri pengguna dari sebuah credit union besar di AS.</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>P15</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>RAG Method</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Menggunakan model dasar Gemma 3 12B-IT dengan jendela konteks 128K, pipeline kurasi data multi-tahap, dan strategi pelatihan dua-tahap termasuk contoh tidak dapat dijawab untuk kalibrasi abstensi.</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>we select Gemma 3 12B-IT ... 128K context window</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>P15:pdf:11; P15:pdf:12; P15:pdf:1</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Gemma 3 12B-IT dengan 128K context, pipeline kurasi multi-tahap, curriculum dua tahap, dan 22% contoh unanswerable ada di chunk 11, 12, 23, 26, 1.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>P15:pdf:11; P15:pdf:12; P15:pdf:26; P15:pdf:1</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>Menggunakan model dasar Gemma 3 12B-IT dengan jendela konteks 128K, pipeline kurasi data multi-tahap, dan strategi pelatihan dua-tahap termasuk contoh tidak dapat dijawab untuk kalibrasi abstensi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>P15</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Evaluation &amp; Metrics</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Dievaluasi dengan tiga dimensi: kualitas jawaban (QA F1), kalibrasi penolakan (refusal rate), dan latency, serta metrik kualitas kutipan (Citation Quality).</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>We evaluate along three dimensions: answer quality, refusal calibration, and latency</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>P15:pdf:31; P15:pdf:5; P15:pdf:45</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Tiga dimensi, QA F1, refusal rate, Citation Quality (dan JudgeLM) ada di chunk 31.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>P15:pdf:31</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>Dievaluasi dengan tiga dimensi: kualitas jawaban (QA F1), kalibrasi penolakan (refusal rate), dan latency, serta metrik kualitas kutipan (Citation Quality).</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>P15</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Main Results</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>FinRAG-12B meningkatkan resolution rate sebesar 7.1 poin persentase, mencapai F1 0.284 pada FinanceBench dengan tingkat kutipan 97.3%, serta menurunkan tingkat penolakan yang tidak tepat.</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>FinRAG-12B improves the resolution rate by 7.1 percentage points</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>P15:pdf:38; P15:pdf:40; P15:pdf:34</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Resolution rate +7.1 pp, F1 0.284, citation rate 97.3% benar. Klaim 'menurunkan penolakan tidak tepat' ambigu: dibanding base model, rate 'I don't know' justru naik dari 4.3% ke 12%; penurunan over-refusal hanya relatif terhadap GPT-4.1 (20.2%).</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>FinRAG-12B menaikkan resolution rate produksi sebesar 7,1 poin persentase dan mencapai F1 tertinggi di FinanceBench (0,284; citation rate 97,3%) di atas base model (0,249) dan GPT-4.1 (0,238). Rate 'I don't know' 12% lebih aman daripada base model (4,3%) dan menghindari over-refusal GPT-4.1 (20,2%).</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>P15:pdf:38; P15:pdf:34; P15:pdf:1</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>FinRAG-12B menaikkan resolution rate produksi sebesar 7,1 poin persentase dan mencapai F1 tertinggi di FinanceBench (0,284; citation rate 97,3%) di atas base model (0,249) dan GPT-4.1 (0,238). Rate 'I don't know' 12% lebih aman daripada base model (4,3%) dan menghindari over-refusal GPT-4.1 (20,2%).</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>P15</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Limitations</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Rasio contoh negatif yang tidak optimal dapat menyebabkan respons tidak berdasar atau over-refusal; evaluasi penolakan tidak sepenuhnya menangkap ungkapan penolakan yang bersifat hedged atau parsial.</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>An insufficient proportion of negative samples causes the model to default to its sycophantic prior</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>P15:pdf:26; P15:pdf:35; P15:pdf:38</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Efek rasio contoh negatif didukung chunk 26 (dari bagian metode) dan keterbatasan evaluasi refusal untuk ungkapan hedged dinyatakan di chunk 43.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>P15:pdf:26; P15:pdf:43</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>Rasio contoh negatif yang tidak optimal dapat menyebabkan respons tidak berdasar atau over-refusal; evaluasi penolakan tidak sepenuhnya menangkap ungkapan penolakan yang bersifat hedged atau parsial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>P15</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Gap</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Inferensi: Meskipun paper menilai faithfulness melalui citation quality dan abstention pada data bahasa Inggris, tidak ada evaluasi pada dokumen produk perbankan berbahasa Indonesia, sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada konteks bahasa Indonesia.</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>our refusal evaluation captures explicit “I don’t know” responses and close variants, but may not fully account for hedged or partial uncertainty expressions</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>P15:pdf:43; P15:pdf:46; P15:pdf:30</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Citation Quality mencakup faithfulness (chunk 31) dan abstention dievaluasi (chunk 1, 31). Bahasa Inggris tidak dinyatakan eksplisit tetapi tidak bertentangan.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>P15:pdf:31; P15:pdf:1; P15:pdf:43</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>Inferensi: Meskipun paper menilai faithfulness melalui citation quality dan abstention pada data bahasa Inggris, tidak ada evaluasi pada dokumen produk perbankan berbahasa Indonesia, sehingga belum menjawab fokus penelitian tentang faithfulness dan abstention pada konteks bahasa Indonesia.</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>P16</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Problem</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Masalahnya adalah mengevaluasi output LLM pada dokumen keuangan multimodal dengan metrik yang tepat.</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Evaluating the output of LLM frameworks remains a significant open research area.</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>P16:pdf:32</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>UNSUPPORTED</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Kutipan berasal dari subbagian strategi evaluasi; masalah utama paper menurut abstrak adalah QA atas dokumen keuangan multimodal yang menyulitkan LLM/RAG, bukan pemilihan metrik evaluasi.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>Dokumen keuangan seperti 10-K dan 10-Q panjangnya ratusan halaman dan memadukan teks, tabel, serta gambar, sehingga menjawab pertanyaan butuh penalaran lintas modalitas. Hal ini menyulitkan LLM dan pipeline RAG konvensional karena batas token, hilangnya layout, dan konteks lintas modal yang terfragmentasi; paper mengusulkan MultiFinRAG untuk masalah ini.</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>P16:abstract:0; P16:pdf:1</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>Dokumen keuangan seperti 10-K dan 10-Q panjangnya ratusan halaman dan memadukan teks, tabel, serta gambar, sehingga menjawab pertanyaan butuh penalaran lintas modalitas. Hal ini menyulitkan LLM dan pipeline RAG konvensional karena batas token, hilangnya layout, dan konteks lintas modal yang terfragmentasi; paper mengusulkan MultiFinRAG untuk masalah ini.</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>P16</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Domain &amp; Data</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Dataset terdiri dari 300 pertanyaan QA yang dibuat dari dokumen keuangan SEC seperti Form 10-K, 10-Q, 8-K, dan DEF 14A, semuanya berbahasa Inggris.</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>For our evaluation, we collected financial documents from various companies, including Form 10-Q (Quarterly Report), Form 10-K (Annual Report), Form 8-K with EX-99.1 (Current Report), and DEF 14A (Proxy Statement).</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>P16:pdf:25</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>300 pertanyaan dan jenis formulir SEC didukung (chunk 25-26), tetapi klaim 'semuanya berbahasa Inggris' tidak dinyatakan di chunk.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>Dataset terdiri dari 300 pertanyaan QA yang disusun manual dari dokumen SEC (Form 10-K, 10-Q, 8-K dengan EX-99.1, dan DEF 14A) yang diunduh dari EDGAR. Pertanyaan dibagi menjadi empat tipe: berbasis teks, gambar, tabel, dan gabungan teks dengan gambar/tabel.</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>P16:pdf:25; P16:pdf:26</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>Dataset terdiri dari 300 pertanyaan QA yang disusun manual dari dokumen SEC (Form 10-K, 10-Q, 8-K dengan EX-99.1, dan DEF 14A) yang diunduh dari EDGAR. Pertanyaan dibagi menjadi empat tipe: berbasis teks, gambar, tabel, dan gabungan teks dengan gambar/tabel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>P16</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>RAG Method</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>MultiFinRAG menggunakan ekstraksi multimodal, embedding dengan threshold kesamaan modalitas, dan strategi fallback bertingkat dari teks ke tabel/gambar, serta DPR sebagai retriever.</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>These outputs, along with narrative text, are embedded and indexed with modality-aware similarity thresholds for precise retrieval.</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>P16:pdf:1</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Ekstraksi multimodal, threshold kesamaan sadar-modalitas, dan tiered fallback didukung; DPR hanya muncul di related work (chunk 8), bukan retriever MultiFinRAG, yang memakai indeks FAISS IVF/PQ.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>MultiFinRAG mengelompokkan gambar tabel dan figur ke batch untuk diproses LLM multimodal open-source terkuantisasi yang menghasilkan JSON terstruktur dan ringkasan teks. Hasilnya bersama teks naratif di-embed dan diindeks (FAISS IVF/PQ) dengan threshold kesamaan sadar-modalitas, lalu strategi tiered fallback naik dari konteks teks ke teks+tabel+gambar bila perlu.</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>P16:pdf:1; P16:pdf:34</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>MultiFinRAG mengelompokkan gambar tabel dan figur ke batch untuk diproses LLM multimodal open-source terkuantisasi yang menghasilkan JSON terstruktur dan ringkasan teks. Hasilnya bersama teks naratif di-embed dan diindeks (FAISS IVF/PQ) dengan threshold kesamaan sadar-modalitas, lalu strategi tiered fallback naik dari konteks teks ke teks+tabel+gambar bila perlu.</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>P16</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Evaluation &amp; Metrics</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>quote_fuzzy</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Evaluasi dilakukan secara manual karena ukuran dataset, mengukur akurasi akhir QA tanpa metrik presisi-recall terperinci.</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>we opt for manual evaluations. This approach ensures more accurate assessments and minimizes the risk of misjudgments.</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>P16:pdf:34</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Evaluasi manual karena ukuran dataset dan keterbatasan sumber daya (chunk 34), fokus akurasi QA end-to-end tanpa statistik retrieval (chunk 25).</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>P16:pdf:34; P16:pdf:25</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>Evaluasi dilakukan secara manual karena ukuran dataset, mengukur akurasi akhir QA tanpa metrik presisi-recall terperinci.</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>P16</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Main Results</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>MultiFinRAG mencapai akurasi 90.4% pada pertanyaan berbasis teks, meningkat 15.1 poin persentase dibanding baseline.</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>accuracy for text-based questions using MultiFinRAG with Gemma 3 is 90.4%, representing an improvement of 15.1% compared to the Baseline framework</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>P16:pdf:34</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Akurasi 90.4% teks-based vs baseline Gemma 3 75.3% (selisih 15.1 poin) ada di chunk 34.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>P16:pdf:34</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>MultiFinRAG mencapai akurasi 90.4% pada pertanyaan berbasis teks, meningkat 15.1 poin persentase dibanding baseline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>P16</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Limitations</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>quote_not_found</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Penulis menyatakan bahwa metrik retrieval detail tidak dilaporkan dan evaluasi modul masih terbuka untuk studi lanjutan.</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Detailed information-retrieval statistics (precision, recall, etc.) for the retrieval components were collected during development but are omitted here due to space constraints</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>P16:pdf:32</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Statistik retrieval dihilangkan karena keterbatasan ruang (chunk 25) dan evaluasi per modul sebagai pekerjaan lanjutan (chunk 45). Catatan: CITED 32 tidak memuat klaim ini; sumbernya chunk 25 dan 45.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>P16:pdf:25; P16:pdf:45</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>Penulis menyatakan bahwa metrik retrieval detail tidak dilaporkan dan evaluasi modul masih terbuka untuk studi lanjutan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>P16</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Gap</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Tidak disebutkan evaluasi faithfulness atau abstention pada dokumen perbankan berbahasa Indonesia. Inferensi: Karena studi hanya menggunakan dokumen SEC berbahasa Inggris dan tidak menguji kemampuan menolak pertanyaan ketika konteks tidak ada, terdapat gap dalam evaluasi faithfulness dan abstention untuk dokumen perbankan Indonesia.</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Questions require both text and image/table are the most challenging, as they require information from both text and images or tables.</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>P16:pdf:31</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Dokumen SEC didukung (chunk 25); tidak ada chunk tentang abstention. Klaim bahasa Inggris tidak eksplisit tetapi tidak bertentangan.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>P16:pdf:25</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>Tidak disebutkan evaluasi faithfulness atau abstention pada dokumen perbankan berbahasa Indonesia. Inferensi: Karena studi hanya menggunakan dokumen SEC berbahasa Inggris dan tidak menguji kemampuan menolak pertanyaan ketika konteks tidak ada, terdapat gap dalam evaluasi faithfulness dan abstention untuk dokumen perbankan Indonesia.</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>P17</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Problem</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>Masalah yang diidentifikasi adalah trade-off antara robustness dan precision pada sistem RAG untuk pertanyaan dokumen keuangan.</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>robustness-precision trade-off</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>P17:abstract:0; P17:abstract:1; P17:abstract:2</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Trade-off robustness-precision dinyatakan eksplisit di abstract:0.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>P17:abstract:0</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>Masalah yang diidentifikasi adalah trade-off antara robustness dan precision pada sistem RAG untuk pertanyaan dokumen keuangan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>P17</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Domain &amp; Data</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>Domain keuangan, menggunakan benchmark FinDER dengan 1.500 kueri pada lima grup; tipe dokumen regulasi, ukuran tidak disebut, bahasa tidak disebut.</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>FinDER benchmark (1,500 queries across five groups)</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>P17:abstract:0; P17:abstract:1; P17:abstract:2</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Regulatory filings are only an example of a homogeneous corpus in the chunks; the document type of FinDER is not stated.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>Domain keuangan dengan benchmark FinDER sebanyak 1.500 kueri dalam lima grup; jenis dokumen, ukuran korpus, dan bahasa tidak disebut.</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>P17:abstract:0</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>Domain keuangan dengan benchmark FinDER sebanyak 1.500 kueri dalam lima grup; jenis dokumen, ukuran korpus, dan bahasa tidak disebut.</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>P17</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>RAG Method</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>Metode menggabungkan Semantic File Routing sebagai filter dokumen dengan retrieval berbasis chunk pada dokumen terfilter melalui arsitektur dua tahap Hybrid Document-Routed Retrieval (HDRR).</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Hybrid Document-Routed Retrieval (HDRR), a two-stage architecture that uses SFR as a document filter followed by chunk retrieval</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>P17:abstract:0; P17:abstract:1; P17:abstract:2</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>HDRR dua tahap: SFR sebagai filter dokumen lalu chunk retrieval.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>P17:abstract:1</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>Metode menggabungkan Semantic File Routing sebagai filter dokumen dengan retrieval berbasis chunk pada dokumen terfilter melalui arsitektur dua tahap Hybrid Document-Routed Retrieval (HDRR).</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>P17</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Evaluation &amp; Metrics</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Evaluasi menggunakan skor rata-rata, tingkat kegagalan, persentase jawaban benar, dan persentase jawaban sempurna, dibandingkan dengan CBR dan SFR sebagai baseline.</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>average score of 7.54 (25.2% above CBR, 16.9% above SFR)</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>P17:abstract:0; P17:abstract:1; P17:abstract:2</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Metrik average score, failure rate, correctness, perfect-answer rate dan baseline CBR/SFR ada di chunk.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>P17:abstract:0; P17:abstract:1</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>Evaluasi menggunakan skor rata-rata, tingkat kegagalan, persentase jawaban benar, dan persentase jawaban sempurna, dibandingkan dengan CBR dan SFR sebagai baseline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>P17</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Main Results</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>HDRR mencapai skor rata-rata 7.54, tingkat kegagalan 6.4%, correctness 67.7% (+18.7 pp), dan perfect-answer rate 20.1% (+6.3 pp).</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>6.4% failure rate, 67.7% correctness (+18.7 pp over CBR)</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>P17:abstract:1; P17:abstract:2</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Semua angka (7.54, 6.4%, 67.7% +18.7 pp, 20.1% +6.3 pp) cocok dengan abstract:1 (pp relatif terhadap CBR).</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>P17:abstract:1</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>HDRR mencapai skor rata-rata 7.54, tingkat kegagalan 6.4%, correctness 67.7% (+18.7 pp), dan perfect-answer rate 20.1% (+6.3 pp).</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>P17</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Limitations</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>tidak disebut</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>NOT_STATED_OK</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Chunk tidak memuat keterbatasan.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>tidak disebut</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>P17</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Gap</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
           <t>Inferensi: Meskipun HDRR meningkatkan akurasi, studi tidak mengevaluasi faithfulness atau kemampuan abstain pada dokumen perbankan berbahasa Indonesia.</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Hybrid Document-Routed Retrieval (HDRR) ... achieves the best performance on every metric</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>P17:abstract:0; P17:abstract:1; P17:abstract:2</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Seluruhnya inferensi; tidak bertentangan dengan chunk.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>P17:abstract:1</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>Inferensi: Meskipun HDRR meningkatkan akurasi, studi tidak mengevaluasi faithfulness atau kemampuan abstain pada dokumen perbankan berbahasa Indonesia.</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>P18</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Problem</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>Makalah mengidentifikasi tiga tantangan utama LLM multi-agent dalam keputusan berisiko tinggi: kontrol halusinasi, penggabungan penalaran semantik dengan simulasi numerik deterministik, serta auditabilitas end-to-end.</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Large language model (LLM)-based multi-agent systems face three open challenges in high-stakes decision support</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>P18:abstract:0</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Tiga tantangan sesuai abstract:0.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>P18:abstract:0</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>Makalah mengidentifikasi tiga tantangan utama LLM multi-agent dalam keputusan berisiko tinggi: kontrol halusinasi, penggabungan penalaran semantik dengan simulasi numerik deterministik, serta auditabilitas end-to-end.</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>P18</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Domain &amp; Data</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>quote_fuzzy</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>Kerangka diuji pada domain stress testing keuangan menggunakan dataset publik (FRED, Yahoo Finance), perpustakaan 150 peristiwa krisis, dan 10 portofolio institusional sintetis.</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>public financial datasets (FRED, Yahoo Finance), a library of 150 curated crisis events, and 10 synthetic institutional portfolios</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>P18:abstract:0; P18:abstract:1; P18:abstract:2</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Financial stress testing, FRED, Yahoo Finance, 150 crisis events, 10 synthetic portfolios ada.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>P18:abstract:0; P18:abstract:1; P18:abstract:2</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>Kerangka diuji pada domain stress testing keuangan menggunakan dataset publik (FRED, Yahoo Finance), perpustakaan 150 peristiwa krisis, dan 10 portofolio institusional sintetis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>P18</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>RAG Method</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>MacroRisk-Agent memperkenalkan pipeline retrieval-augmented generation dengan deterministic validation gates yang mengubah intent stres bahasa alami menjadi objek parameter ber-skema.</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>a retrieval-augmented generation (RAG) pipeline with deterministic validation gates</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>P18:abstract:0; P18:abstract:1</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>RAG pipeline dengan deterministic validation gates yang mengubah stress intent menjadi schema-constrained parameter objects.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>P18:abstract:0; P18:abstract:1</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>MacroRisk-Agent memperkenalkan pipeline retrieval-augmented generation dengan deterministic validation gates yang mengubah intent stres bahasa alami menjadi objek parameter ber-skema.</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>P18</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Evaluation &amp; Metrics</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>Evaluasi mencakup tingkat validitas 92.6% vs 78.4% (p&lt;0.001), peningkatan estimasi kerugian sistemik 52%, dan tingkat keberhasilan keputusan top-1 sebesar 68.6%.</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>92.6% validity rate versus 78.4% for RAG-augmented baselines (p&lt;0.001)</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>P18:abstract:1; P18:abstract:2</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Angka 92.6% vs 78.4% (p&lt;0.001), 52%, 68.6% sesuai; isinya lebih ke hasil, tetapi klaimnya didukung.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>P18:abstract:1</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>Evaluasi mencakup tingkat validitas 92.6% vs 78.4% (p&lt;0.001), peningkatan estimasi kerugian sistemik 52%, dan tingkat keberhasilan keputusan top-1 sebesar 68.6%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>P18</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Main Results</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>MacroRisk-Agent mencapai validitas 92.6% (lebih tinggi 14.2 poin persentase), menghasilkan estimasi kerugian sistemik 52% lebih tinggi, dan sukses keputusan top-1 sebesar 68.6%.</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>92.6% validity rate versus 78.4% for RAG-augmented baselines</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>P18:abstract:1</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Angka sesuai; selisih 14.2 pp = 92.6-78.4.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>P18:abstract:1</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>MacroRisk-Agent mencapai validitas 92.6% (lebih tinggi 14.2 poin persentase), menghasilkan estimasi kerugian sistemik 52% lebih tinggi, dan sukses keputusan top-1 sebesar 68.6%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>P18</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Limitations</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Validasi pada data institusional nyata belum dilakukan; penelitian masih bersifat proof-of-concept pada data sintetis dan publik.</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>validation on real institutional data is left to future work</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>P18:abstract:2</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Proof-of-concept; validasi pada data institusional nyata ditunda ke future work.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>P18:abstract:1; P18:abstract:2</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>Validasi pada data institusional nyata belum dilakukan; penelitian masih bersifat proof-of-concept pada data sintetis dan publik.</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>P18</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Gap</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Penulis tidak mengevaluasi faithfulness atau kemampuan abstention pada dokumen perbankan berbahasa Indonesia; mereka hanya menguji pada dataset publik berbahasa Inggris dan data sintetis. Inferensi: Oleh karena itu, belum ada analisis tentang bagaimana RAG menangani konteks bahasa Indonesia atau menolak menjawab bila konteks tidak memadai.</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>validation on real institutional data is left to future work</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>P18:abstract:2</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Premis faktual 'dataset publik berbahasa Inggris' tidak dinyatakan di chunk; bahasa data tidak disebut sama sekali.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>Studi hanya dievaluasi sebagai proof-of-concept pada dataset keuangan publik (FRED, Yahoo Finance), 150 peristiwa krisis kurasi, dan 10 portofolio institusional sintetis; validasi pada data institusional nyata belum dilakukan. Inferensi: faithfulness dan kemampuan abstention pada dokumen perbankan berbahasa Indonesia belum dikaji.</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>P18:abstract:1; P18:abstract:2</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>Studi hanya dievaluasi sebagai proof-of-concept pada dataset keuangan publik (FRED, Yahoo Finance), 150 peristiwa krisis kurasi, dan 10 portofolio institusional sintetis; validasi pada data institusional nyata belum dilakukan. Inferensi: faithfulness dan kemampuan abstention pada dokumen perbankan berbahasa Indonesia belum dikaji.</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>P19</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Problem</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Penelitian ini mengevaluasi sistem RAG yang menjelaskan kontrak asuransi Quebec dengan fokus pada pengalaman pengguna secara manusiawi.</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>conducting a large-scale extrinsic study within the Quebec (francophone) insurance context</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>P19:pdf:10</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Studi ekstrinsik human-centric dalam konteks asuransi Quebec (francophone).</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>P19:pdf:10</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>Penelitian ini mengevaluasi sistem RAG yang menjelaskan kontrak asuransi Quebec dengan fokus pada pengalaman pengguna secara manusiawi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>P19</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Domain &amp; Data</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>quote_not_found</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Domainnya adalah asuransi kendaraan di Quebec, menggunakan dataset percakapan 3.759 pasangan pesan-jawaban dari 154 peserta yang mayoritas berbahasa Prancis.</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Study Sample Our user study successfully concluded with the collection of complete responses from 154 participants, along with the 3,759 message-answer pairs</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>P19:pdf:11; P19:pdf:12; P19:pdf:5</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Asuransi kendaraan Quebec, 154 peserta, 3.759 pasangan pesan-jawaban didukung; klaim 'peserta mayoritas berbahasa Prancis' tidak dinyatakan (chunk hanya menyebut konteks francophone dan peserta dari Universitas Laval).</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>Domain asuransi kendaraan bermotor di Quebec (konteks francophone). Data berupa 3.759 pasangan pesan-jawaban dari 154 peserta (mahasiswa dan karyawan Universitas Laval) selama 30 hari, ditambah survei pasca-penggunaan 21 pertanyaan.</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>P19:pdf:10; P19:pdf:11; P19:pdf:12; P19:pdf:15; P19:pdf:42</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>Domain asuransi kendaraan bermotor di Quebec (konteks francophone). Data berupa 3.759 pasangan pesan-jawaban dari 154 peserta (mahasiswa dan karyawan Universitas Laval) selama 30 hari, ditambah survei pasca-penggunaan 21 pertanyaan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>P19</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>RAG Method</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>Sistem menggunakan model LLM OpenAI “o3-2025-04-16” dengan arsitektur RAG standar, namun detail retriever dan strategi chunking tidak dijelaskan.</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>The insurance RAG system under evaluation utilizes OpenAI “o3-2025-04-16” LLM, along with the same RAG as described in [5]</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>P19:pdf:11; P19:pdf:5; P19:pdf:42</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>LLM o3-2025-04-16 dan 'RAG yang sama seperti di [5]' didukung; karakterisasi 'arsitektur RAG standar' tidak didukung.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>Sistem memakai LLM OpenAI o3-2025-04-16 dengan arsitektur RAG yang sama seperti yang dijelaskan pada referensi [5] makalah tersebut; detail retriever dan strategi chunking tidak dijelaskan dalam teks yang tersedia.</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>P19:pdf:11</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>Sistem memakai LLM OpenAI o3-2025-04-16 dengan arsitektur RAG yang sama seperti yang dijelaskan pada referensi [5] makalah tersebut; detail retriever dan strategi chunking tidak dijelaskan dalam teks yang tersedia.</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>P19</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Evaluation &amp; Metrics</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>Evaluasi mencakup survei Likert 7-point, analisis statistik t-test, Kruskal-Wallis, dan korelasi Pearson untuk mengukur kepuasan, usaha kognitif, dan kepercayaan.</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Most questions utilized a 7-point Likert scale</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>P19:pdf:13; P19:pdf:15; P19:pdf:20</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Likert 7-point, t-test, Kruskal-Wallis, Pearson, tema SS/CE/PA/PR dan pertanyaan trust (Q7) ada.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>P19:pdf:12; P19:pdf:13; P19:pdf:15; P19:pdf:20</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>Evaluasi mencakup survei Likert 7-point, analisis statistik t-test, Kruskal-Wallis, dan korelasi Pearson untuk mengukur kepuasan, usaha kognitif, dan kepercayaan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>P19</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Main Results</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>quote_fuzzy</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>Pengguna dengan literasi rendah melaporkan kepuasan secara signifikan lebih tinggi, sementara manfaat inti sistem diakui secara universal oleh semua kelompok.</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>reported significantly higher overall satisfaction than their high-literacy counterparts</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>P19:pdf:21; P19:pdf:22; P19:pdf:8</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Kepuasan lebih tinggi pada kelompok literasi rendah; trust, edukasi, empowerment seragam antar kelompok.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>P19:pdf:20; P19:pdf:21; P19:pdf:22</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>Pengguna dengan literasi rendah melaporkan kepuasan secara signifikan lebih tinggi, sementara manfaat inti sistem diakui secara universal oleh semua kelompok.</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>P19</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Limitations</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>Penulis mencatat adanya kesalahan faktual, preferensi pengguna terhadap agen manusia, serta keterbatasan generalisasi karena sampel berpendidikan tinggi dan setting eksperimental.</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>the system is not yet ready for fully autonomous, unsupervised public deployment</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>P19:pdf:37; P19:pdf:38; P19:pdf:24</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Kesalahan faktual, preferensi agen manusia, sampel lebih terdidik/literasi tinggi, setting eksperimental 30 menit didukung.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>P19:pdf:37; P19:pdf:40; P19:pdf:41</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>Penulis mencatat adanya kesalahan faktual, preferensi pengguna terhadap agen manusia, serta keterbatasan generalisasi karena sampel berpendidikan tinggi dan setting eksperimental.</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>P19</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Gap</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>Penelitian ini tidak mengevaluasi faithfulness atau kemampuan abstention RAG pada dokumen perbankan berbahasa Indonesia; fokusnya terbatas pada konteks asuransi Quebec berbahasa Prancis. Inferensi: Karena tidak ada pengujian terhadap keakuratan faktual atau penolakan ketika konteks tidak memadai, gap muncul untuk aplikasi bahasa Indonesia di domain perbankan.</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>may not be fully generalizable to a broader, more diverse demographic</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>P19:pdf:41; P19:pdf:24</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Premis konteks Quebec francophone didukung, tetapi inferensi 'tidak ada pengujian terhadap keakuratan faktual' bertentangan sebagian dengan chunk: pengguna mendokumentasikan kesalahan faktual dan kontradiksi logis.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>Studi berfokus pada evaluasi human-centric (UX) RAG di konteks asuransi kendaraan Quebec yang francophone; kesalahan faktual hanya dilaporkan dari temuan pengguna, bukan diukur dengan metrik faithfulness. Inferensi: faithfulness terukur dan kemampuan abstention pada dokumen perbankan berbahasa Indonesia belum dikaji.</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>P19:pdf:10; P19:pdf:37; P19:pdf:42</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>Studi berfokus pada evaluasi human-centric (UX) RAG di konteks asuransi kendaraan Quebec yang francophone; kesalahan faktual hanya dilaporkan dari temuan pengguna, bukan diukur dengan metrik faithfulness. Inferensi: faithfulness terukur dan kemampuan abstention pada dokumen perbankan berbahasa Indonesia belum dikaji.</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>P20</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Problem</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>Penelitian ini mengevaluasi dua pendekatan peningkatan performa LLM, yaitu fine-tuning dan retrieval-augmented generation (RAG), untuk mendukung pengambilan keputusan hukum dalam konteks pajak pertambahan nilai (VAT).</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Methods This study experimentally evaluates two common approaches for enhancing LLM performance—fine-tuning and retrieval-augmented generation (RAG)</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>P20:abstract:0</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Evaluasi fine-tuning vs RAG untuk keputusan hukum VAT Austria/EU.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>P20:abstract:0</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>Penelitian ini mengevaluasi dua pendekatan peningkatan performa LLM, yaitu fine-tuning dan retrieval-augmented generation (RAG), untuk mendukung pengambilan keputusan hukum dalam konteks pajak pertambahan nilai (VAT).</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>P20</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Domain &amp; Data</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>Domainnya adalah pajak nilai tambah (VAT) di Austria/EU, menggunakan kasus VAT dari buku teks serta kasus nyata dari firma konsultan pajak; bahasa tidak disebut.</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>applied to both textbook VAT cases and real-world cases from a tax consulting firm</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>P20:abstract:0; P20:abstract:1</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>VAT Austria/EU, kasus buku teks dan kasus nyata firma konsultan pajak.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>P20:abstract:0</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>Domainnya adalah pajak nilai tambah (VAT) di Austria/EU, menggunakan kasus VAT dari buku teks serta kasus nyata dari firma konsultan pajak; bahasa tidak disebut.</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>P20</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>RAG Method</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>tidak disebut</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>NOT_STATED_WRONG</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Chunk menyatakan RAG diterapkan dan dibandingkan dengan fine-tuning untuk mencari konfigurasi optimal, walau tanpa detail teknis.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>Studi menerapkan RAG dan membandingkannya dengan fine-tuning untuk mengidentifikasi konfigurasi sistem berbasis LLM yang optimal; detail retriever, chunking, dan model tidak disebut.</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>P20:abstract:0</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>Studi menerapkan RAG dan membandingkannya dengan fine-tuning untuk mengidentifikasi konfigurasi sistem berbasis LLM yang optimal; detail retriever, chunking, dan model tidak disebut.</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>P20</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Evaluation &amp; Metrics</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>tidak disebut</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>NOT_STATED_OK</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Hanya disebut menilai kemampuan legal reasoning pada kasus buku teks dan nyata; tidak ada metrik.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>tidak disebut</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>P20</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Main Results</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>quote_fuzzy</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>LLM yang dikonfigurasi dengan tepat dapat secara efektif mendukung profesional pajak dalam tugas-tugas VAT, mengotomatisasi pekerjaan rutin, dan menghasilkan justifikasi hukum yang kuat.</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Properly configured LLMs can effectively support tax professionals in VAT-related tasks, automating routine work, providing initial analyses, and generating legally grounded justifications for decisions</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>P20:abstract:0; P20:abstract:1</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Klaim umum didukung, tetapi 'justifikasi hukum yang kuat' melebihkan 'legally grounded'; 'initial analyses' terlewat.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>LLM yang dikonfigurasi dengan tepat dapat mendukung profesional pajak dalam tugas VAT: mengotomatisasi pekerjaan rutin, memberikan analisis awal, dan menghasilkan justifikasi keputusan yang berlandaskan hukum (legally grounded).</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>P20:abstract:0; P20:abstract:1</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>LLM yang dikonfigurasi dengan tepat dapat mendukung profesional pajak dalam tugas VAT: mengotomatisasi pekerjaan rutin, memberikan analisis awal, dan menghasilkan justifikasi keputusan yang berlandaskan hukum (legally grounded).</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>P20</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Limitations</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>Prototipe belum siap untuk otomatisasi penuh karena sensitivitas domain hukum, serta masih terdapat keterbatasan dalam menangani pengetahuan implisit klien dan dokumentasi kontekstual.</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>current prototypes are not yet ready for full automation given the sensitivity of the legal domain, and limitations persist in handling implicit client knowledge and context-specific documentation</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>P20:abstract:1</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Sesuai abstract:1.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>P20:abstract:1</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>Prototipe belum siap untuk otomatisasi penuh karena sensitivitas domain hukum, serta masih terdapat keterbatasan dalam menangani pengetahuan implisit klien dan dokumentasi kontekstual.</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>P20</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Gap</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>Inferensi: Makalah ini tidak membahas faithfulness atau abstention pada sistem RAG, tidak menggunakan dokumen perbankan berbahasa Indonesia, sehingga tidak menjawab fokus penelitian yang menilai kemampuan RAG dalam konteks tersebut.</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>LLMs show strong potential to assist tax consultants by reducing workload and supporting VAT decision-making</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>P20:abstract:0; P20:abstract:1</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Seluruhnya inferensi; tidak bertentangan dengan chunk.</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>P20:abstract:0; P20:abstract:1</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>Inferensi: Makalah ini tidak membahas faithfulness atau abstention pada sistem RAG, tidak menggunakan dokumen perbankan berbahasa Indonesia, sehingga tidak menjawab fokus penelitian yang menilai kemampuan RAG dalam konteks tersebut.</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>P21</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Problem</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>Penelitian ini mengevaluasi peluncuran pilot GenAI "no-regret" dalam satu kuartal untuk meningkatkan nilai pada Alpes Bank.</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>deliver a “no-regret” GenAI pilot within one quarter</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>P21:abstract:0</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Paper adalah teaching case, bukan penelitian evaluatif; 'untuk meningkatkan nilai' tidak disebut. Chunk: model bisnis bank ditantang GenAI, mandat pilot no-regret dalam satu kuartal.</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>Teaching case ini menggambarkan Alpes Bank, yang model layanan premium berbasis cabangnya ditantang oleh GenAI, dan mandat dewan untuk menghadirkan pilot GenAI 'no-regret' dalam satu kuartal; Part B membahas fondasi organisasi dan tata kelola untuk penskalaan GenAI.</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>P21:abstract:0; P21:abstract:1</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>Teaching case ini menggambarkan Alpes Bank, yang model layanan premium berbasis cabangnya ditantang oleh GenAI, dan mandat dewan untuk menghadirkan pilot GenAI 'no-regret' dalam satu kuartal; Part B membahas fondasi organisasi dan tata kelola untuk penskalaan GenAI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>P21</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Domain &amp; Data</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>Studi kasus pada Alpes Bank, bank universal Swiss, menggunakan email inquiry sebagai data; bahasa tidak disebut.</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Alpes Bank, a Swiss universal bank whose branch-centric, premium-service model is challenged by generative AI</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>P21:abstract:0</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Alpes Bank bank universal Swiss didukung; 'email inquiry sebagai data' tidak dinyatakan (tidak ada dataset; email assistant menangani inquiry rutin).</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>Studi kasus (teaching case) pada Alpes Bank, bank universal Swiss; use case berupa email assistant untuk inquiry rutin. Dataset dan bahasa tidak disebut.</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>P21:abstract:0</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>Studi kasus (teaching case) pada Alpes Bank, bank universal Swiss; use case berupa email assistant untuk inquiry rutin. Dataset dan bahasa tidak disebut.</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>P21</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>RAG Method</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>Tim membangun email assistant berbasis retrieval-augmented generation (RAG) bekerja sama dengan AILabs; detail teknis tidak disebut.</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>builds a retrieval-augmented generation (RAG) email assistant with an external partner (i.e., AILabs)</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>P21:abstract:0</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>RAG email assistant bersama AILabs.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>P21:abstract:0</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>Tim membangun email assistant berbasis retrieval-augmented generation (RAG) bekerja sama dengan AILabs; detail teknis tidak disebut.</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>P21</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Evaluation &amp; Metrics</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>Evaluasi dilakukan dengan mengukur pengurangan waktu penanganan inquiry rutin, tercatat penurunan 21%.</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>the GenAI email assistant reduces handling time for routine inquiries by 21%</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>P21:abstract:0</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Pengurangan waktu penanganan 21% (pada limited rollout).</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>P21:abstract:0</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>Evaluasi dilakukan dengan mengukur pengurangan waktu penanganan inquiry rutin, tercatat penurunan 21%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>P21</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Main Results</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>Email assistant berbasis GenAI mengurangi waktu penanganan inquiry rutin sebesar 21%.</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>the GenAI email assistant reduces handling time for routine inquiries by 21%</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>P21:abstract:0</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>21% pengurangan handling time didukung.</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>P21:abstract:0</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>Email assistant berbasis GenAI mengurangi waktu penanganan inquiry rutin sebesar 21%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>P21</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Limitations</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>tidak disebut</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>NOT_STATED_WRONG</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Chunk menyebut pilot memunculkan beberapa 'unexpected tensions' dan hasil 21% hanya dari limited rollout.</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>Pilot GenAI memunculkan sejumlah ketegangan (tensions) yang tidak terduga, dan hasil 21% hanya diperoleh dari rollout terbatas; rincian ketegangan tersebut tidak disebut.</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>P21:abstract:0</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>Pilot GenAI memunculkan sejumlah ketegangan (tensions) yang tidak terduga, dan hasil 21% hanya diperoleh dari rollout terbatas; rincian ketegangan tersebut tidak disebut.</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>P21</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Gap</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>Inferensi: Penelitian ini tidak mengevaluasi faithfulness atau abstention pada dokumen produk perbankan berbahasa Indonesia, sehingga tidak menjawab fokus riset yang diusulkan.</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Bank move from a special-project setup to an organizational design and governance process that supports enterprise-wide scaling</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>P21:abstract:1</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Seluruhnya inferensi; tidak bertentangan dengan chunk.</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>P21:abstract:0; P21:abstract:1</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>Inferensi: Penelitian ini tidak mengevaluasi faithfulness atau abstention pada dokumen produk perbankan berbahasa Indonesia, sehingga tidak menjawab fokus riset yang diusulkan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>P22</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Problem</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>Penelitian ini memperkenalkan NextRAG, kerangka Retrieval-Augmented Generation bilingual untuk meningkatkan penelusuran pengetahuan keuangan dan menjawab pertanyaan.</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>This study introduces NextRAG, a bilingual Retrieval-Augmented Generation (RAG) framework for financial knowledge retrieval and question answering</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>P22:abstract:0</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>NextRAG bilingual untuk financial knowledge retrieval dan QA (konteks Bangladesh).</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>P22:abstract:0</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>Penelitian ini memperkenalkan NextRAG, kerangka Retrieval-Augmented Generation bilingual untuk meningkatkan penelusuran pengetahuan keuangan dan menjawab pertanyaan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>P22</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Domain &amp; Data</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>Fokus pada dokumen keuangan multibahasa dari institusi dan regulator di Bangladesh, serta dataset Q&amp;A keuangan bilingual yang beragam.</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Financial institutions and regulators produce large volumes of complex, multilingual documents... Evaluation on a diverse bilingual financial Q&amp;A dataset</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>P22:abstract:0; P22:abstract:1</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Dokumen keuangan multibahasa, konteks Bangladesh, dataset Q&amp;A keuangan bilingual didukung.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>P22:abstract:0; P22:abstract:1</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>Fokus pada dokumen keuangan multibahasa dari institusi dan regulator di Bangladesh, serta dataset Q&amp;A keuangan bilingual yang beragam.</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>P22</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>RAG Method</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>Menggunakan retrieval sparse BM25 dengan smoothing Dirichlet, fusi Reciprocal Rank Fusion, re-ranking cross-encoder, serta prompting yang sadar bahasa untuk Bangla dan Inggris.</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>NextRAG employs specialized preprocessing... integrates sparse retrieval with BM25, probabilistic query modeling via Dirichlet smoothing, and fuses results using Reciprocal Rank Fusion (RRF), followed by cross-encoder re-ranking</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>P22:abstract:0; P22:abstract:1</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>BM25, Dirichlet smoothing, RRF, cross-encoder re-ranking, language-aware prompting Bangla-Inggris didukung (OCR preprocessing tidak disebut tetapi bukan kesalahan).</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>P22:abstract:0; P22:abstract:1</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>Menggunakan retrieval sparse BM25 dengan smoothing Dirichlet, fusi Reciprocal Rank Fusion, re-ranking cross-encoder, serta prompting yang sadar bahasa untuk Bangla dan Inggris.</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>P22</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Evaluation &amp; Metrics</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>Dievaluasi pada dataset Q&amp;A bilingual dengan metrik mean cosine similarity dan F1 score, membandingkan dengan RAG konvensional.</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>achieving a mean cosine similarity of 0.77 and an F1 score of 68.3%</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>P22:abstract:1</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Mean cosine similarity dan F1, dibanding RAG konvensional.</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>P22:abstract:1</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>Dievaluasi pada dataset Q&amp;A bilingual dengan metrik mean cosine similarity dan F1 score, membandingkan dengan RAG konvensional.</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>P22</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Main Results</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>NextRAG secara konsisten mengungguli RAG konvensional, memperoleh mean cosine similarity 0.77 dan F1 68.3%.</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>NextRAG consistently outperforms conventional RAG, achieving a mean cosine similarity of 0.77 and an F1 score of 68.3%</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>P22:abstract:1</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>0.77 dan 68.3% sesuai.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>P22:abstract:1</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>NextRAG secara konsisten mengungguli RAG konvensional, memperoleh mean cosine similarity 0.77 dan F1 68.3%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>P22</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Limitations</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>tidak disebut</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>NOT_STATED_OK</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Chunk tidak memuat keterbatasan.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>tidak disebut</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>P22</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Gap</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>quote_verified</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>Inferensi: Meskipun NextRAG menangani dokumen bilingual, penelitian ini tidak mengevaluasi faithfulness atau kemampuan abstention pada dokumen perbankan berbahasa Indonesia, sehingga belum menjawab fokus riset yang diinginkan.</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Bangladeshi context... low-resource bilingual setting</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>P22:abstract:0; P22:abstract:1</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>SUPPORTED</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Inferensi; premis bilingual didukung.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>P22:abstract:0; P22:abstract:1</t>
-        </is>
-      </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>Inferensi: Meskipun NextRAG menangani dokumen bilingual, penelitian ini tidak mengevaluasi faithfulness atau kemampuan abstention pada dokumen perbankan berbahasa Indonesia, sehingga belum menjawab fokus riset yang diinginkan.</t>
         </is>
       </c>
     </row>
